--- a/public/assets/2430_2530_Members.xlsx
+++ b/public/assets/2430_2530_Members.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\Raziq_Projects\gdscmmu\public\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{935D1FD3-C4B2-4A97-93A4-BC624CC0E703}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AA83D35F-6824-433B-904A-D5B631A806E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="247">
   <si>
     <t>Registration terms</t>
   </si>
@@ -387,6 +387,381 @@
   <si>
     <t>Alim Imanmalik</t>
   </si>
+  <si>
+    <t>Muhammad Amir Rahimi Bin Muhammad Assuad</t>
+  </si>
+  <si>
+    <t>KHALID HOSHAM OMER MOHAMED</t>
+  </si>
+  <si>
+    <t>RAYYAN SYAHMI BIN SUKRI EFENDI</t>
+  </si>
+  <si>
+    <t>MAGILNAN A/L ARIVANANDAN</t>
+  </si>
+  <si>
+    <t>Bethany Bond Bouniu</t>
+  </si>
+  <si>
+    <t>EAOSN CHOO ZHEN YI</t>
+  </si>
+  <si>
+    <t>SUSNITHA A/P BALAMURUGAN</t>
+  </si>
+  <si>
+    <t>DEVESH A/L KRISHNASAMY</t>
+  </si>
+  <si>
+    <t>May Myat Noe Htun</t>
+  </si>
+  <si>
+    <t>ERUHANAFUI AMURO</t>
+  </si>
+  <si>
+    <t>ACERINE TERYLRATT A/P PHI RAT</t>
+  </si>
+  <si>
+    <t>Myat Min Han</t>
+  </si>
+  <si>
+    <t>GOH KAI YAO</t>
+  </si>
+  <si>
+    <t>Syahreza Muharman</t>
+  </si>
+  <si>
+    <t>MUHAMMAD YUSUF BIN RIDUAN</t>
+  </si>
+  <si>
+    <t>Eula Samantha Reyes</t>
+  </si>
+  <si>
+    <t>Tan Kenji</t>
+  </si>
+  <si>
+    <t>Palaniappan</t>
+  </si>
+  <si>
+    <t>NUR IMAN BINTI MOHD SHAHREL FAIZAL</t>
+  </si>
+  <si>
+    <t>Mohamad Ezzwafri Bin Mohamad Ezri</t>
+  </si>
+  <si>
+    <t>Muhammad Haikal bin Mohd Hazim</t>
+  </si>
+  <si>
+    <t>Sanjeevan A/L Rames</t>
+  </si>
+  <si>
+    <t>Muhammad Ashiqur Rahman</t>
+  </si>
+  <si>
+    <t>Syed Munyem</t>
+  </si>
+  <si>
+    <t>Irfan zuhair bin Azman</t>
+  </si>
+  <si>
+    <t>MUHAMMAD NUR AIZAD BIN MURTADHA</t>
+  </si>
+  <si>
+    <t>ADEENA SHAHIRA BINTI MOHD HAFIZ</t>
+  </si>
+  <si>
+    <t>CHEW JIA YI</t>
+  </si>
+  <si>
+    <t>Chan Jia Yi</t>
+  </si>
+  <si>
+    <t>MUHAMMAD ZAKWAN BIN MOHAMAD SHAHIR</t>
+  </si>
+  <si>
+    <t>Yap Li Xuan</t>
+  </si>
+  <si>
+    <t>KYAW HTET MYAT TUN</t>
+  </si>
+  <si>
+    <t>Chadi El Dukhi</t>
+  </si>
+  <si>
+    <t>Homam Fadel bin Abdulla</t>
+  </si>
+  <si>
+    <t>MUHAMMAD IQBAAL ZACKARY BIN MOHD KHALID</t>
+  </si>
+  <si>
+    <t>Liu Liao Lyot</t>
+  </si>
+  <si>
+    <t>Khandaker Zarif Hossain</t>
+  </si>
+  <si>
+    <t>AIDIL AMDAN BIN ZULAIME</t>
+  </si>
+  <si>
+    <t>SITI AISYAH SOFEA BINTI AZIZUL</t>
+  </si>
+  <si>
+    <t>TAN YU KAI</t>
+  </si>
+  <si>
+    <t>Vipul Kumar</t>
+  </si>
+  <si>
+    <t>MUHAMMAD HAFIZUDDIN BIN MOHD KHALIL AL FARID</t>
+  </si>
+  <si>
+    <t>Khalid Bayzid</t>
+  </si>
+  <si>
+    <t>NUR SYAFIEQA AYUNI BINTI SAHRIMAN</t>
+  </si>
+  <si>
+    <t>TAY SHI XIANG</t>
+  </si>
+  <si>
+    <t>DARCHANAA MARAN A/L SUGUMARAN</t>
+  </si>
+  <si>
+    <t>NUR ADILAH BINTI NORHISHAM</t>
+  </si>
+  <si>
+    <t>Nur Iman binti Mohamad Idros</t>
+  </si>
+  <si>
+    <t>AMEERA IZZATI BT ISMAIL</t>
+  </si>
+  <si>
+    <t>Dyu Kristian Jian Hua</t>
+  </si>
+  <si>
+    <t>MD NAFIZ UDDIN FUAD</t>
+  </si>
+  <si>
+    <t>Afrian Rizki Anugrah</t>
+  </si>
+  <si>
+    <t>Joy Yu Wen</t>
+  </si>
+  <si>
+    <t>Muhammad Haziq Irfan Bin Zairul</t>
+  </si>
+  <si>
+    <t>Aljwhari mayada</t>
+  </si>
+  <si>
+    <t>BIBI NURMAHIRAH</t>
+  </si>
+  <si>
+    <t>ANGELA WONG XIN YI</t>
+  </si>
+  <si>
+    <t>SO LI HENG</t>
+  </si>
+  <si>
+    <t>Muntamimur Rahaman</t>
+  </si>
+  <si>
+    <t>TAN SZU RI</t>
+  </si>
+  <si>
+    <t>PRAVEENA NAIR A/P SURINDRAGANESH</t>
+  </si>
+  <si>
+    <t>Ahmed Abdalla Awadalla Dafaalla</t>
+  </si>
+  <si>
+    <t>KABILAN A/L JEGATHESAN</t>
+  </si>
+  <si>
+    <t>SHARVIN A/L RAMANATHAN</t>
+  </si>
+  <si>
+    <t>Mohammed Alaeldin Mohamed Abdien</t>
+  </si>
+  <si>
+    <t>Pua Yee Thong</t>
+  </si>
+  <si>
+    <t>Agnes Sang Li Ping</t>
+  </si>
+  <si>
+    <t>HAREEN A/L VIJAYA KUMAR</t>
+  </si>
+  <si>
+    <t>Vishallan Ramamurthi</t>
+  </si>
+  <si>
+    <t>Manesh Mathialagen</t>
+  </si>
+  <si>
+    <t>Nawaf Shafik Al Kabbani</t>
+  </si>
+  <si>
+    <t>ZEID KHABAZEH</t>
+  </si>
+  <si>
+    <t>Hein Htet Zaw</t>
+  </si>
+  <si>
+    <t>ARIEF RIDZKEEN BIN ABDUL JAMAL</t>
+  </si>
+  <si>
+    <t>WONG JUN KIT</t>
+  </si>
+  <si>
+    <t>Sayid Abdur-Rahman Al-Aidarus</t>
+  </si>
+  <si>
+    <t>NAHIN BIN MONIR</t>
+  </si>
+  <si>
+    <t>NURIN ALICE BATRISYIA BINTI HUSSIN</t>
+  </si>
+  <si>
+    <t>SANDY RURAN KAMUA</t>
+  </si>
+  <si>
+    <t>MUHAMMED EMIR 'AQASYA BIN RUZAINEE</t>
+  </si>
+  <si>
+    <t>Khoo Ji Sheng</t>
+  </si>
+  <si>
+    <t>KASHVIN GEORGE</t>
+  </si>
+  <si>
+    <t>MUHAMMAD FAHMI AIMAN BIN MOHD FAUZU</t>
+  </si>
+  <si>
+    <t>FATIN NURDINI BINTI JAMSARI</t>
+  </si>
+  <si>
+    <t>FEBRIAN AULIA BIN IBNUL HAJJAR</t>
+  </si>
+  <si>
+    <t>UMAR ZAID BIN AZZADDIN</t>
+  </si>
+  <si>
+    <t>ALI ABBAS ABUBAKARELSIDIG</t>
+  </si>
+  <si>
+    <t>MUHAMMED MUTASIM ALI MADANI</t>
+  </si>
+  <si>
+    <t>ABDALLAH ELNOUR OSMAN ELNOUR</t>
+  </si>
+  <si>
+    <t>RIVALINO GEO RIZQY</t>
+  </si>
+  <si>
+    <t>Khaled Mutwakil Abdelrazig Mohamed</t>
+  </si>
+  <si>
+    <t>BARANIDARRAN A/L SIVABALAN</t>
+  </si>
+  <si>
+    <t>MUHAMMAD MUHAIMIN BIN MOHAMED RUSLI</t>
+  </si>
+  <si>
+    <t>NOR ZAREEF ZIDANE BIN NOR EFFENDI</t>
+  </si>
+  <si>
+    <t>HARIZ HILMIY BIN MOHD SHAMSURIZAL</t>
+  </si>
+  <si>
+    <t>MUHAMMAD MUHAIMIN BIN MAZLAN</t>
+  </si>
+  <si>
+    <t>MUHAMMAD AMSYAR BIN PAIZOL AKMAN</t>
+  </si>
+  <si>
+    <t>LUQMAN HAKIM BIN MOHAMMAD ZIKRI</t>
+  </si>
+  <si>
+    <t>NUR KHALIDAH ADILAH BINTI MOHAMMAD</t>
+  </si>
+  <si>
+    <t>NUR SAMIRA BINTI OTHMAN</t>
+  </si>
+  <si>
+    <t>KIASATI DIAN NAJMA BINTI ANDRIANTO ARFAN WARDHANA</t>
+  </si>
+  <si>
+    <t>Muhammad Habibullah</t>
+  </si>
+  <si>
+    <t>AKIRA DHEVIANT JHEYARESA</t>
+  </si>
+  <si>
+    <t>Waqar Azeem</t>
+  </si>
+  <si>
+    <t>MUHAMMAD NAFHAN AIMAN BIN MOHD NAZRUDIN</t>
+  </si>
+  <si>
+    <t>Jawiriyyah Hamza Fadhlalmawla</t>
+  </si>
+  <si>
+    <t>ARIEF IRFAN HAKIMI BIN SALEHUDDIN</t>
+  </si>
+  <si>
+    <t>Narmatha Paartiban</t>
+  </si>
+  <si>
+    <t>Narmatha a/p Narendran</t>
+  </si>
+  <si>
+    <t>Yassin mohamed mohsen mohamed hassan badawy</t>
+  </si>
+  <si>
+    <t>Syed Farhan Bin Salahudeen</t>
+  </si>
+  <si>
+    <t>SYED HAQEEM BIN SYED ISA</t>
+  </si>
+  <si>
+    <t>SHAWN HUANG QI YANG</t>
+  </si>
+  <si>
+    <t>Zul Fadhli Bin Zaiman</t>
+  </si>
+  <si>
+    <t>NURAFRINA BATRISYIA BINTI NORDZAMAN</t>
+  </si>
+  <si>
+    <t>ABISEK MITTHARAN A/L RAMAYS</t>
+  </si>
+  <si>
+    <t>NURISH MIZA BINTI NU AMRAN SHAH</t>
+  </si>
+  <si>
+    <t>LIM ZI JUN</t>
+  </si>
+  <si>
+    <t>WAN NUR FARHANAH BINTI WAN AMIR NIZAM</t>
+  </si>
+  <si>
+    <t>DANIA AISHA BINTI IZWAN ZARIK</t>
+  </si>
+  <si>
+    <t>FARIHA ALEEYA BINTI MOHD SANI</t>
+  </si>
+  <si>
+    <t>MUHAMMAD HAFIY AL-HAFIIZH BIN JOHARI</t>
+  </si>
+  <si>
+    <t>MOHAMAD FAIZUL HANIF BIN MOHAMED NAZIR</t>
+  </si>
+  <si>
+    <t>MUHAMMAD NAFIZ BIN MOHD FAUZI</t>
+  </si>
+  <si>
+    <t>AWAB HAYTHAM ABDELGABAR</t>
+  </si>
 </sst>
 </file>
 
@@ -431,7 +806,7 @@
       <name val="Roboto"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -453,6 +828,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D2E9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -512,7 +893,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -542,6 +923,18 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4695,10 +5088,14 @@
       <c r="Y122" s="4"/>
       <c r="Z122" s="4"/>
     </row>
-    <row r="123" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:26" ht="35.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A123" s="4"/>
-      <c r="B123" s="5"/>
-      <c r="C123" s="7"/>
+      <c r="B123" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C123" s="13" t="s">
+        <v>122</v>
+      </c>
       <c r="D123" s="4"/>
       <c r="E123" s="4"/>
       <c r="F123" s="4"/>
@@ -4723,10 +5120,14 @@
       <c r="Y123" s="4"/>
       <c r="Z123" s="4"/>
     </row>
-    <row r="124" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A124" s="4"/>
-      <c r="B124" s="5"/>
-      <c r="C124" s="7"/>
+      <c r="B124" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C124" s="14" t="s">
+        <v>123</v>
+      </c>
       <c r="D124" s="4"/>
       <c r="E124" s="4"/>
       <c r="F124" s="4"/>
@@ -4751,10 +5152,14 @@
       <c r="Y124" s="4"/>
       <c r="Z124" s="4"/>
     </row>
-    <row r="125" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A125" s="4"/>
-      <c r="B125" s="5"/>
-      <c r="C125" s="7"/>
+      <c r="B125" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C125" s="14" t="s">
+        <v>124</v>
+      </c>
       <c r="D125" s="4"/>
       <c r="E125" s="4"/>
       <c r="F125" s="4"/>
@@ -4779,10 +5184,14 @@
       <c r="Y125" s="4"/>
       <c r="Z125" s="4"/>
     </row>
-    <row r="126" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A126" s="4"/>
-      <c r="B126" s="5"/>
-      <c r="C126" s="7"/>
+      <c r="B126" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C126" s="14" t="s">
+        <v>125</v>
+      </c>
       <c r="D126" s="4"/>
       <c r="E126" s="4"/>
       <c r="F126" s="4"/>
@@ -4807,10 +5216,14 @@
       <c r="Y126" s="4"/>
       <c r="Z126" s="4"/>
     </row>
-    <row r="127" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A127" s="4"/>
-      <c r="B127" s="5"/>
-      <c r="C127" s="7"/>
+      <c r="B127" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C127" s="14" t="s">
+        <v>126</v>
+      </c>
       <c r="D127" s="4"/>
       <c r="E127" s="4"/>
       <c r="F127" s="4"/>
@@ -4835,10 +5248,14 @@
       <c r="Y127" s="4"/>
       <c r="Z127" s="4"/>
     </row>
-    <row r="128" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A128" s="4"/>
-      <c r="B128" s="5"/>
-      <c r="C128" s="7"/>
+      <c r="B128" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C128" s="14" t="s">
+        <v>127</v>
+      </c>
       <c r="D128" s="4"/>
       <c r="E128" s="4"/>
       <c r="F128" s="4"/>
@@ -4863,10 +5280,14 @@
       <c r="Y128" s="4"/>
       <c r="Z128" s="4"/>
     </row>
-    <row r="129" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A129" s="4"/>
-      <c r="B129" s="5"/>
-      <c r="C129" s="7"/>
+      <c r="B129" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C129" s="14" t="s">
+        <v>128</v>
+      </c>
       <c r="D129" s="4"/>
       <c r="E129" s="4"/>
       <c r="F129" s="4"/>
@@ -4891,10 +5312,14 @@
       <c r="Y129" s="4"/>
       <c r="Z129" s="4"/>
     </row>
-    <row r="130" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A130" s="4"/>
-      <c r="B130" s="5"/>
-      <c r="C130" s="7"/>
+      <c r="B130" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C130" s="14" t="s">
+        <v>129</v>
+      </c>
       <c r="D130" s="4"/>
       <c r="E130" s="4"/>
       <c r="F130" s="4"/>
@@ -4919,10 +5344,14 @@
       <c r="Y130" s="4"/>
       <c r="Z130" s="4"/>
     </row>
-    <row r="131" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A131" s="4"/>
-      <c r="B131" s="5"/>
-      <c r="C131" s="7"/>
+      <c r="B131" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C131" s="14" t="s">
+        <v>130</v>
+      </c>
       <c r="D131" s="4"/>
       <c r="E131" s="4"/>
       <c r="F131" s="4"/>
@@ -4947,10 +5376,14 @@
       <c r="Y131" s="4"/>
       <c r="Z131" s="4"/>
     </row>
-    <row r="132" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A132" s="4"/>
-      <c r="B132" s="5"/>
-      <c r="C132" s="7"/>
+      <c r="B132" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C132" s="14" t="s">
+        <v>131</v>
+      </c>
       <c r="D132" s="4"/>
       <c r="E132" s="4"/>
       <c r="F132" s="4"/>
@@ -4975,10 +5408,14 @@
       <c r="Y132" s="4"/>
       <c r="Z132" s="4"/>
     </row>
-    <row r="133" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A133" s="4"/>
-      <c r="B133" s="5"/>
-      <c r="C133" s="7"/>
+      <c r="B133" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C133" s="14" t="s">
+        <v>132</v>
+      </c>
       <c r="D133" s="4"/>
       <c r="E133" s="4"/>
       <c r="F133" s="4"/>
@@ -5003,10 +5440,14 @@
       <c r="Y133" s="4"/>
       <c r="Z133" s="4"/>
     </row>
-    <row r="134" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A134" s="4"/>
-      <c r="B134" s="5"/>
-      <c r="C134" s="7"/>
+      <c r="B134" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C134" s="14" t="s">
+        <v>133</v>
+      </c>
       <c r="D134" s="4"/>
       <c r="E134" s="4"/>
       <c r="F134" s="4"/>
@@ -5031,10 +5472,14 @@
       <c r="Y134" s="4"/>
       <c r="Z134" s="4"/>
     </row>
-    <row r="135" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A135" s="4"/>
-      <c r="B135" s="5"/>
-      <c r="C135" s="7"/>
+      <c r="B135" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C135" s="14" t="s">
+        <v>134</v>
+      </c>
       <c r="D135" s="4"/>
       <c r="E135" s="4"/>
       <c r="F135" s="4"/>
@@ -5059,10 +5504,14 @@
       <c r="Y135" s="4"/>
       <c r="Z135" s="4"/>
     </row>
-    <row r="136" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A136" s="4"/>
-      <c r="B136" s="5"/>
-      <c r="C136" s="7"/>
+      <c r="B136" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C136" s="14" t="s">
+        <v>135</v>
+      </c>
       <c r="D136" s="4"/>
       <c r="E136" s="4"/>
       <c r="F136" s="4"/>
@@ -5087,10 +5536,14 @@
       <c r="Y136" s="4"/>
       <c r="Z136" s="4"/>
     </row>
-    <row r="137" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A137" s="4"/>
-      <c r="B137" s="5"/>
-      <c r="C137" s="7"/>
+      <c r="B137" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C137" s="14" t="s">
+        <v>136</v>
+      </c>
       <c r="D137" s="4"/>
       <c r="E137" s="4"/>
       <c r="F137" s="4"/>
@@ -5115,10 +5568,14 @@
       <c r="Y137" s="4"/>
       <c r="Z137" s="4"/>
     </row>
-    <row r="138" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A138" s="4"/>
-      <c r="B138" s="5"/>
-      <c r="C138" s="7"/>
+      <c r="B138" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C138" s="14" t="s">
+        <v>137</v>
+      </c>
       <c r="D138" s="4"/>
       <c r="E138" s="4"/>
       <c r="F138" s="4"/>
@@ -5143,10 +5600,14 @@
       <c r="Y138" s="4"/>
       <c r="Z138" s="4"/>
     </row>
-    <row r="139" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A139" s="4"/>
-      <c r="B139" s="5"/>
-      <c r="C139" s="7"/>
+      <c r="B139" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C139" s="14" t="s">
+        <v>138</v>
+      </c>
       <c r="D139" s="4"/>
       <c r="E139" s="4"/>
       <c r="F139" s="4"/>
@@ -5171,10 +5632,14 @@
       <c r="Y139" s="4"/>
       <c r="Z139" s="4"/>
     </row>
-    <row r="140" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A140" s="4"/>
-      <c r="B140" s="5"/>
-      <c r="C140" s="7"/>
+      <c r="B140" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C140" s="14" t="s">
+        <v>139</v>
+      </c>
       <c r="D140" s="4"/>
       <c r="E140" s="4"/>
       <c r="F140" s="4"/>
@@ -5199,10 +5664,14 @@
       <c r="Y140" s="4"/>
       <c r="Z140" s="4"/>
     </row>
-    <row r="141" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:26" ht="35.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A141" s="4"/>
-      <c r="B141" s="5"/>
-      <c r="C141" s="7"/>
+      <c r="B141" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C141" s="14" t="s">
+        <v>140</v>
+      </c>
       <c r="D141" s="4"/>
       <c r="E141" s="4"/>
       <c r="F141" s="4"/>
@@ -5227,10 +5696,14 @@
       <c r="Y141" s="4"/>
       <c r="Z141" s="4"/>
     </row>
-    <row r="142" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A142" s="4"/>
-      <c r="B142" s="5"/>
-      <c r="C142" s="7"/>
+      <c r="B142" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C142" s="14" t="s">
+        <v>141</v>
+      </c>
       <c r="D142" s="4"/>
       <c r="E142" s="4"/>
       <c r="F142" s="4"/>
@@ -5255,10 +5728,14 @@
       <c r="Y142" s="4"/>
       <c r="Z142" s="4"/>
     </row>
-    <row r="143" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A143" s="4"/>
-      <c r="B143" s="5"/>
-      <c r="C143" s="7"/>
+      <c r="B143" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C143" s="14" t="s">
+        <v>142</v>
+      </c>
       <c r="D143" s="4"/>
       <c r="E143" s="4"/>
       <c r="F143" s="4"/>
@@ -5283,10 +5760,14 @@
       <c r="Y143" s="4"/>
       <c r="Z143" s="4"/>
     </row>
-    <row r="144" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A144" s="4"/>
-      <c r="B144" s="5"/>
-      <c r="C144" s="7"/>
+      <c r="B144" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C144" s="14" t="s">
+        <v>143</v>
+      </c>
       <c r="D144" s="4"/>
       <c r="E144" s="4"/>
       <c r="F144" s="4"/>
@@ -5311,10 +5792,14 @@
       <c r="Y144" s="4"/>
       <c r="Z144" s="4"/>
     </row>
-    <row r="145" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A145" s="4"/>
-      <c r="B145" s="5"/>
-      <c r="C145" s="7"/>
+      <c r="B145" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C145" s="14" t="s">
+        <v>144</v>
+      </c>
       <c r="D145" s="4"/>
       <c r="E145" s="4"/>
       <c r="F145" s="4"/>
@@ -5339,10 +5824,14 @@
       <c r="Y145" s="4"/>
       <c r="Z145" s="4"/>
     </row>
-    <row r="146" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A146" s="4"/>
-      <c r="B146" s="5"/>
-      <c r="C146" s="7"/>
+      <c r="B146" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C146" s="14" t="s">
+        <v>145</v>
+      </c>
       <c r="D146" s="4"/>
       <c r="E146" s="4"/>
       <c r="F146" s="4"/>
@@ -5367,10 +5856,14 @@
       <c r="Y146" s="4"/>
       <c r="Z146" s="4"/>
     </row>
-    <row r="147" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A147" s="4"/>
-      <c r="B147" s="5"/>
-      <c r="C147" s="7"/>
+      <c r="B147" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C147" s="14" t="s">
+        <v>146</v>
+      </c>
       <c r="D147" s="4"/>
       <c r="E147" s="4"/>
       <c r="F147" s="4"/>
@@ -5395,10 +5888,14 @@
       <c r="Y147" s="4"/>
       <c r="Z147" s="4"/>
     </row>
-    <row r="148" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:26" ht="35.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A148" s="4"/>
-      <c r="B148" s="5"/>
-      <c r="C148" s="7"/>
+      <c r="B148" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C148" s="14" t="s">
+        <v>147</v>
+      </c>
       <c r="D148" s="4"/>
       <c r="E148" s="4"/>
       <c r="F148" s="4"/>
@@ -5423,10 +5920,14 @@
       <c r="Y148" s="4"/>
       <c r="Z148" s="4"/>
     </row>
-    <row r="149" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:26" ht="35.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A149" s="4"/>
-      <c r="B149" s="5"/>
-      <c r="C149" s="7"/>
+      <c r="B149" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C149" s="14" t="s">
+        <v>148</v>
+      </c>
       <c r="D149" s="4"/>
       <c r="E149" s="4"/>
       <c r="F149" s="4"/>
@@ -5451,10 +5952,14 @@
       <c r="Y149" s="4"/>
       <c r="Z149" s="4"/>
     </row>
-    <row r="150" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A150" s="4"/>
-      <c r="B150" s="5"/>
-      <c r="C150" s="7"/>
+      <c r="B150" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C150" s="14" t="s">
+        <v>149</v>
+      </c>
       <c r="D150" s="4"/>
       <c r="E150" s="4"/>
       <c r="F150" s="4"/>
@@ -5479,10 +5984,14 @@
       <c r="Y150" s="4"/>
       <c r="Z150" s="4"/>
     </row>
-    <row r="151" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A151" s="4"/>
-      <c r="B151" s="5"/>
-      <c r="C151" s="7"/>
+      <c r="B151" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C151" s="14" t="s">
+        <v>150</v>
+      </c>
       <c r="D151" s="4"/>
       <c r="E151" s="4"/>
       <c r="F151" s="4"/>
@@ -5507,10 +6016,14 @@
       <c r="Y151" s="4"/>
       <c r="Z151" s="4"/>
     </row>
-    <row r="152" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:26" ht="35.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A152" s="4"/>
-      <c r="B152" s="5"/>
-      <c r="C152" s="7"/>
+      <c r="B152" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C152" s="14" t="s">
+        <v>151</v>
+      </c>
       <c r="D152" s="4"/>
       <c r="E152" s="4"/>
       <c r="F152" s="4"/>
@@ -5535,10 +6048,14 @@
       <c r="Y152" s="4"/>
       <c r="Z152" s="4"/>
     </row>
-    <row r="153" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A153" s="4"/>
-      <c r="B153" s="5"/>
-      <c r="C153" s="7"/>
+      <c r="B153" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C153" s="14" t="s">
+        <v>152</v>
+      </c>
       <c r="D153" s="4"/>
       <c r="E153" s="4"/>
       <c r="F153" s="4"/>
@@ -5563,10 +6080,14 @@
       <c r="Y153" s="4"/>
       <c r="Z153" s="4"/>
     </row>
-    <row r="154" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A154" s="4"/>
-      <c r="B154" s="5"/>
-      <c r="C154" s="7"/>
+      <c r="B154" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C154" s="14" t="s">
+        <v>153</v>
+      </c>
       <c r="D154" s="4"/>
       <c r="E154" s="4"/>
       <c r="F154" s="4"/>
@@ -5591,10 +6112,14 @@
       <c r="Y154" s="4"/>
       <c r="Z154" s="4"/>
     </row>
-    <row r="155" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A155" s="4"/>
-      <c r="B155" s="5"/>
-      <c r="C155" s="7"/>
+      <c r="B155" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C155" s="14" t="s">
+        <v>154</v>
+      </c>
       <c r="D155" s="4"/>
       <c r="E155" s="4"/>
       <c r="F155" s="4"/>
@@ -5619,10 +6144,14 @@
       <c r="Y155" s="4"/>
       <c r="Z155" s="4"/>
     </row>
-    <row r="156" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A156" s="4"/>
-      <c r="B156" s="5"/>
-      <c r="C156" s="7"/>
+      <c r="B156" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C156" s="14" t="s">
+        <v>155</v>
+      </c>
       <c r="D156" s="4"/>
       <c r="E156" s="4"/>
       <c r="F156" s="4"/>
@@ -5647,10 +6176,14 @@
       <c r="Y156" s="4"/>
       <c r="Z156" s="4"/>
     </row>
-    <row r="157" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:26" ht="35.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A157" s="4"/>
-      <c r="B157" s="5"/>
-      <c r="C157" s="7"/>
+      <c r="B157" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C157" s="14" t="s">
+        <v>156</v>
+      </c>
       <c r="D157" s="4"/>
       <c r="E157" s="4"/>
       <c r="F157" s="4"/>
@@ -5675,10 +6208,14 @@
       <c r="Y157" s="4"/>
       <c r="Z157" s="4"/>
     </row>
-    <row r="158" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A158" s="4"/>
-      <c r="B158" s="5"/>
-      <c r="C158" s="7"/>
+      <c r="B158" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C158" s="14" t="s">
+        <v>157</v>
+      </c>
       <c r="D158" s="4"/>
       <c r="E158" s="4"/>
       <c r="F158" s="4"/>
@@ -5703,10 +6240,14 @@
       <c r="Y158" s="4"/>
       <c r="Z158" s="4"/>
     </row>
-    <row r="159" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A159" s="4"/>
-      <c r="B159" s="5"/>
-      <c r="C159" s="7"/>
+      <c r="B159" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C159" s="14" t="s">
+        <v>158</v>
+      </c>
       <c r="D159" s="4"/>
       <c r="E159" s="4"/>
       <c r="F159" s="4"/>
@@ -5731,10 +6272,14 @@
       <c r="Y159" s="4"/>
       <c r="Z159" s="4"/>
     </row>
-    <row r="160" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A160" s="4"/>
-      <c r="B160" s="5"/>
-      <c r="C160" s="7"/>
+      <c r="B160" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C160" s="14" t="s">
+        <v>159</v>
+      </c>
       <c r="D160" s="4"/>
       <c r="E160" s="4"/>
       <c r="F160" s="4"/>
@@ -5759,10 +6304,14 @@
       <c r="Y160" s="4"/>
       <c r="Z160" s="4"/>
     </row>
-    <row r="161" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A161" s="4"/>
-      <c r="B161" s="5"/>
-      <c r="C161" s="7"/>
+      <c r="B161" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C161" s="14" t="s">
+        <v>160</v>
+      </c>
       <c r="D161" s="4"/>
       <c r="E161" s="4"/>
       <c r="F161" s="4"/>
@@ -5787,10 +6336,14 @@
       <c r="Y161" s="4"/>
       <c r="Z161" s="4"/>
     </row>
-    <row r="162" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A162" s="4"/>
-      <c r="B162" s="5"/>
-      <c r="C162" s="7"/>
+      <c r="B162" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C162" s="14" t="s">
+        <v>161</v>
+      </c>
       <c r="D162" s="4"/>
       <c r="E162" s="4"/>
       <c r="F162" s="4"/>
@@ -5815,10 +6368,14 @@
       <c r="Y162" s="4"/>
       <c r="Z162" s="4"/>
     </row>
-    <row r="163" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A163" s="4"/>
-      <c r="B163" s="5"/>
-      <c r="C163" s="7"/>
+      <c r="B163" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C163" s="14" t="s">
+        <v>162</v>
+      </c>
       <c r="D163" s="4"/>
       <c r="E163" s="4"/>
       <c r="F163" s="4"/>
@@ -5843,10 +6400,14 @@
       <c r="Y163" s="4"/>
       <c r="Z163" s="4"/>
     </row>
-    <row r="164" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:26" ht="35.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A164" s="4"/>
-      <c r="B164" s="5"/>
-      <c r="C164" s="7"/>
+      <c r="B164" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C164" s="14" t="s">
+        <v>163</v>
+      </c>
       <c r="D164" s="4"/>
       <c r="E164" s="4"/>
       <c r="F164" s="4"/>
@@ -5871,10 +6432,14 @@
       <c r="Y164" s="4"/>
       <c r="Z164" s="4"/>
     </row>
-    <row r="165" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A165" s="4"/>
-      <c r="B165" s="5"/>
-      <c r="C165" s="7"/>
+      <c r="B165" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C165" s="14" t="s">
+        <v>164</v>
+      </c>
       <c r="D165" s="4"/>
       <c r="E165" s="4"/>
       <c r="F165" s="4"/>
@@ -5899,10 +6464,14 @@
       <c r="Y165" s="4"/>
       <c r="Z165" s="4"/>
     </row>
-    <row r="166" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:26" ht="35.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A166" s="4"/>
-      <c r="B166" s="5"/>
-      <c r="C166" s="7"/>
+      <c r="B166" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C166" s="14" t="s">
+        <v>165</v>
+      </c>
       <c r="D166" s="4"/>
       <c r="E166" s="4"/>
       <c r="F166" s="4"/>
@@ -5927,10 +6496,14 @@
       <c r="Y166" s="4"/>
       <c r="Z166" s="4"/>
     </row>
-    <row r="167" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A167" s="4"/>
-      <c r="B167" s="5"/>
-      <c r="C167" s="7"/>
+      <c r="B167" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C167" s="14" t="s">
+        <v>166</v>
+      </c>
       <c r="D167" s="4"/>
       <c r="E167" s="4"/>
       <c r="F167" s="4"/>
@@ -5955,10 +6528,14 @@
       <c r="Y167" s="4"/>
       <c r="Z167" s="4"/>
     </row>
-    <row r="168" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:26" ht="35.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A168" s="4"/>
-      <c r="B168" s="5"/>
-      <c r="C168" s="7"/>
+      <c r="B168" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C168" s="14" t="s">
+        <v>167</v>
+      </c>
       <c r="D168" s="4"/>
       <c r="E168" s="4"/>
       <c r="F168" s="4"/>
@@ -5983,10 +6560,14 @@
       <c r="Y168" s="4"/>
       <c r="Z168" s="4"/>
     </row>
-    <row r="169" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A169" s="4"/>
-      <c r="B169" s="5"/>
-      <c r="C169" s="7"/>
+      <c r="B169" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C169" s="14" t="s">
+        <v>168</v>
+      </c>
       <c r="D169" s="4"/>
       <c r="E169" s="4"/>
       <c r="F169" s="4"/>
@@ -6011,10 +6592,14 @@
       <c r="Y169" s="4"/>
       <c r="Z169" s="4"/>
     </row>
-    <row r="170" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A170" s="4"/>
-      <c r="B170" s="5"/>
-      <c r="C170" s="7"/>
+      <c r="B170" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C170" s="14" t="s">
+        <v>169</v>
+      </c>
       <c r="D170" s="4"/>
       <c r="E170" s="4"/>
       <c r="F170" s="4"/>
@@ -6039,10 +6624,14 @@
       <c r="Y170" s="4"/>
       <c r="Z170" s="4"/>
     </row>
-    <row r="171" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A171" s="4"/>
-      <c r="B171" s="5"/>
-      <c r="C171" s="7"/>
+      <c r="B171" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C171" s="14" t="s">
+        <v>170</v>
+      </c>
       <c r="D171" s="4"/>
       <c r="E171" s="4"/>
       <c r="F171" s="4"/>
@@ -6067,10 +6656,14 @@
       <c r="Y171" s="4"/>
       <c r="Z171" s="4"/>
     </row>
-    <row r="172" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A172" s="4"/>
-      <c r="B172" s="5"/>
-      <c r="C172" s="7"/>
+      <c r="B172" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C172" s="14" t="s">
+        <v>171</v>
+      </c>
       <c r="D172" s="4"/>
       <c r="E172" s="4"/>
       <c r="F172" s="4"/>
@@ -6095,10 +6688,14 @@
       <c r="Y172" s="4"/>
       <c r="Z172" s="4"/>
     </row>
-    <row r="173" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A173" s="4"/>
-      <c r="B173" s="5"/>
-      <c r="C173" s="7"/>
+      <c r="B173" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C173" s="14" t="s">
+        <v>172</v>
+      </c>
       <c r="D173" s="4"/>
       <c r="E173" s="4"/>
       <c r="F173" s="4"/>
@@ -6123,10 +6720,14 @@
       <c r="Y173" s="4"/>
       <c r="Z173" s="4"/>
     </row>
-    <row r="174" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A174" s="4"/>
-      <c r="B174" s="5"/>
-      <c r="C174" s="7"/>
+      <c r="B174" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C174" s="14" t="s">
+        <v>173</v>
+      </c>
       <c r="D174" s="4"/>
       <c r="E174" s="4"/>
       <c r="F174" s="4"/>
@@ -6151,10 +6752,14 @@
       <c r="Y174" s="4"/>
       <c r="Z174" s="4"/>
     </row>
-    <row r="175" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A175" s="4"/>
-      <c r="B175" s="5"/>
-      <c r="C175" s="7"/>
+      <c r="B175" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C175" s="14" t="s">
+        <v>174</v>
+      </c>
       <c r="D175" s="4"/>
       <c r="E175" s="4"/>
       <c r="F175" s="4"/>
@@ -6179,10 +6784,14 @@
       <c r="Y175" s="4"/>
       <c r="Z175" s="4"/>
     </row>
-    <row r="176" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A176" s="4"/>
-      <c r="B176" s="5"/>
-      <c r="C176" s="7"/>
+      <c r="B176" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C176" s="14" t="s">
+        <v>175</v>
+      </c>
       <c r="D176" s="4"/>
       <c r="E176" s="4"/>
       <c r="F176" s="4"/>
@@ -6207,10 +6816,14 @@
       <c r="Y176" s="4"/>
       <c r="Z176" s="4"/>
     </row>
-    <row r="177" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A177" s="4"/>
-      <c r="B177" s="5"/>
-      <c r="C177" s="7"/>
+      <c r="B177" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C177" s="14" t="s">
+        <v>176</v>
+      </c>
       <c r="D177" s="4"/>
       <c r="E177" s="4"/>
       <c r="F177" s="4"/>
@@ -6235,10 +6848,14 @@
       <c r="Y177" s="4"/>
       <c r="Z177" s="4"/>
     </row>
-    <row r="178" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A178" s="4"/>
-      <c r="B178" s="5"/>
-      <c r="C178" s="7"/>
+      <c r="B178" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C178" s="14" t="s">
+        <v>177</v>
+      </c>
       <c r="D178" s="4"/>
       <c r="E178" s="4"/>
       <c r="F178" s="4"/>
@@ -6263,10 +6880,14 @@
       <c r="Y178" s="4"/>
       <c r="Z178" s="4"/>
     </row>
-    <row r="179" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A179" s="4"/>
-      <c r="B179" s="5"/>
-      <c r="C179" s="7"/>
+      <c r="B179" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C179" s="14" t="s">
+        <v>178</v>
+      </c>
       <c r="D179" s="4"/>
       <c r="E179" s="4"/>
       <c r="F179" s="4"/>
@@ -6291,10 +6912,14 @@
       <c r="Y179" s="4"/>
       <c r="Z179" s="4"/>
     </row>
-    <row r="180" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A180" s="4"/>
-      <c r="B180" s="5"/>
-      <c r="C180" s="7"/>
+      <c r="B180" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C180" s="14" t="s">
+        <v>179</v>
+      </c>
       <c r="D180" s="4"/>
       <c r="E180" s="4"/>
       <c r="F180" s="4"/>
@@ -6319,10 +6944,14 @@
       <c r="Y180" s="4"/>
       <c r="Z180" s="4"/>
     </row>
-    <row r="181" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A181" s="4"/>
-      <c r="B181" s="5"/>
-      <c r="C181" s="7"/>
+      <c r="B181" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C181" s="14" t="s">
+        <v>180</v>
+      </c>
       <c r="D181" s="4"/>
       <c r="E181" s="4"/>
       <c r="F181" s="4"/>
@@ -6347,10 +6976,14 @@
       <c r="Y181" s="4"/>
       <c r="Z181" s="4"/>
     </row>
-    <row r="182" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A182" s="4"/>
-      <c r="B182" s="5"/>
-      <c r="C182" s="7"/>
+      <c r="B182" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C182" s="14" t="s">
+        <v>181</v>
+      </c>
       <c r="D182" s="4"/>
       <c r="E182" s="4"/>
       <c r="F182" s="4"/>
@@ -6375,10 +7008,14 @@
       <c r="Y182" s="4"/>
       <c r="Z182" s="4"/>
     </row>
-    <row r="183" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:26" ht="35.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A183" s="4"/>
-      <c r="B183" s="5"/>
-      <c r="C183" s="7"/>
+      <c r="B183" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C183" s="14" t="s">
+        <v>182</v>
+      </c>
       <c r="D183" s="4"/>
       <c r="E183" s="4"/>
       <c r="F183" s="4"/>
@@ -6403,10 +7040,14 @@
       <c r="Y183" s="4"/>
       <c r="Z183" s="4"/>
     </row>
-    <row r="184" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A184" s="4"/>
-      <c r="B184" s="5"/>
-      <c r="C184" s="7"/>
+      <c r="B184" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C184" s="14" t="s">
+        <v>183</v>
+      </c>
       <c r="D184" s="4"/>
       <c r="E184" s="4"/>
       <c r="F184" s="4"/>
@@ -6431,10 +7072,14 @@
       <c r="Y184" s="4"/>
       <c r="Z184" s="4"/>
     </row>
-    <row r="185" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A185" s="4"/>
-      <c r="B185" s="5"/>
-      <c r="C185" s="7"/>
+      <c r="B185" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C185" s="14" t="s">
+        <v>184</v>
+      </c>
       <c r="D185" s="4"/>
       <c r="E185" s="4"/>
       <c r="F185" s="4"/>
@@ -6459,10 +7104,14 @@
       <c r="Y185" s="4"/>
       <c r="Z185" s="4"/>
     </row>
-    <row r="186" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A186" s="4"/>
-      <c r="B186" s="5"/>
-      <c r="C186" s="7"/>
+      <c r="B186" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C186" s="14" t="s">
+        <v>185</v>
+      </c>
       <c r="D186" s="4"/>
       <c r="E186" s="4"/>
       <c r="F186" s="4"/>
@@ -6487,10 +7136,14 @@
       <c r="Y186" s="4"/>
       <c r="Z186" s="4"/>
     </row>
-    <row r="187" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:26" ht="35.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A187" s="4"/>
-      <c r="B187" s="5"/>
-      <c r="C187" s="7"/>
+      <c r="B187" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C187" s="14" t="s">
+        <v>186</v>
+      </c>
       <c r="D187" s="4"/>
       <c r="E187" s="4"/>
       <c r="F187" s="4"/>
@@ -6515,10 +7168,14 @@
       <c r="Y187" s="4"/>
       <c r="Z187" s="4"/>
     </row>
-    <row r="188" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A188" s="4"/>
-      <c r="B188" s="5"/>
-      <c r="C188" s="7"/>
+      <c r="B188" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C188" s="14" t="s">
+        <v>187</v>
+      </c>
       <c r="D188" s="4"/>
       <c r="E188" s="4"/>
       <c r="F188" s="4"/>
@@ -6543,10 +7200,14 @@
       <c r="Y188" s="4"/>
       <c r="Z188" s="4"/>
     </row>
-    <row r="189" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A189" s="1"/>
-      <c r="B189" s="6"/>
-      <c r="C189" s="7"/>
+      <c r="B189" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C189" s="14" t="s">
+        <v>188</v>
+      </c>
       <c r="D189" s="1"/>
       <c r="E189" s="1"/>
       <c r="F189" s="1"/>
@@ -6571,10 +7232,14 @@
       <c r="Y189" s="1"/>
       <c r="Z189" s="1"/>
     </row>
-    <row r="190" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A190" s="1"/>
-      <c r="B190" s="6"/>
-      <c r="C190" s="7"/>
+      <c r="B190" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C190" s="14" t="s">
+        <v>189</v>
+      </c>
       <c r="D190" s="1"/>
       <c r="E190" s="1"/>
       <c r="F190" s="1"/>
@@ -6599,10 +7264,14 @@
       <c r="Y190" s="1"/>
       <c r="Z190" s="1"/>
     </row>
-    <row r="191" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A191" s="1"/>
-      <c r="B191" s="6"/>
-      <c r="C191" s="7"/>
+      <c r="B191" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C191" s="14" t="s">
+        <v>190</v>
+      </c>
       <c r="D191" s="1"/>
       <c r="E191" s="1"/>
       <c r="F191" s="1"/>
@@ -6627,10 +7296,14 @@
       <c r="Y191" s="1"/>
       <c r="Z191" s="1"/>
     </row>
-    <row r="192" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A192" s="1"/>
-      <c r="B192" s="6"/>
-      <c r="C192" s="7"/>
+      <c r="B192" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C192" s="14" t="s">
+        <v>191</v>
+      </c>
       <c r="D192" s="1"/>
       <c r="E192" s="1"/>
       <c r="F192" s="1"/>
@@ -6655,10 +7328,14 @@
       <c r="Y192" s="1"/>
       <c r="Z192" s="1"/>
     </row>
-    <row r="193" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A193" s="1"/>
-      <c r="B193" s="6"/>
-      <c r="C193" s="7"/>
+      <c r="B193" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C193" s="14" t="s">
+        <v>192</v>
+      </c>
       <c r="D193" s="1"/>
       <c r="E193" s="1"/>
       <c r="F193" s="1"/>
@@ -6683,10 +7360,14 @@
       <c r="Y193" s="1"/>
       <c r="Z193" s="1"/>
     </row>
-    <row r="194" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A194" s="1"/>
-      <c r="B194" s="6"/>
-      <c r="C194" s="7"/>
+      <c r="B194" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C194" s="14" t="s">
+        <v>193</v>
+      </c>
       <c r="D194" s="1"/>
       <c r="E194" s="1"/>
       <c r="F194" s="1"/>
@@ -6711,10 +7392,14 @@
       <c r="Y194" s="1"/>
       <c r="Z194" s="1"/>
     </row>
-    <row r="195" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A195" s="1"/>
-      <c r="B195" s="6"/>
-      <c r="C195" s="7"/>
+      <c r="B195" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C195" s="14" t="s">
+        <v>194</v>
+      </c>
       <c r="D195" s="1"/>
       <c r="E195" s="1"/>
       <c r="F195" s="1"/>
@@ -6739,10 +7424,14 @@
       <c r="Y195" s="1"/>
       <c r="Z195" s="1"/>
     </row>
-    <row r="196" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A196" s="1"/>
-      <c r="B196" s="6"/>
-      <c r="C196" s="7"/>
+      <c r="B196" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C196" s="14" t="s">
+        <v>195</v>
+      </c>
       <c r="D196" s="1"/>
       <c r="E196" s="1"/>
       <c r="F196" s="1"/>
@@ -6767,10 +7456,14 @@
       <c r="Y196" s="1"/>
       <c r="Z196" s="1"/>
     </row>
-    <row r="197" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A197" s="1"/>
-      <c r="B197" s="6"/>
-      <c r="C197" s="7"/>
+      <c r="B197" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C197" s="14" t="s">
+        <v>196</v>
+      </c>
       <c r="D197" s="1"/>
       <c r="E197" s="1"/>
       <c r="F197" s="1"/>
@@ -6795,10 +7488,14 @@
       <c r="Y197" s="1"/>
       <c r="Z197" s="1"/>
     </row>
-    <row r="198" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A198" s="1"/>
-      <c r="B198" s="6"/>
-      <c r="C198" s="7"/>
+      <c r="B198" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C198" s="14" t="s">
+        <v>197</v>
+      </c>
       <c r="D198" s="1"/>
       <c r="E198" s="1"/>
       <c r="F198" s="1"/>
@@ -6823,10 +7520,14 @@
       <c r="Y198" s="1"/>
       <c r="Z198" s="1"/>
     </row>
-    <row r="199" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A199" s="1"/>
-      <c r="B199" s="6"/>
-      <c r="C199" s="7"/>
+      <c r="B199" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C199" s="14" t="s">
+        <v>198</v>
+      </c>
       <c r="D199" s="1"/>
       <c r="E199" s="1"/>
       <c r="F199" s="1"/>
@@ -6851,10 +7552,14 @@
       <c r="Y199" s="1"/>
       <c r="Z199" s="1"/>
     </row>
-    <row r="200" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:26" ht="35.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A200" s="1"/>
-      <c r="B200" s="6"/>
-      <c r="C200" s="7"/>
+      <c r="B200" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C200" s="14" t="s">
+        <v>199</v>
+      </c>
       <c r="D200" s="1"/>
       <c r="E200" s="1"/>
       <c r="F200" s="1"/>
@@ -6879,10 +7584,14 @@
       <c r="Y200" s="1"/>
       <c r="Z200" s="1"/>
     </row>
-    <row r="201" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A201" s="1"/>
-      <c r="B201" s="6"/>
-      <c r="C201" s="7"/>
+      <c r="B201" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C201" s="14" t="s">
+        <v>200</v>
+      </c>
       <c r="D201" s="1"/>
       <c r="E201" s="1"/>
       <c r="F201" s="1"/>
@@ -6907,10 +7616,14 @@
       <c r="Y201" s="1"/>
       <c r="Z201" s="1"/>
     </row>
-    <row r="202" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:26" ht="35.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A202" s="1"/>
-      <c r="B202" s="6"/>
-      <c r="C202" s="7"/>
+      <c r="B202" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C202" s="14" t="s">
+        <v>201</v>
+      </c>
       <c r="D202" s="1"/>
       <c r="E202" s="1"/>
       <c r="F202" s="1"/>
@@ -6935,10 +7648,14 @@
       <c r="Y202" s="1"/>
       <c r="Z202" s="1"/>
     </row>
-    <row r="203" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A203" s="1"/>
-      <c r="B203" s="6"/>
-      <c r="C203" s="7"/>
+      <c r="B203" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C203" s="14" t="s">
+        <v>202</v>
+      </c>
       <c r="D203" s="1"/>
       <c r="E203" s="1"/>
       <c r="F203" s="1"/>
@@ -6963,10 +7680,14 @@
       <c r="Y203" s="1"/>
       <c r="Z203" s="1"/>
     </row>
-    <row r="204" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A204" s="1"/>
-      <c r="B204" s="6"/>
-      <c r="C204" s="7"/>
+      <c r="B204" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C204" s="14" t="s">
+        <v>203</v>
+      </c>
       <c r="D204" s="1"/>
       <c r="E204" s="1"/>
       <c r="F204" s="1"/>
@@ -6991,10 +7712,14 @@
       <c r="Y204" s="1"/>
       <c r="Z204" s="1"/>
     </row>
-    <row r="205" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:26" ht="35.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A205" s="1"/>
-      <c r="B205" s="6"/>
-      <c r="C205" s="7"/>
+      <c r="B205" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C205" s="14" t="s">
+        <v>204</v>
+      </c>
       <c r="D205" s="1"/>
       <c r="E205" s="1"/>
       <c r="F205" s="1"/>
@@ -7019,10 +7744,14 @@
       <c r="Y205" s="1"/>
       <c r="Z205" s="1"/>
     </row>
-    <row r="206" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A206" s="1"/>
-      <c r="B206" s="6"/>
-      <c r="C206" s="7"/>
+      <c r="B206" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C206" s="14" t="s">
+        <v>205</v>
+      </c>
       <c r="D206" s="1"/>
       <c r="E206" s="1"/>
       <c r="F206" s="1"/>
@@ -7047,10 +7776,14 @@
       <c r="Y206" s="1"/>
       <c r="Z206" s="1"/>
     </row>
-    <row r="207" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A207" s="1"/>
-      <c r="B207" s="6"/>
-      <c r="C207" s="7"/>
+      <c r="B207" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C207" s="14" t="s">
+        <v>206</v>
+      </c>
       <c r="D207" s="1"/>
       <c r="E207" s="1"/>
       <c r="F207" s="1"/>
@@ -7075,10 +7808,14 @@
       <c r="Y207" s="1"/>
       <c r="Z207" s="1"/>
     </row>
-    <row r="208" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A208" s="1"/>
-      <c r="B208" s="6"/>
-      <c r="C208" s="7"/>
+      <c r="B208" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C208" s="14" t="s">
+        <v>207</v>
+      </c>
       <c r="D208" s="1"/>
       <c r="E208" s="1"/>
       <c r="F208" s="1"/>
@@ -7103,10 +7840,14 @@
       <c r="Y208" s="1"/>
       <c r="Z208" s="1"/>
     </row>
-    <row r="209" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A209" s="1"/>
-      <c r="B209" s="6"/>
-      <c r="C209" s="7"/>
+      <c r="B209" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C209" s="14" t="s">
+        <v>208</v>
+      </c>
       <c r="D209" s="1"/>
       <c r="E209" s="1"/>
       <c r="F209" s="1"/>
@@ -7131,10 +7872,14 @@
       <c r="Y209" s="1"/>
       <c r="Z209" s="1"/>
     </row>
-    <row r="210" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A210" s="1"/>
-      <c r="B210" s="6"/>
-      <c r="C210" s="7"/>
+      <c r="B210" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C210" s="14" t="s">
+        <v>209</v>
+      </c>
       <c r="D210" s="1"/>
       <c r="E210" s="1"/>
       <c r="F210" s="1"/>
@@ -7159,10 +7904,14 @@
       <c r="Y210" s="1"/>
       <c r="Z210" s="1"/>
     </row>
-    <row r="211" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A211" s="1"/>
-      <c r="B211" s="6"/>
-      <c r="C211" s="7"/>
+      <c r="B211" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C211" s="14" t="s">
+        <v>210</v>
+      </c>
       <c r="D211" s="1"/>
       <c r="E211" s="1"/>
       <c r="F211" s="1"/>
@@ -7187,10 +7936,14 @@
       <c r="Y211" s="1"/>
       <c r="Z211" s="1"/>
     </row>
-    <row r="212" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A212" s="1"/>
-      <c r="B212" s="6"/>
-      <c r="C212" s="7"/>
+      <c r="B212" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C212" s="14" t="s">
+        <v>211</v>
+      </c>
       <c r="D212" s="1"/>
       <c r="E212" s="1"/>
       <c r="F212" s="1"/>
@@ -7215,10 +7968,14 @@
       <c r="Y212" s="1"/>
       <c r="Z212" s="1"/>
     </row>
-    <row r="213" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A213" s="1"/>
-      <c r="B213" s="6"/>
-      <c r="C213" s="7"/>
+      <c r="B213" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C213" s="14" t="s">
+        <v>212</v>
+      </c>
       <c r="D213" s="1"/>
       <c r="E213" s="1"/>
       <c r="F213" s="1"/>
@@ -7243,10 +8000,14 @@
       <c r="Y213" s="1"/>
       <c r="Z213" s="1"/>
     </row>
-    <row r="214" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A214" s="1"/>
-      <c r="B214" s="6"/>
-      <c r="C214" s="7"/>
+      <c r="B214" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C214" s="14" t="s">
+        <v>213</v>
+      </c>
       <c r="D214" s="1"/>
       <c r="E214" s="1"/>
       <c r="F214" s="1"/>
@@ -7271,10 +8032,14 @@
       <c r="Y214" s="1"/>
       <c r="Z214" s="1"/>
     </row>
-    <row r="215" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:26" ht="35.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A215" s="1"/>
-      <c r="B215" s="6"/>
-      <c r="C215" s="7"/>
+      <c r="B215" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C215" s="14" t="s">
+        <v>214</v>
+      </c>
       <c r="D215" s="1"/>
       <c r="E215" s="1"/>
       <c r="F215" s="1"/>
@@ -7299,10 +8064,14 @@
       <c r="Y215" s="1"/>
       <c r="Z215" s="1"/>
     </row>
-    <row r="216" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:26" ht="35.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A216" s="1"/>
-      <c r="B216" s="6"/>
-      <c r="C216" s="7"/>
+      <c r="B216" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C216" s="14" t="s">
+        <v>215</v>
+      </c>
       <c r="D216" s="1"/>
       <c r="E216" s="1"/>
       <c r="F216" s="1"/>
@@ -7327,10 +8096,14 @@
       <c r="Y216" s="1"/>
       <c r="Z216" s="1"/>
     </row>
-    <row r="217" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:26" ht="35.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A217" s="1"/>
-      <c r="B217" s="6"/>
-      <c r="C217" s="7"/>
+      <c r="B217" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C217" s="14" t="s">
+        <v>216</v>
+      </c>
       <c r="D217" s="1"/>
       <c r="E217" s="1"/>
       <c r="F217" s="1"/>
@@ -7355,10 +8128,14 @@
       <c r="Y217" s="1"/>
       <c r="Z217" s="1"/>
     </row>
-    <row r="218" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:26" ht="35.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A218" s="1"/>
-      <c r="B218" s="6"/>
-      <c r="C218" s="7"/>
+      <c r="B218" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C218" s="14" t="s">
+        <v>217</v>
+      </c>
       <c r="D218" s="1"/>
       <c r="E218" s="1"/>
       <c r="F218" s="1"/>
@@ -7383,10 +8160,14 @@
       <c r="Y218" s="1"/>
       <c r="Z218" s="1"/>
     </row>
-    <row r="219" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:26" ht="35.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A219" s="1"/>
-      <c r="B219" s="6"/>
-      <c r="C219" s="7"/>
+      <c r="B219" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C219" s="14" t="s">
+        <v>218</v>
+      </c>
       <c r="D219" s="1"/>
       <c r="E219" s="1"/>
       <c r="F219" s="1"/>
@@ -7411,10 +8192,14 @@
       <c r="Y219" s="1"/>
       <c r="Z219" s="1"/>
     </row>
-    <row r="220" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:26" ht="35.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A220" s="1"/>
-      <c r="B220" s="6"/>
-      <c r="C220" s="7"/>
+      <c r="B220" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C220" s="14" t="s">
+        <v>219</v>
+      </c>
       <c r="D220" s="1"/>
       <c r="E220" s="1"/>
       <c r="F220" s="1"/>
@@ -7439,10 +8224,14 @@
       <c r="Y220" s="1"/>
       <c r="Z220" s="1"/>
     </row>
-    <row r="221" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:26" ht="35.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A221" s="1"/>
-      <c r="B221" s="6"/>
-      <c r="C221" s="7"/>
+      <c r="B221" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C221" s="14" t="s">
+        <v>220</v>
+      </c>
       <c r="D221" s="1"/>
       <c r="E221" s="1"/>
       <c r="F221" s="1"/>
@@ -7467,10 +8256,14 @@
       <c r="Y221" s="1"/>
       <c r="Z221" s="1"/>
     </row>
-    <row r="222" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A222" s="1"/>
-      <c r="B222" s="6"/>
-      <c r="C222" s="7"/>
+      <c r="B222" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C222" s="14" t="s">
+        <v>221</v>
+      </c>
       <c r="D222" s="1"/>
       <c r="E222" s="1"/>
       <c r="F222" s="1"/>
@@ -7495,10 +8288,14 @@
       <c r="Y222" s="1"/>
       <c r="Z222" s="1"/>
     </row>
-    <row r="223" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:26" ht="35.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A223" s="1"/>
-      <c r="B223" s="6"/>
-      <c r="C223" s="7"/>
+      <c r="B223" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C223" s="14" t="s">
+        <v>222</v>
+      </c>
       <c r="D223" s="1"/>
       <c r="E223" s="1"/>
       <c r="F223" s="1"/>
@@ -7523,10 +8320,14 @@
       <c r="Y223" s="1"/>
       <c r="Z223" s="1"/>
     </row>
-    <row r="224" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A224" s="1"/>
-      <c r="B224" s="6"/>
-      <c r="C224" s="7"/>
+      <c r="B224" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C224" s="14" t="s">
+        <v>223</v>
+      </c>
       <c r="D224" s="1"/>
       <c r="E224" s="1"/>
       <c r="F224" s="1"/>
@@ -7551,10 +8352,14 @@
       <c r="Y224" s="1"/>
       <c r="Z224" s="1"/>
     </row>
-    <row r="225" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A225" s="1"/>
-      <c r="B225" s="6"/>
-      <c r="C225" s="7"/>
+      <c r="B225" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C225" s="14" t="s">
+        <v>224</v>
+      </c>
       <c r="D225" s="1"/>
       <c r="E225" s="1"/>
       <c r="F225" s="1"/>
@@ -7579,10 +8384,14 @@
       <c r="Y225" s="1"/>
       <c r="Z225" s="1"/>
     </row>
-    <row r="226" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A226" s="1"/>
-      <c r="B226" s="6"/>
-      <c r="C226" s="7"/>
+      <c r="B226" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C226" s="14" t="s">
+        <v>225</v>
+      </c>
       <c r="D226" s="1"/>
       <c r="E226" s="1"/>
       <c r="F226" s="1"/>
@@ -7607,10 +8416,14 @@
       <c r="Y226" s="1"/>
       <c r="Z226" s="1"/>
     </row>
-    <row r="227" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:26" ht="35.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A227" s="1"/>
-      <c r="B227" s="6"/>
-      <c r="C227" s="7"/>
+      <c r="B227" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C227" s="14" t="s">
+        <v>226</v>
+      </c>
       <c r="D227" s="1"/>
       <c r="E227" s="1"/>
       <c r="F227" s="1"/>
@@ -7635,10 +8448,14 @@
       <c r="Y227" s="1"/>
       <c r="Z227" s="1"/>
     </row>
-    <row r="228" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A228" s="1"/>
-      <c r="B228" s="6"/>
-      <c r="C228" s="7"/>
+      <c r="B228" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C228" s="14" t="s">
+        <v>227</v>
+      </c>
       <c r="D228" s="1"/>
       <c r="E228" s="1"/>
       <c r="F228" s="1"/>
@@ -7663,10 +8480,14 @@
       <c r="Y228" s="1"/>
       <c r="Z228" s="1"/>
     </row>
-    <row r="229" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:26" ht="35.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A229" s="1"/>
-      <c r="B229" s="6"/>
-      <c r="C229" s="7"/>
+      <c r="B229" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C229" s="14" t="s">
+        <v>228</v>
+      </c>
       <c r="D229" s="1"/>
       <c r="E229" s="1"/>
       <c r="F229" s="1"/>
@@ -7691,10 +8512,14 @@
       <c r="Y229" s="1"/>
       <c r="Z229" s="1"/>
     </row>
-    <row r="230" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A230" s="1"/>
-      <c r="B230" s="6"/>
-      <c r="C230" s="7"/>
+      <c r="B230" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C230" s="14" t="s">
+        <v>229</v>
+      </c>
       <c r="D230" s="1"/>
       <c r="E230" s="1"/>
       <c r="F230" s="1"/>
@@ -7719,10 +8544,14 @@
       <c r="Y230" s="1"/>
       <c r="Z230" s="1"/>
     </row>
-    <row r="231" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A231" s="1"/>
-      <c r="B231" s="6"/>
-      <c r="C231" s="7"/>
+      <c r="B231" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C231" s="14" t="s">
+        <v>230</v>
+      </c>
       <c r="D231" s="1"/>
       <c r="E231" s="1"/>
       <c r="F231" s="1"/>
@@ -7747,10 +8576,14 @@
       <c r="Y231" s="1"/>
       <c r="Z231" s="1"/>
     </row>
-    <row r="232" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:26" ht="35.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A232" s="1"/>
-      <c r="B232" s="6"/>
-      <c r="C232" s="7"/>
+      <c r="B232" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C232" s="14" t="s">
+        <v>231</v>
+      </c>
       <c r="D232" s="1"/>
       <c r="E232" s="1"/>
       <c r="F232" s="1"/>
@@ -7775,10 +8608,14 @@
       <c r="Y232" s="1"/>
       <c r="Z232" s="1"/>
     </row>
-    <row r="233" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A233" s="1"/>
-      <c r="B233" s="6"/>
-      <c r="C233" s="7"/>
+      <c r="B233" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C233" s="14" t="s">
+        <v>232</v>
+      </c>
       <c r="D233" s="1"/>
       <c r="E233" s="1"/>
       <c r="F233" s="1"/>
@@ -7803,10 +8640,14 @@
       <c r="Y233" s="1"/>
       <c r="Z233" s="1"/>
     </row>
-    <row r="234" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A234" s="1"/>
-      <c r="B234" s="6"/>
-      <c r="C234" s="7"/>
+      <c r="B234" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C234" s="14" t="s">
+        <v>233</v>
+      </c>
       <c r="D234" s="1"/>
       <c r="E234" s="1"/>
       <c r="F234" s="1"/>
@@ -7831,10 +8672,14 @@
       <c r="Y234" s="1"/>
       <c r="Z234" s="1"/>
     </row>
-    <row r="235" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A235" s="1"/>
-      <c r="B235" s="6"/>
-      <c r="C235" s="7"/>
+      <c r="B235" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C235" s="14" t="s">
+        <v>234</v>
+      </c>
       <c r="D235" s="1"/>
       <c r="E235" s="1"/>
       <c r="F235" s="1"/>
@@ -7859,10 +8704,14 @@
       <c r="Y235" s="1"/>
       <c r="Z235" s="1"/>
     </row>
-    <row r="236" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A236" s="1"/>
-      <c r="B236" s="6"/>
-      <c r="C236" s="7"/>
+      <c r="B236" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C236" s="14" t="s">
+        <v>235</v>
+      </c>
       <c r="D236" s="1"/>
       <c r="E236" s="1"/>
       <c r="F236" s="1"/>
@@ -7887,10 +8736,14 @@
       <c r="Y236" s="1"/>
       <c r="Z236" s="1"/>
     </row>
-    <row r="237" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:26" ht="35.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A237" s="1"/>
-      <c r="B237" s="6"/>
-      <c r="C237" s="7"/>
+      <c r="B237" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C237" s="14" t="s">
+        <v>236</v>
+      </c>
       <c r="D237" s="1"/>
       <c r="E237" s="1"/>
       <c r="F237" s="1"/>
@@ -7915,10 +8768,14 @@
       <c r="Y237" s="1"/>
       <c r="Z237" s="1"/>
     </row>
-    <row r="238" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A238" s="1"/>
-      <c r="B238" s="6"/>
-      <c r="C238" s="7"/>
+      <c r="B238" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C238" s="14" t="s">
+        <v>237</v>
+      </c>
       <c r="D238" s="1"/>
       <c r="E238" s="1"/>
       <c r="F238" s="1"/>
@@ -7943,10 +8800,14 @@
       <c r="Y238" s="1"/>
       <c r="Z238" s="1"/>
     </row>
-    <row r="239" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:26" ht="35.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A239" s="1"/>
-      <c r="B239" s="6"/>
-      <c r="C239" s="7"/>
+      <c r="B239" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C239" s="14" t="s">
+        <v>238</v>
+      </c>
       <c r="D239" s="1"/>
       <c r="E239" s="1"/>
       <c r="F239" s="1"/>
@@ -7971,10 +8832,14 @@
       <c r="Y239" s="1"/>
       <c r="Z239" s="1"/>
     </row>
-    <row r="240" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A240" s="1"/>
-      <c r="B240" s="6"/>
-      <c r="C240" s="7"/>
+      <c r="B240" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C240" s="14" t="s">
+        <v>239</v>
+      </c>
       <c r="D240" s="1"/>
       <c r="E240" s="1"/>
       <c r="F240" s="1"/>
@@ -7999,10 +8864,14 @@
       <c r="Y240" s="1"/>
       <c r="Z240" s="1"/>
     </row>
-    <row r="241" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:26" ht="35.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A241" s="1"/>
-      <c r="B241" s="6"/>
-      <c r="C241" s="7"/>
+      <c r="B241" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C241" s="14" t="s">
+        <v>240</v>
+      </c>
       <c r="D241" s="1"/>
       <c r="E241" s="1"/>
       <c r="F241" s="1"/>
@@ -8027,10 +8896,14 @@
       <c r="Y241" s="1"/>
       <c r="Z241" s="1"/>
     </row>
-    <row r="242" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A242" s="1"/>
-      <c r="B242" s="6"/>
-      <c r="C242" s="7"/>
+      <c r="B242" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C242" s="14" t="s">
+        <v>241</v>
+      </c>
       <c r="D242" s="1"/>
       <c r="E242" s="1"/>
       <c r="F242" s="1"/>
@@ -8055,10 +8928,14 @@
       <c r="Y242" s="1"/>
       <c r="Z242" s="1"/>
     </row>
-    <row r="243" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A243" s="1"/>
-      <c r="B243" s="6"/>
-      <c r="C243" s="7"/>
+      <c r="B243" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C243" s="14" t="s">
+        <v>52</v>
+      </c>
       <c r="D243" s="1"/>
       <c r="E243" s="1"/>
       <c r="F243" s="1"/>
@@ -8083,10 +8960,14 @@
       <c r="Y243" s="1"/>
       <c r="Z243" s="1"/>
     </row>
-    <row r="244" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A244" s="1"/>
-      <c r="B244" s="6"/>
-      <c r="C244" s="7"/>
+      <c r="B244" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C244" s="14" t="s">
+        <v>242</v>
+      </c>
       <c r="D244" s="1"/>
       <c r="E244" s="1"/>
       <c r="F244" s="1"/>
@@ -8111,10 +8992,14 @@
       <c r="Y244" s="1"/>
       <c r="Z244" s="1"/>
     </row>
-    <row r="245" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:26" ht="35.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A245" s="1"/>
-      <c r="B245" s="6"/>
-      <c r="C245" s="7"/>
+      <c r="B245" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C245" s="14" t="s">
+        <v>243</v>
+      </c>
       <c r="D245" s="1"/>
       <c r="E245" s="1"/>
       <c r="F245" s="1"/>
@@ -8139,10 +9024,14 @@
       <c r="Y245" s="1"/>
       <c r="Z245" s="1"/>
     </row>
-    <row r="246" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:26" ht="35.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A246" s="1"/>
-      <c r="B246" s="6"/>
-      <c r="C246" s="7"/>
+      <c r="B246" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C246" s="14" t="s">
+        <v>244</v>
+      </c>
       <c r="D246" s="1"/>
       <c r="E246" s="1"/>
       <c r="F246" s="1"/>
@@ -8167,10 +9056,14 @@
       <c r="Y246" s="1"/>
       <c r="Z246" s="1"/>
     </row>
-    <row r="247" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A247" s="1"/>
-      <c r="B247" s="6"/>
-      <c r="C247" s="7"/>
+      <c r="B247" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C247" s="14" t="s">
+        <v>245</v>
+      </c>
       <c r="D247" s="1"/>
       <c r="E247" s="1"/>
       <c r="F247" s="1"/>
@@ -8195,10 +9088,14 @@
       <c r="Y247" s="1"/>
       <c r="Z247" s="1"/>
     </row>
-    <row r="248" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A248" s="1"/>
-      <c r="B248" s="6"/>
-      <c r="C248" s="7"/>
+      <c r="B248" s="5">
+        <v>2530</v>
+      </c>
+      <c r="C248" s="14" t="s">
+        <v>246</v>
+      </c>
       <c r="D248" s="1"/>
       <c r="E248" s="1"/>
       <c r="F248" s="1"/>
@@ -8223,10 +9120,10 @@
       <c r="Y248" s="1"/>
       <c r="Z248" s="1"/>
     </row>
-    <row r="249" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A249" s="1"/>
       <c r="B249" s="6"/>
-      <c r="C249" s="7"/>
+      <c r="C249" s="11"/>
       <c r="D249" s="1"/>
       <c r="E249" s="1"/>
       <c r="F249" s="1"/>
@@ -8251,10 +9148,10 @@
       <c r="Y249" s="1"/>
       <c r="Z249" s="1"/>
     </row>
-    <row r="250" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A250" s="1"/>
       <c r="B250" s="6"/>
-      <c r="C250" s="7"/>
+      <c r="C250" s="11"/>
       <c r="D250" s="1"/>
       <c r="E250" s="1"/>
       <c r="F250" s="1"/>
@@ -8279,10 +9176,10 @@
       <c r="Y250" s="1"/>
       <c r="Z250" s="1"/>
     </row>
-    <row r="251" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A251" s="1"/>
       <c r="B251" s="6"/>
-      <c r="C251" s="7"/>
+      <c r="C251" s="11"/>
       <c r="D251" s="1"/>
       <c r="E251" s="1"/>
       <c r="F251" s="1"/>
@@ -8307,10 +9204,10 @@
       <c r="Y251" s="1"/>
       <c r="Z251" s="1"/>
     </row>
-    <row r="252" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A252" s="1"/>
       <c r="B252" s="6"/>
-      <c r="C252" s="7"/>
+      <c r="C252" s="11"/>
       <c r="D252" s="1"/>
       <c r="E252" s="1"/>
       <c r="F252" s="1"/>
@@ -8335,10 +9232,10 @@
       <c r="Y252" s="1"/>
       <c r="Z252" s="1"/>
     </row>
-    <row r="253" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A253" s="1"/>
       <c r="B253" s="6"/>
-      <c r="C253" s="7"/>
+      <c r="C253" s="11"/>
       <c r="D253" s="1"/>
       <c r="E253" s="1"/>
       <c r="F253" s="1"/>
@@ -8363,10 +9260,10 @@
       <c r="Y253" s="1"/>
       <c r="Z253" s="1"/>
     </row>
-    <row r="254" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A254" s="1"/>
       <c r="B254" s="6"/>
-      <c r="C254" s="7"/>
+      <c r="C254" s="11"/>
       <c r="D254" s="1"/>
       <c r="E254" s="1"/>
       <c r="F254" s="1"/>
@@ -8391,10 +9288,10 @@
       <c r="Y254" s="1"/>
       <c r="Z254" s="1"/>
     </row>
-    <row r="255" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A255" s="1"/>
       <c r="B255" s="6"/>
-      <c r="C255" s="7"/>
+      <c r="C255" s="11"/>
       <c r="D255" s="1"/>
       <c r="E255" s="1"/>
       <c r="F255" s="1"/>
@@ -8419,10 +9316,10 @@
       <c r="Y255" s="1"/>
       <c r="Z255" s="1"/>
     </row>
-    <row r="256" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A256" s="1"/>
       <c r="B256" s="6"/>
-      <c r="C256" s="7"/>
+      <c r="C256" s="11"/>
       <c r="D256" s="1"/>
       <c r="E256" s="1"/>
       <c r="F256" s="1"/>
@@ -8447,10 +9344,10 @@
       <c r="Y256" s="1"/>
       <c r="Z256" s="1"/>
     </row>
-    <row r="257" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A257" s="1"/>
       <c r="B257" s="6"/>
-      <c r="C257" s="7"/>
+      <c r="C257" s="11"/>
       <c r="D257" s="1"/>
       <c r="E257" s="1"/>
       <c r="F257" s="1"/>
@@ -8475,10 +9372,10 @@
       <c r="Y257" s="1"/>
       <c r="Z257" s="1"/>
     </row>
-    <row r="258" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A258" s="1"/>
       <c r="B258" s="6"/>
-      <c r="C258" s="7"/>
+      <c r="C258" s="11"/>
       <c r="D258" s="1"/>
       <c r="E258" s="1"/>
       <c r="F258" s="1"/>
@@ -8503,10 +9400,10 @@
       <c r="Y258" s="1"/>
       <c r="Z258" s="1"/>
     </row>
-    <row r="259" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A259" s="1"/>
       <c r="B259" s="6"/>
-      <c r="C259" s="7"/>
+      <c r="C259" s="12"/>
       <c r="D259" s="1"/>
       <c r="E259" s="1"/>
       <c r="F259" s="1"/>
@@ -8531,10 +9428,10 @@
       <c r="Y259" s="1"/>
       <c r="Z259" s="1"/>
     </row>
-    <row r="260" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A260" s="1"/>
       <c r="B260" s="6"/>
-      <c r="C260" s="7"/>
+      <c r="C260" s="11"/>
       <c r="D260" s="1"/>
       <c r="E260" s="1"/>
       <c r="F260" s="1"/>
@@ -8559,10 +9456,10 @@
       <c r="Y260" s="1"/>
       <c r="Z260" s="1"/>
     </row>
-    <row r="261" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A261" s="1"/>
       <c r="B261" s="6"/>
-      <c r="C261" s="7"/>
+      <c r="C261" s="11"/>
       <c r="D261" s="1"/>
       <c r="E261" s="1"/>
       <c r="F261" s="1"/>
@@ -8587,10 +9484,10 @@
       <c r="Y261" s="1"/>
       <c r="Z261" s="1"/>
     </row>
-    <row r="262" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A262" s="1"/>
       <c r="B262" s="6"/>
-      <c r="C262" s="7"/>
+      <c r="C262" s="11"/>
       <c r="D262" s="1"/>
       <c r="E262" s="1"/>
       <c r="F262" s="1"/>
@@ -8615,10 +9512,10 @@
       <c r="Y262" s="1"/>
       <c r="Z262" s="1"/>
     </row>
-    <row r="263" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A263" s="1"/>
       <c r="B263" s="6"/>
-      <c r="C263" s="7"/>
+      <c r="C263" s="11"/>
       <c r="D263" s="1"/>
       <c r="E263" s="1"/>
       <c r="F263" s="1"/>
@@ -8643,10 +9540,10 @@
       <c r="Y263" s="1"/>
       <c r="Z263" s="1"/>
     </row>
-    <row r="264" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A264" s="1"/>
       <c r="B264" s="6"/>
-      <c r="C264" s="7"/>
+      <c r="C264" s="11"/>
       <c r="D264" s="1"/>
       <c r="E264" s="1"/>
       <c r="F264" s="1"/>
@@ -8671,10 +9568,10 @@
       <c r="Y264" s="1"/>
       <c r="Z264" s="1"/>
     </row>
-    <row r="265" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A265" s="1"/>
       <c r="B265" s="6"/>
-      <c r="C265" s="7"/>
+      <c r="C265" s="11"/>
       <c r="D265" s="1"/>
       <c r="E265" s="1"/>
       <c r="F265" s="1"/>
@@ -8699,10 +9596,10 @@
       <c r="Y265" s="1"/>
       <c r="Z265" s="1"/>
     </row>
-    <row r="266" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A266" s="1"/>
       <c r="B266" s="6"/>
-      <c r="C266" s="7"/>
+      <c r="C266" s="11"/>
       <c r="D266" s="1"/>
       <c r="E266" s="1"/>
       <c r="F266" s="1"/>
@@ -8727,10 +9624,10 @@
       <c r="Y266" s="1"/>
       <c r="Z266" s="1"/>
     </row>
-    <row r="267" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A267" s="1"/>
       <c r="B267" s="6"/>
-      <c r="C267" s="7"/>
+      <c r="C267" s="11"/>
       <c r="D267" s="1"/>
       <c r="E267" s="1"/>
       <c r="F267" s="1"/>
@@ -8755,10 +9652,10 @@
       <c r="Y267" s="1"/>
       <c r="Z267" s="1"/>
     </row>
-    <row r="268" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A268" s="1"/>
       <c r="B268" s="6"/>
-      <c r="C268" s="7"/>
+      <c r="C268" s="11"/>
       <c r="D268" s="1"/>
       <c r="E268" s="1"/>
       <c r="F268" s="1"/>
@@ -8783,10 +9680,10 @@
       <c r="Y268" s="1"/>
       <c r="Z268" s="1"/>
     </row>
-    <row r="269" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A269" s="1"/>
       <c r="B269" s="6"/>
-      <c r="C269" s="7"/>
+      <c r="C269" s="11"/>
       <c r="D269" s="1"/>
       <c r="E269" s="1"/>
       <c r="F269" s="1"/>
@@ -8811,10 +9708,10 @@
       <c r="Y269" s="1"/>
       <c r="Z269" s="1"/>
     </row>
-    <row r="270" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A270" s="1"/>
       <c r="B270" s="6"/>
-      <c r="C270" s="7"/>
+      <c r="C270" s="11"/>
       <c r="D270" s="1"/>
       <c r="E270" s="1"/>
       <c r="F270" s="1"/>
@@ -8839,10 +9736,10 @@
       <c r="Y270" s="1"/>
       <c r="Z270" s="1"/>
     </row>
-    <row r="271" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A271" s="1"/>
       <c r="B271" s="6"/>
-      <c r="C271" s="7"/>
+      <c r="C271" s="11"/>
       <c r="D271" s="1"/>
       <c r="E271" s="1"/>
       <c r="F271" s="1"/>
@@ -8867,10 +9764,10 @@
       <c r="Y271" s="1"/>
       <c r="Z271" s="1"/>
     </row>
-    <row r="272" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A272" s="1"/>
       <c r="B272" s="6"/>
-      <c r="C272" s="7"/>
+      <c r="C272" s="11"/>
       <c r="D272" s="1"/>
       <c r="E272" s="1"/>
       <c r="F272" s="1"/>
@@ -8895,10 +9792,10 @@
       <c r="Y272" s="1"/>
       <c r="Z272" s="1"/>
     </row>
-    <row r="273" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A273" s="1"/>
       <c r="B273" s="6"/>
-      <c r="C273" s="7"/>
+      <c r="C273" s="11"/>
       <c r="D273" s="1"/>
       <c r="E273" s="1"/>
       <c r="F273" s="1"/>
@@ -8923,10 +9820,10 @@
       <c r="Y273" s="1"/>
       <c r="Z273" s="1"/>
     </row>
-    <row r="274" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A274" s="1"/>
       <c r="B274" s="6"/>
-      <c r="C274" s="7"/>
+      <c r="C274" s="11"/>
       <c r="D274" s="1"/>
       <c r="E274" s="1"/>
       <c r="F274" s="1"/>
@@ -8951,10 +9848,10 @@
       <c r="Y274" s="1"/>
       <c r="Z274" s="1"/>
     </row>
-    <row r="275" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A275" s="1"/>
       <c r="B275" s="6"/>
-      <c r="C275" s="7"/>
+      <c r="C275" s="11"/>
       <c r="D275" s="1"/>
       <c r="E275" s="1"/>
       <c r="F275" s="1"/>
@@ -8979,10 +9876,10 @@
       <c r="Y275" s="1"/>
       <c r="Z275" s="1"/>
     </row>
-    <row r="276" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A276" s="1"/>
       <c r="B276" s="6"/>
-      <c r="C276" s="7"/>
+      <c r="C276" s="11"/>
       <c r="D276" s="1"/>
       <c r="E276" s="1"/>
       <c r="F276" s="1"/>
@@ -9007,10 +9904,10 @@
       <c r="Y276" s="1"/>
       <c r="Z276" s="1"/>
     </row>
-    <row r="277" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A277" s="1"/>
       <c r="B277" s="6"/>
-      <c r="C277" s="7"/>
+      <c r="C277" s="11"/>
       <c r="D277" s="1"/>
       <c r="E277" s="1"/>
       <c r="F277" s="1"/>
@@ -9035,7 +9932,7 @@
       <c r="Y277" s="1"/>
       <c r="Z277" s="1"/>
     </row>
-    <row r="278" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A278" s="1"/>
       <c r="B278" s="6"/>
       <c r="C278" s="7"/>
@@ -9063,7 +9960,7 @@
       <c r="Y278" s="1"/>
       <c r="Z278" s="1"/>
     </row>
-    <row r="279" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A279" s="1"/>
       <c r="B279" s="6"/>
       <c r="C279" s="7"/>
@@ -9091,7 +9988,7 @@
       <c r="Y279" s="1"/>
       <c r="Z279" s="1"/>
     </row>
-    <row r="280" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A280" s="1"/>
       <c r="B280" s="6"/>
       <c r="C280" s="7"/>
@@ -9119,7 +10016,7 @@
       <c r="Y280" s="1"/>
       <c r="Z280" s="1"/>
     </row>
-    <row r="281" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A281" s="1"/>
       <c r="B281" s="6"/>
       <c r="C281" s="7"/>
@@ -9147,7 +10044,7 @@
       <c r="Y281" s="1"/>
       <c r="Z281" s="1"/>
     </row>
-    <row r="282" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A282" s="1"/>
       <c r="B282" s="6"/>
       <c r="C282" s="7"/>
@@ -9175,7 +10072,7 @@
       <c r="Y282" s="1"/>
       <c r="Z282" s="1"/>
     </row>
-    <row r="283" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A283" s="1"/>
       <c r="B283" s="6"/>
       <c r="C283" s="7"/>
@@ -9203,7 +10100,7 @@
       <c r="Y283" s="1"/>
       <c r="Z283" s="1"/>
     </row>
-    <row r="284" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A284" s="1"/>
       <c r="B284" s="6"/>
       <c r="C284" s="7"/>
@@ -9231,7 +10128,7 @@
       <c r="Y284" s="1"/>
       <c r="Z284" s="1"/>
     </row>
-    <row r="285" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A285" s="1"/>
       <c r="B285" s="6"/>
       <c r="C285" s="7"/>
@@ -9259,7 +10156,7 @@
       <c r="Y285" s="1"/>
       <c r="Z285" s="1"/>
     </row>
-    <row r="286" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A286" s="1"/>
       <c r="B286" s="6"/>
       <c r="C286" s="7"/>
@@ -9287,7 +10184,7 @@
       <c r="Y286" s="1"/>
       <c r="Z286" s="1"/>
     </row>
-    <row r="287" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A287" s="1"/>
       <c r="B287" s="6"/>
       <c r="C287" s="7"/>
@@ -9315,7 +10212,7 @@
       <c r="Y287" s="1"/>
       <c r="Z287" s="1"/>
     </row>
-    <row r="288" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A288" s="1"/>
       <c r="B288" s="6"/>
       <c r="C288" s="7"/>
@@ -9343,7 +10240,7 @@
       <c r="Y288" s="1"/>
       <c r="Z288" s="1"/>
     </row>
-    <row r="289" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A289" s="1"/>
       <c r="B289" s="6"/>
       <c r="C289" s="7"/>
@@ -9371,7 +10268,7 @@
       <c r="Y289" s="1"/>
       <c r="Z289" s="1"/>
     </row>
-    <row r="290" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A290" s="1"/>
       <c r="B290" s="6"/>
       <c r="C290" s="7"/>
@@ -9399,7 +10296,7 @@
       <c r="Y290" s="1"/>
       <c r="Z290" s="1"/>
     </row>
-    <row r="291" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A291" s="1"/>
       <c r="B291" s="6"/>
       <c r="C291" s="7"/>
@@ -9427,7 +10324,7 @@
       <c r="Y291" s="1"/>
       <c r="Z291" s="1"/>
     </row>
-    <row r="292" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A292" s="1"/>
       <c r="B292" s="6"/>
       <c r="C292" s="7"/>
@@ -9455,7 +10352,7 @@
       <c r="Y292" s="1"/>
       <c r="Z292" s="1"/>
     </row>
-    <row r="293" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A293" s="1"/>
       <c r="B293" s="6"/>
       <c r="C293" s="7"/>
@@ -9483,7 +10380,7 @@
       <c r="Y293" s="1"/>
       <c r="Z293" s="1"/>
     </row>
-    <row r="294" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A294" s="1"/>
       <c r="B294" s="6"/>
       <c r="C294" s="7"/>
@@ -9511,7 +10408,7 @@
       <c r="Y294" s="1"/>
       <c r="Z294" s="1"/>
     </row>
-    <row r="295" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A295" s="1"/>
       <c r="B295" s="6"/>
       <c r="C295" s="7"/>
@@ -9539,7 +10436,7 @@
       <c r="Y295" s="1"/>
       <c r="Z295" s="1"/>
     </row>
-    <row r="296" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A296" s="1"/>
       <c r="B296" s="6"/>
       <c r="C296" s="7"/>
@@ -9567,7 +10464,7 @@
       <c r="Y296" s="1"/>
       <c r="Z296" s="1"/>
     </row>
-    <row r="297" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A297" s="1"/>
       <c r="B297" s="6"/>
       <c r="C297" s="7"/>
@@ -9595,7 +10492,7 @@
       <c r="Y297" s="1"/>
       <c r="Z297" s="1"/>
     </row>
-    <row r="298" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A298" s="1"/>
       <c r="B298" s="6"/>
       <c r="C298" s="7"/>
@@ -9623,7 +10520,7 @@
       <c r="Y298" s="1"/>
       <c r="Z298" s="1"/>
     </row>
-    <row r="299" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A299" s="1"/>
       <c r="B299" s="6"/>
       <c r="C299" s="7"/>
@@ -9651,7 +10548,7 @@
       <c r="Y299" s="1"/>
       <c r="Z299" s="1"/>
     </row>
-    <row r="300" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A300" s="1"/>
       <c r="B300" s="6"/>
       <c r="C300" s="7"/>
@@ -9679,7 +10576,7 @@
       <c r="Y300" s="1"/>
       <c r="Z300" s="1"/>
     </row>
-    <row r="301" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A301" s="1"/>
       <c r="B301" s="6"/>
       <c r="C301" s="7"/>
@@ -9707,7 +10604,7 @@
       <c r="Y301" s="1"/>
       <c r="Z301" s="1"/>
     </row>
-    <row r="302" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A302" s="1"/>
       <c r="B302" s="6"/>
       <c r="C302" s="7"/>
@@ -9735,7 +10632,7 @@
       <c r="Y302" s="1"/>
       <c r="Z302" s="1"/>
     </row>
-    <row r="303" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A303" s="1"/>
       <c r="B303" s="6"/>
       <c r="C303" s="7"/>
@@ -9763,7 +10660,7 @@
       <c r="Y303" s="1"/>
       <c r="Z303" s="1"/>
     </row>
-    <row r="304" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A304" s="1"/>
       <c r="B304" s="6"/>
       <c r="C304" s="7"/>
@@ -9791,7 +10688,7 @@
       <c r="Y304" s="1"/>
       <c r="Z304" s="1"/>
     </row>
-    <row r="305" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A305" s="1"/>
       <c r="B305" s="6"/>
       <c r="C305" s="7"/>
@@ -9819,7 +10716,7 @@
       <c r="Y305" s="1"/>
       <c r="Z305" s="1"/>
     </row>
-    <row r="306" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A306" s="1"/>
       <c r="B306" s="6"/>
       <c r="C306" s="7"/>
@@ -9847,7 +10744,7 @@
       <c r="Y306" s="1"/>
       <c r="Z306" s="1"/>
     </row>
-    <row r="307" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A307" s="1"/>
       <c r="B307" s="6"/>
       <c r="C307" s="7"/>
@@ -9875,7 +10772,7 @@
       <c r="Y307" s="1"/>
       <c r="Z307" s="1"/>
     </row>
-    <row r="308" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A308" s="1"/>
       <c r="B308" s="6"/>
       <c r="C308" s="7"/>
@@ -9903,7 +10800,7 @@
       <c r="Y308" s="1"/>
       <c r="Z308" s="1"/>
     </row>
-    <row r="309" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A309" s="1"/>
       <c r="B309" s="6"/>
       <c r="C309" s="7"/>
@@ -9931,7 +10828,7 @@
       <c r="Y309" s="1"/>
       <c r="Z309" s="1"/>
     </row>
-    <row r="310" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A310" s="1"/>
       <c r="B310" s="6"/>
       <c r="C310" s="7"/>
@@ -9959,7 +10856,7 @@
       <c r="Y310" s="1"/>
       <c r="Z310" s="1"/>
     </row>
-    <row r="311" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A311" s="1"/>
       <c r="B311" s="6"/>
       <c r="C311" s="7"/>
@@ -9987,7 +10884,7 @@
       <c r="Y311" s="1"/>
       <c r="Z311" s="1"/>
     </row>
-    <row r="312" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A312" s="1"/>
       <c r="B312" s="6"/>
       <c r="C312" s="7"/>
@@ -10015,7 +10912,7 @@
       <c r="Y312" s="1"/>
       <c r="Z312" s="1"/>
     </row>
-    <row r="313" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A313" s="1"/>
       <c r="B313" s="6"/>
       <c r="C313" s="7"/>
@@ -10043,7 +10940,7 @@
       <c r="Y313" s="1"/>
       <c r="Z313" s="1"/>
     </row>
-    <row r="314" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A314" s="1"/>
       <c r="B314" s="6"/>
       <c r="C314" s="7"/>
@@ -10071,7 +10968,7 @@
       <c r="Y314" s="1"/>
       <c r="Z314" s="1"/>
     </row>
-    <row r="315" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A315" s="1"/>
       <c r="B315" s="6"/>
       <c r="C315" s="7"/>
@@ -10099,7 +10996,7 @@
       <c r="Y315" s="1"/>
       <c r="Z315" s="1"/>
     </row>
-    <row r="316" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A316" s="1"/>
       <c r="B316" s="6"/>
       <c r="C316" s="7"/>
@@ -10127,7 +11024,7 @@
       <c r="Y316" s="1"/>
       <c r="Z316" s="1"/>
     </row>
-    <row r="317" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A317" s="1"/>
       <c r="B317" s="6"/>
       <c r="C317" s="7"/>
@@ -10155,7 +11052,7 @@
       <c r="Y317" s="1"/>
       <c r="Z317" s="1"/>
     </row>
-    <row r="318" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A318" s="1"/>
       <c r="B318" s="6"/>
       <c r="C318" s="7"/>
@@ -10183,7 +11080,7 @@
       <c r="Y318" s="1"/>
       <c r="Z318" s="1"/>
     </row>
-    <row r="319" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A319" s="1"/>
       <c r="B319" s="6"/>
       <c r="C319" s="7"/>
@@ -10211,7 +11108,7 @@
       <c r="Y319" s="1"/>
       <c r="Z319" s="1"/>
     </row>
-    <row r="320" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A320" s="1"/>
       <c r="B320" s="6"/>
       <c r="C320" s="7"/>
@@ -10239,7 +11136,7 @@
       <c r="Y320" s="1"/>
       <c r="Z320" s="1"/>
     </row>
-    <row r="321" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A321" s="1"/>
       <c r="B321" s="6"/>
       <c r="C321" s="7"/>
@@ -10267,7 +11164,7 @@
       <c r="Y321" s="1"/>
       <c r="Z321" s="1"/>
     </row>
-    <row r="322" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A322" s="1"/>
       <c r="B322" s="6"/>
       <c r="C322" s="7"/>
@@ -10295,7 +11192,7 @@
       <c r="Y322" s="1"/>
       <c r="Z322" s="1"/>
     </row>
-    <row r="323" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A323" s="1"/>
       <c r="B323" s="6"/>
       <c r="C323" s="7"/>
@@ -10323,7 +11220,7 @@
       <c r="Y323" s="1"/>
       <c r="Z323" s="1"/>
     </row>
-    <row r="324" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A324" s="1"/>
       <c r="B324" s="6"/>
       <c r="C324" s="7"/>
@@ -10351,7 +11248,7 @@
       <c r="Y324" s="1"/>
       <c r="Z324" s="1"/>
     </row>
-    <row r="325" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A325" s="1"/>
       <c r="B325" s="6"/>
       <c r="C325" s="7"/>
@@ -10379,7 +11276,7 @@
       <c r="Y325" s="1"/>
       <c r="Z325" s="1"/>
     </row>
-    <row r="326" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A326" s="1"/>
       <c r="B326" s="6"/>
       <c r="C326" s="7"/>
@@ -10407,7 +11304,7 @@
       <c r="Y326" s="1"/>
       <c r="Z326" s="1"/>
     </row>
-    <row r="327" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A327" s="1"/>
       <c r="B327" s="6"/>
       <c r="C327" s="7"/>
@@ -10435,7 +11332,7 @@
       <c r="Y327" s="1"/>
       <c r="Z327" s="1"/>
     </row>
-    <row r="328" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A328" s="1"/>
       <c r="B328" s="6"/>
       <c r="C328" s="7"/>
@@ -10463,7 +11360,7 @@
       <c r="Y328" s="1"/>
       <c r="Z328" s="1"/>
     </row>
-    <row r="329" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A329" s="1"/>
       <c r="B329" s="6"/>
       <c r="C329" s="7"/>
@@ -10491,7 +11388,7 @@
       <c r="Y329" s="1"/>
       <c r="Z329" s="1"/>
     </row>
-    <row r="330" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A330" s="1"/>
       <c r="B330" s="6"/>
       <c r="C330" s="7"/>
@@ -10519,7 +11416,7 @@
       <c r="Y330" s="1"/>
       <c r="Z330" s="1"/>
     </row>
-    <row r="331" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A331" s="1"/>
       <c r="B331" s="6"/>
       <c r="C331" s="7"/>
@@ -10547,7 +11444,7 @@
       <c r="Y331" s="1"/>
       <c r="Z331" s="1"/>
     </row>
-    <row r="332" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A332" s="1"/>
       <c r="B332" s="6"/>
       <c r="C332" s="7"/>
@@ -10575,7 +11472,7 @@
       <c r="Y332" s="1"/>
       <c r="Z332" s="1"/>
     </row>
-    <row r="333" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A333" s="1"/>
       <c r="B333" s="6"/>
       <c r="C333" s="7"/>
@@ -10603,7 +11500,7 @@
       <c r="Y333" s="1"/>
       <c r="Z333" s="1"/>
     </row>
-    <row r="334" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A334" s="1"/>
       <c r="B334" s="6"/>
       <c r="C334" s="7"/>
@@ -10631,7 +11528,7 @@
       <c r="Y334" s="1"/>
       <c r="Z334" s="1"/>
     </row>
-    <row r="335" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A335" s="1"/>
       <c r="B335" s="6"/>
       <c r="C335" s="7"/>
@@ -10659,7 +11556,7 @@
       <c r="Y335" s="1"/>
       <c r="Z335" s="1"/>
     </row>
-    <row r="336" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A336" s="1"/>
       <c r="B336" s="6"/>
       <c r="C336" s="7"/>
@@ -10687,7 +11584,7 @@
       <c r="Y336" s="1"/>
       <c r="Z336" s="1"/>
     </row>
-    <row r="337" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A337" s="1"/>
       <c r="B337" s="6"/>
       <c r="C337" s="7"/>
@@ -10715,7 +11612,7 @@
       <c r="Y337" s="1"/>
       <c r="Z337" s="1"/>
     </row>
-    <row r="338" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A338" s="1"/>
       <c r="B338" s="6"/>
       <c r="C338" s="7"/>
@@ -10743,7 +11640,7 @@
       <c r="Y338" s="1"/>
       <c r="Z338" s="1"/>
     </row>
-    <row r="339" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A339" s="1"/>
       <c r="B339" s="6"/>
       <c r="C339" s="7"/>
@@ -10771,7 +11668,7 @@
       <c r="Y339" s="1"/>
       <c r="Z339" s="1"/>
     </row>
-    <row r="340" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A340" s="1"/>
       <c r="B340" s="6"/>
       <c r="C340" s="7"/>
@@ -10799,7 +11696,7 @@
       <c r="Y340" s="1"/>
       <c r="Z340" s="1"/>
     </row>
-    <row r="341" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A341" s="1"/>
       <c r="B341" s="6"/>
       <c r="C341" s="7"/>
@@ -10827,7 +11724,7 @@
       <c r="Y341" s="1"/>
       <c r="Z341" s="1"/>
     </row>
-    <row r="342" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A342" s="1"/>
       <c r="B342" s="6"/>
       <c r="C342" s="7"/>
@@ -10855,7 +11752,7 @@
       <c r="Y342" s="1"/>
       <c r="Z342" s="1"/>
     </row>
-    <row r="343" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A343" s="1"/>
       <c r="B343" s="6"/>
       <c r="C343" s="7"/>
@@ -10883,7 +11780,7 @@
       <c r="Y343" s="1"/>
       <c r="Z343" s="1"/>
     </row>
-    <row r="344" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A344" s="1"/>
       <c r="B344" s="6"/>
       <c r="C344" s="7"/>
@@ -10911,7 +11808,7 @@
       <c r="Y344" s="1"/>
       <c r="Z344" s="1"/>
     </row>
-    <row r="345" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A345" s="1"/>
       <c r="B345" s="6"/>
       <c r="C345" s="7"/>
@@ -10939,7 +11836,7 @@
       <c r="Y345" s="1"/>
       <c r="Z345" s="1"/>
     </row>
-    <row r="346" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A346" s="1"/>
       <c r="B346" s="6"/>
       <c r="C346" s="7"/>
@@ -10967,7 +11864,7 @@
       <c r="Y346" s="1"/>
       <c r="Z346" s="1"/>
     </row>
-    <row r="347" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A347" s="1"/>
       <c r="B347" s="6"/>
       <c r="C347" s="7"/>
@@ -10995,7 +11892,7 @@
       <c r="Y347" s="1"/>
       <c r="Z347" s="1"/>
     </row>
-    <row r="348" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A348" s="1"/>
       <c r="B348" s="6"/>
       <c r="C348" s="7"/>
@@ -11023,7 +11920,7 @@
       <c r="Y348" s="1"/>
       <c r="Z348" s="1"/>
     </row>
-    <row r="349" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A349" s="1"/>
       <c r="B349" s="6"/>
       <c r="C349" s="7"/>
@@ -11051,7 +11948,7 @@
       <c r="Y349" s="1"/>
       <c r="Z349" s="1"/>
     </row>
-    <row r="350" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A350" s="1"/>
       <c r="B350" s="6"/>
       <c r="C350" s="7"/>
@@ -11079,7 +11976,7 @@
       <c r="Y350" s="1"/>
       <c r="Z350" s="1"/>
     </row>
-    <row r="351" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A351" s="1"/>
       <c r="B351" s="6"/>
       <c r="C351" s="7"/>
@@ -11107,7 +12004,7 @@
       <c r="Y351" s="1"/>
       <c r="Z351" s="1"/>
     </row>
-    <row r="352" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A352" s="1"/>
       <c r="B352" s="6"/>
       <c r="C352" s="7"/>
@@ -11135,7 +12032,7 @@
       <c r="Y352" s="1"/>
       <c r="Z352" s="1"/>
     </row>
-    <row r="353" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A353" s="1"/>
       <c r="B353" s="6"/>
       <c r="C353" s="7"/>
@@ -11163,7 +12060,7 @@
       <c r="Y353" s="1"/>
       <c r="Z353" s="1"/>
     </row>
-    <row r="354" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A354" s="1"/>
       <c r="B354" s="6"/>
       <c r="C354" s="7"/>
@@ -11191,7 +12088,7 @@
       <c r="Y354" s="1"/>
       <c r="Z354" s="1"/>
     </row>
-    <row r="355" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A355" s="1"/>
       <c r="B355" s="6"/>
       <c r="C355" s="7"/>
@@ -11219,7 +12116,7 @@
       <c r="Y355" s="1"/>
       <c r="Z355" s="1"/>
     </row>
-    <row r="356" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A356" s="1"/>
       <c r="B356" s="6"/>
       <c r="C356" s="7"/>
@@ -11247,7 +12144,7 @@
       <c r="Y356" s="1"/>
       <c r="Z356" s="1"/>
     </row>
-    <row r="357" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A357" s="1"/>
       <c r="B357" s="6"/>
       <c r="C357" s="7"/>
@@ -11275,7 +12172,7 @@
       <c r="Y357" s="1"/>
       <c r="Z357" s="1"/>
     </row>
-    <row r="358" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A358" s="1"/>
       <c r="B358" s="6"/>
       <c r="C358" s="7"/>
@@ -11303,7 +12200,7 @@
       <c r="Y358" s="1"/>
       <c r="Z358" s="1"/>
     </row>
-    <row r="359" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A359" s="1"/>
       <c r="B359" s="6"/>
       <c r="C359" s="7"/>
@@ -11331,7 +12228,7 @@
       <c r="Y359" s="1"/>
       <c r="Z359" s="1"/>
     </row>
-    <row r="360" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A360" s="1"/>
       <c r="B360" s="6"/>
       <c r="C360" s="7"/>
@@ -11359,7 +12256,7 @@
       <c r="Y360" s="1"/>
       <c r="Z360" s="1"/>
     </row>
-    <row r="361" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A361" s="1"/>
       <c r="B361" s="6"/>
       <c r="C361" s="7"/>
@@ -11387,7 +12284,7 @@
       <c r="Y361" s="1"/>
       <c r="Z361" s="1"/>
     </row>
-    <row r="362" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A362" s="1"/>
       <c r="B362" s="6"/>
       <c r="C362" s="7"/>
@@ -11415,7 +12312,7 @@
       <c r="Y362" s="1"/>
       <c r="Z362" s="1"/>
     </row>
-    <row r="363" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A363" s="1"/>
       <c r="B363" s="6"/>
       <c r="C363" s="7"/>
@@ -11443,7 +12340,7 @@
       <c r="Y363" s="1"/>
       <c r="Z363" s="1"/>
     </row>
-    <row r="364" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A364" s="1"/>
       <c r="B364" s="6"/>
       <c r="C364" s="7"/>
@@ -11471,7 +12368,7 @@
       <c r="Y364" s="1"/>
       <c r="Z364" s="1"/>
     </row>
-    <row r="365" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A365" s="1"/>
       <c r="B365" s="6"/>
       <c r="C365" s="7"/>
@@ -11499,7 +12396,7 @@
       <c r="Y365" s="1"/>
       <c r="Z365" s="1"/>
     </row>
-    <row r="366" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A366" s="1"/>
       <c r="B366" s="6"/>
       <c r="C366" s="7"/>
@@ -11527,7 +12424,7 @@
       <c r="Y366" s="1"/>
       <c r="Z366" s="1"/>
     </row>
-    <row r="367" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A367" s="1"/>
       <c r="B367" s="6"/>
       <c r="C367" s="7"/>
@@ -11555,7 +12452,7 @@
       <c r="Y367" s="1"/>
       <c r="Z367" s="1"/>
     </row>
-    <row r="368" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A368" s="1"/>
       <c r="B368" s="6"/>
       <c r="C368" s="7"/>
@@ -11583,7 +12480,7 @@
       <c r="Y368" s="1"/>
       <c r="Z368" s="1"/>
     </row>
-    <row r="369" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A369" s="1"/>
       <c r="B369" s="6"/>
       <c r="C369" s="7"/>
@@ -11611,7 +12508,7 @@
       <c r="Y369" s="1"/>
       <c r="Z369" s="1"/>
     </row>
-    <row r="370" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A370" s="1"/>
       <c r="B370" s="6"/>
       <c r="C370" s="7"/>
@@ -11639,7 +12536,7 @@
       <c r="Y370" s="1"/>
       <c r="Z370" s="1"/>
     </row>
-    <row r="371" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A371" s="1"/>
       <c r="B371" s="6"/>
       <c r="C371" s="7"/>
@@ -11667,7 +12564,7 @@
       <c r="Y371" s="1"/>
       <c r="Z371" s="1"/>
     </row>
-    <row r="372" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A372" s="1"/>
       <c r="B372" s="6"/>
       <c r="C372" s="7"/>
@@ -11695,7 +12592,7 @@
       <c r="Y372" s="1"/>
       <c r="Z372" s="1"/>
     </row>
-    <row r="373" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A373" s="1"/>
       <c r="B373" s="6"/>
       <c r="C373" s="7"/>
@@ -11723,7 +12620,7 @@
       <c r="Y373" s="1"/>
       <c r="Z373" s="1"/>
     </row>
-    <row r="374" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A374" s="1"/>
       <c r="B374" s="6"/>
       <c r="C374" s="7"/>
@@ -11751,7 +12648,7 @@
       <c r="Y374" s="1"/>
       <c r="Z374" s="1"/>
     </row>
-    <row r="375" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A375" s="1"/>
       <c r="B375" s="6"/>
       <c r="C375" s="7"/>
@@ -11779,7 +12676,7 @@
       <c r="Y375" s="1"/>
       <c r="Z375" s="1"/>
     </row>
-    <row r="376" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A376" s="1"/>
       <c r="B376" s="6"/>
       <c r="C376" s="7"/>
@@ -11807,7 +12704,7 @@
       <c r="Y376" s="1"/>
       <c r="Z376" s="1"/>
     </row>
-    <row r="377" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A377" s="1"/>
       <c r="B377" s="6"/>
       <c r="C377" s="7"/>
@@ -11835,7 +12732,7 @@
       <c r="Y377" s="1"/>
       <c r="Z377" s="1"/>
     </row>
-    <row r="378" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A378" s="1"/>
       <c r="B378" s="6"/>
       <c r="C378" s="7"/>
@@ -11863,7 +12760,7 @@
       <c r="Y378" s="1"/>
       <c r="Z378" s="1"/>
     </row>
-    <row r="379" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A379" s="1"/>
       <c r="B379" s="6"/>
       <c r="C379" s="7"/>
@@ -11891,7 +12788,7 @@
       <c r="Y379" s="1"/>
       <c r="Z379" s="1"/>
     </row>
-    <row r="380" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A380" s="1"/>
       <c r="B380" s="6"/>
       <c r="C380" s="7"/>
@@ -11919,7 +12816,7 @@
       <c r="Y380" s="1"/>
       <c r="Z380" s="1"/>
     </row>
-    <row r="381" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A381" s="1"/>
       <c r="B381" s="6"/>
       <c r="C381" s="7"/>
@@ -11947,7 +12844,7 @@
       <c r="Y381" s="1"/>
       <c r="Z381" s="1"/>
     </row>
-    <row r="382" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A382" s="1"/>
       <c r="B382" s="6"/>
       <c r="C382" s="7"/>
@@ -11975,7 +12872,7 @@
       <c r="Y382" s="1"/>
       <c r="Z382" s="1"/>
     </row>
-    <row r="383" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A383" s="1"/>
       <c r="B383" s="6"/>
       <c r="C383" s="7"/>
@@ -12003,7 +12900,7 @@
       <c r="Y383" s="1"/>
       <c r="Z383" s="1"/>
     </row>
-    <row r="384" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A384" s="1"/>
       <c r="B384" s="6"/>
       <c r="C384" s="7"/>
@@ -12031,7 +12928,7 @@
       <c r="Y384" s="1"/>
       <c r="Z384" s="1"/>
     </row>
-    <row r="385" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A385" s="1"/>
       <c r="B385" s="6"/>
       <c r="C385" s="7"/>
@@ -12059,7 +12956,7 @@
       <c r="Y385" s="1"/>
       <c r="Z385" s="1"/>
     </row>
-    <row r="386" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A386" s="1"/>
       <c r="B386" s="6"/>
       <c r="C386" s="7"/>
@@ -12087,7 +12984,7 @@
       <c r="Y386" s="1"/>
       <c r="Z386" s="1"/>
     </row>
-    <row r="387" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A387" s="1"/>
       <c r="B387" s="6"/>
       <c r="C387" s="7"/>
@@ -12115,7 +13012,7 @@
       <c r="Y387" s="1"/>
       <c r="Z387" s="1"/>
     </row>
-    <row r="388" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A388" s="1"/>
       <c r="B388" s="6"/>
       <c r="C388" s="7"/>
@@ -12143,7 +13040,7 @@
       <c r="Y388" s="1"/>
       <c r="Z388" s="1"/>
     </row>
-    <row r="389" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A389" s="1"/>
       <c r="B389" s="6"/>
       <c r="C389" s="7"/>
@@ -12171,7 +13068,7 @@
       <c r="Y389" s="1"/>
       <c r="Z389" s="1"/>
     </row>
-    <row r="390" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A390" s="1"/>
       <c r="B390" s="6"/>
       <c r="C390" s="7"/>
@@ -12199,7 +13096,7 @@
       <c r="Y390" s="1"/>
       <c r="Z390" s="1"/>
     </row>
-    <row r="391" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A391" s="1"/>
       <c r="B391" s="6"/>
       <c r="C391" s="7"/>
@@ -12227,7 +13124,7 @@
       <c r="Y391" s="1"/>
       <c r="Z391" s="1"/>
     </row>
-    <row r="392" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A392" s="1"/>
       <c r="B392" s="6"/>
       <c r="C392" s="7"/>
@@ -12255,7 +13152,7 @@
       <c r="Y392" s="1"/>
       <c r="Z392" s="1"/>
     </row>
-    <row r="393" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A393" s="1"/>
       <c r="B393" s="6"/>
       <c r="C393" s="7"/>
@@ -12283,7 +13180,7 @@
       <c r="Y393" s="1"/>
       <c r="Z393" s="1"/>
     </row>
-    <row r="394" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A394" s="1"/>
       <c r="B394" s="6"/>
       <c r="C394" s="7"/>
@@ -12311,7 +13208,7 @@
       <c r="Y394" s="1"/>
       <c r="Z394" s="1"/>
     </row>
-    <row r="395" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A395" s="1"/>
       <c r="B395" s="6"/>
       <c r="C395" s="7"/>
@@ -12339,7 +13236,7 @@
       <c r="Y395" s="1"/>
       <c r="Z395" s="1"/>
     </row>
-    <row r="396" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A396" s="1"/>
       <c r="B396" s="6"/>
       <c r="C396" s="7"/>
@@ -12367,7 +13264,7 @@
       <c r="Y396" s="1"/>
       <c r="Z396" s="1"/>
     </row>
-    <row r="397" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A397" s="1"/>
       <c r="B397" s="6"/>
       <c r="C397" s="7"/>
@@ -12395,7 +13292,7 @@
       <c r="Y397" s="1"/>
       <c r="Z397" s="1"/>
     </row>
-    <row r="398" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A398" s="1"/>
       <c r="B398" s="6"/>
       <c r="C398" s="7"/>
@@ -12423,7 +13320,7 @@
       <c r="Y398" s="1"/>
       <c r="Z398" s="1"/>
     </row>
-    <row r="399" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A399" s="1"/>
       <c r="B399" s="6"/>
       <c r="C399" s="7"/>
@@ -12451,7 +13348,7 @@
       <c r="Y399" s="1"/>
       <c r="Z399" s="1"/>
     </row>
-    <row r="400" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A400" s="1"/>
       <c r="B400" s="6"/>
       <c r="C400" s="7"/>
@@ -12479,7 +13376,7 @@
       <c r="Y400" s="1"/>
       <c r="Z400" s="1"/>
     </row>
-    <row r="401" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A401" s="1"/>
       <c r="B401" s="6"/>
       <c r="C401" s="7"/>
@@ -12507,7 +13404,7 @@
       <c r="Y401" s="1"/>
       <c r="Z401" s="1"/>
     </row>
-    <row r="402" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A402" s="1"/>
       <c r="B402" s="6"/>
       <c r="C402" s="7"/>
@@ -12535,7 +13432,7 @@
       <c r="Y402" s="1"/>
       <c r="Z402" s="1"/>
     </row>
-    <row r="403" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A403" s="1"/>
       <c r="B403" s="6"/>
       <c r="C403" s="7"/>
@@ -12563,7 +13460,7 @@
       <c r="Y403" s="1"/>
       <c r="Z403" s="1"/>
     </row>
-    <row r="404" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A404" s="1"/>
       <c r="B404" s="6"/>
       <c r="C404" s="7"/>
@@ -12591,7 +13488,7 @@
       <c r="Y404" s="1"/>
       <c r="Z404" s="1"/>
     </row>
-    <row r="405" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A405" s="1"/>
       <c r="B405" s="6"/>
       <c r="C405" s="7"/>
@@ -12619,7 +13516,7 @@
       <c r="Y405" s="1"/>
       <c r="Z405" s="1"/>
     </row>
-    <row r="406" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A406" s="1"/>
       <c r="B406" s="6"/>
       <c r="C406" s="7"/>
@@ -12647,7 +13544,7 @@
       <c r="Y406" s="1"/>
       <c r="Z406" s="1"/>
     </row>
-    <row r="407" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A407" s="1"/>
       <c r="B407" s="6"/>
       <c r="C407" s="7"/>
@@ -12675,7 +13572,7 @@
       <c r="Y407" s="1"/>
       <c r="Z407" s="1"/>
     </row>
-    <row r="408" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A408" s="1"/>
       <c r="B408" s="6"/>
       <c r="C408" s="7"/>
@@ -12703,7 +13600,7 @@
       <c r="Y408" s="1"/>
       <c r="Z408" s="1"/>
     </row>
-    <row r="409" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A409" s="1"/>
       <c r="B409" s="6"/>
       <c r="C409" s="7"/>
@@ -12731,7 +13628,7 @@
       <c r="Y409" s="1"/>
       <c r="Z409" s="1"/>
     </row>
-    <row r="410" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A410" s="1"/>
       <c r="B410" s="6"/>
       <c r="C410" s="7"/>
@@ -12759,7 +13656,7 @@
       <c r="Y410" s="1"/>
       <c r="Z410" s="1"/>
     </row>
-    <row r="411" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A411" s="1"/>
       <c r="B411" s="6"/>
       <c r="C411" s="7"/>
@@ -12787,7 +13684,7 @@
       <c r="Y411" s="1"/>
       <c r="Z411" s="1"/>
     </row>
-    <row r="412" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A412" s="1"/>
       <c r="B412" s="6"/>
       <c r="C412" s="7"/>
@@ -12815,7 +13712,7 @@
       <c r="Y412" s="1"/>
       <c r="Z412" s="1"/>
     </row>
-    <row r="413" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A413" s="1"/>
       <c r="B413" s="6"/>
       <c r="C413" s="7"/>
@@ -12843,7 +13740,7 @@
       <c r="Y413" s="1"/>
       <c r="Z413" s="1"/>
     </row>
-    <row r="414" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A414" s="1"/>
       <c r="B414" s="6"/>
       <c r="C414" s="7"/>
@@ -12871,7 +13768,7 @@
       <c r="Y414" s="1"/>
       <c r="Z414" s="1"/>
     </row>
-    <row r="415" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A415" s="1"/>
       <c r="B415" s="6"/>
       <c r="C415" s="7"/>
@@ -12899,7 +13796,7 @@
       <c r="Y415" s="1"/>
       <c r="Z415" s="1"/>
     </row>
-    <row r="416" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A416" s="1"/>
       <c r="B416" s="6"/>
       <c r="C416" s="7"/>
@@ -12927,7 +13824,7 @@
       <c r="Y416" s="1"/>
       <c r="Z416" s="1"/>
     </row>
-    <row r="417" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A417" s="1"/>
       <c r="B417" s="6"/>
       <c r="C417" s="7"/>
@@ -12955,7 +13852,7 @@
       <c r="Y417" s="1"/>
       <c r="Z417" s="1"/>
     </row>
-    <row r="418" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A418" s="1"/>
       <c r="B418" s="6"/>
       <c r="C418" s="7"/>
@@ -12983,7 +13880,7 @@
       <c r="Y418" s="1"/>
       <c r="Z418" s="1"/>
     </row>
-    <row r="419" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A419" s="1"/>
       <c r="B419" s="6"/>
       <c r="C419" s="7"/>
@@ -13011,7 +13908,7 @@
       <c r="Y419" s="1"/>
       <c r="Z419" s="1"/>
     </row>
-    <row r="420" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A420" s="1"/>
       <c r="B420" s="6"/>
       <c r="C420" s="7"/>
@@ -13039,7 +13936,7 @@
       <c r="Y420" s="1"/>
       <c r="Z420" s="1"/>
     </row>
-    <row r="421" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A421" s="1"/>
       <c r="B421" s="6"/>
       <c r="C421" s="7"/>
@@ -13067,7 +13964,7 @@
       <c r="Y421" s="1"/>
       <c r="Z421" s="1"/>
     </row>
-    <row r="422" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A422" s="1"/>
       <c r="B422" s="6"/>
       <c r="C422" s="7"/>
@@ -13095,7 +13992,7 @@
       <c r="Y422" s="1"/>
       <c r="Z422" s="1"/>
     </row>
-    <row r="423" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A423" s="1"/>
       <c r="B423" s="6"/>
       <c r="C423" s="7"/>
@@ -13123,7 +14020,7 @@
       <c r="Y423" s="1"/>
       <c r="Z423" s="1"/>
     </row>
-    <row r="424" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A424" s="1"/>
       <c r="B424" s="6"/>
       <c r="C424" s="7"/>
@@ -13151,7 +14048,7 @@
       <c r="Y424" s="1"/>
       <c r="Z424" s="1"/>
     </row>
-    <row r="425" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A425" s="1"/>
       <c r="B425" s="6"/>
       <c r="C425" s="7"/>
@@ -13179,7 +14076,7 @@
       <c r="Y425" s="1"/>
       <c r="Z425" s="1"/>
     </row>
-    <row r="426" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A426" s="1"/>
       <c r="B426" s="6"/>
       <c r="C426" s="7"/>
@@ -13207,7 +14104,7 @@
       <c r="Y426" s="1"/>
       <c r="Z426" s="1"/>
     </row>
-    <row r="427" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A427" s="1"/>
       <c r="B427" s="6"/>
       <c r="C427" s="7"/>
@@ -13235,7 +14132,7 @@
       <c r="Y427" s="1"/>
       <c r="Z427" s="1"/>
     </row>
-    <row r="428" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A428" s="1"/>
       <c r="B428" s="6"/>
       <c r="C428" s="7"/>
@@ -13263,7 +14160,7 @@
       <c r="Y428" s="1"/>
       <c r="Z428" s="1"/>
     </row>
-    <row r="429" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A429" s="1"/>
       <c r="B429" s="6"/>
       <c r="C429" s="7"/>
@@ -13291,7 +14188,7 @@
       <c r="Y429" s="1"/>
       <c r="Z429" s="1"/>
     </row>
-    <row r="430" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A430" s="1"/>
       <c r="B430" s="6"/>
       <c r="C430" s="7"/>
@@ -13319,7 +14216,7 @@
       <c r="Y430" s="1"/>
       <c r="Z430" s="1"/>
     </row>
-    <row r="431" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A431" s="1"/>
       <c r="B431" s="6"/>
       <c r="C431" s="7"/>
@@ -13347,7 +14244,7 @@
       <c r="Y431" s="1"/>
       <c r="Z431" s="1"/>
     </row>
-    <row r="432" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A432" s="1"/>
       <c r="B432" s="6"/>
       <c r="C432" s="7"/>
@@ -13375,7 +14272,7 @@
       <c r="Y432" s="1"/>
       <c r="Z432" s="1"/>
     </row>
-    <row r="433" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A433" s="1"/>
       <c r="B433" s="6"/>
       <c r="C433" s="7"/>
@@ -13403,7 +14300,7 @@
       <c r="Y433" s="1"/>
       <c r="Z433" s="1"/>
     </row>
-    <row r="434" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A434" s="1"/>
       <c r="B434" s="6"/>
       <c r="C434" s="7"/>
@@ -13431,7 +14328,7 @@
       <c r="Y434" s="1"/>
       <c r="Z434" s="1"/>
     </row>
-    <row r="435" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A435" s="1"/>
       <c r="B435" s="6"/>
       <c r="C435" s="7"/>
@@ -13459,7 +14356,7 @@
       <c r="Y435" s="1"/>
       <c r="Z435" s="1"/>
     </row>
-    <row r="436" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A436" s="1"/>
       <c r="B436" s="6"/>
       <c r="C436" s="7"/>
@@ -13487,7 +14384,7 @@
       <c r="Y436" s="1"/>
       <c r="Z436" s="1"/>
     </row>
-    <row r="437" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A437" s="1"/>
       <c r="B437" s="6"/>
       <c r="C437" s="7"/>
@@ -13515,7 +14412,7 @@
       <c r="Y437" s="1"/>
       <c r="Z437" s="1"/>
     </row>
-    <row r="438" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A438" s="1"/>
       <c r="B438" s="6"/>
       <c r="C438" s="7"/>
@@ -13543,7 +14440,7 @@
       <c r="Y438" s="1"/>
       <c r="Z438" s="1"/>
     </row>
-    <row r="439" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A439" s="1"/>
       <c r="B439" s="6"/>
       <c r="C439" s="7"/>
@@ -13571,7 +14468,7 @@
       <c r="Y439" s="1"/>
       <c r="Z439" s="1"/>
     </row>
-    <row r="440" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A440" s="1"/>
       <c r="B440" s="6"/>
       <c r="C440" s="7"/>
@@ -13599,7 +14496,7 @@
       <c r="Y440" s="1"/>
       <c r="Z440" s="1"/>
     </row>
-    <row r="441" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A441" s="1"/>
       <c r="B441" s="6"/>
       <c r="C441" s="7"/>
@@ -13627,7 +14524,7 @@
       <c r="Y441" s="1"/>
       <c r="Z441" s="1"/>
     </row>
-    <row r="442" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A442" s="1"/>
       <c r="B442" s="6"/>
       <c r="C442" s="7"/>
@@ -13655,7 +14552,7 @@
       <c r="Y442" s="1"/>
       <c r="Z442" s="1"/>
     </row>
-    <row r="443" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A443" s="1"/>
       <c r="B443" s="6"/>
       <c r="C443" s="7"/>
@@ -13683,7 +14580,7 @@
       <c r="Y443" s="1"/>
       <c r="Z443" s="1"/>
     </row>
-    <row r="444" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A444" s="1"/>
       <c r="B444" s="6"/>
       <c r="C444" s="7"/>
@@ -13711,7 +14608,7 @@
       <c r="Y444" s="1"/>
       <c r="Z444" s="1"/>
     </row>
-    <row r="445" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A445" s="1"/>
       <c r="B445" s="6"/>
       <c r="C445" s="7"/>
@@ -13739,7 +14636,7 @@
       <c r="Y445" s="1"/>
       <c r="Z445" s="1"/>
     </row>
-    <row r="446" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A446" s="1"/>
       <c r="B446" s="6"/>
       <c r="C446" s="7"/>
@@ -13767,7 +14664,7 @@
       <c r="Y446" s="1"/>
       <c r="Z446" s="1"/>
     </row>
-    <row r="447" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A447" s="1"/>
       <c r="B447" s="6"/>
       <c r="C447" s="7"/>
@@ -13795,7 +14692,7 @@
       <c r="Y447" s="1"/>
       <c r="Z447" s="1"/>
     </row>
-    <row r="448" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A448" s="1"/>
       <c r="B448" s="6"/>
       <c r="C448" s="7"/>
@@ -13823,7 +14720,7 @@
       <c r="Y448" s="1"/>
       <c r="Z448" s="1"/>
     </row>
-    <row r="449" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A449" s="1"/>
       <c r="B449" s="6"/>
       <c r="C449" s="7"/>
@@ -13851,7 +14748,7 @@
       <c r="Y449" s="1"/>
       <c r="Z449" s="1"/>
     </row>
-    <row r="450" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A450" s="1"/>
       <c r="B450" s="6"/>
       <c r="C450" s="7"/>
@@ -13879,7 +14776,7 @@
       <c r="Y450" s="1"/>
       <c r="Z450" s="1"/>
     </row>
-    <row r="451" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A451" s="1"/>
       <c r="B451" s="6"/>
       <c r="C451" s="7"/>
@@ -13907,7 +14804,7 @@
       <c r="Y451" s="1"/>
       <c r="Z451" s="1"/>
     </row>
-    <row r="452" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A452" s="1"/>
       <c r="B452" s="6"/>
       <c r="C452" s="7"/>
@@ -13935,7 +14832,7 @@
       <c r="Y452" s="1"/>
       <c r="Z452" s="1"/>
     </row>
-    <row r="453" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A453" s="1"/>
       <c r="B453" s="6"/>
       <c r="C453" s="7"/>
@@ -13963,7 +14860,7 @@
       <c r="Y453" s="1"/>
       <c r="Z453" s="1"/>
     </row>
-    <row r="454" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A454" s="1"/>
       <c r="B454" s="6"/>
       <c r="C454" s="7"/>
@@ -13991,7 +14888,7 @@
       <c r="Y454" s="1"/>
       <c r="Z454" s="1"/>
     </row>
-    <row r="455" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A455" s="1"/>
       <c r="B455" s="6"/>
       <c r="C455" s="7"/>
@@ -14019,7 +14916,7 @@
       <c r="Y455" s="1"/>
       <c r="Z455" s="1"/>
     </row>
-    <row r="456" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A456" s="1"/>
       <c r="B456" s="6"/>
       <c r="C456" s="7"/>
@@ -14047,7 +14944,7 @@
       <c r="Y456" s="1"/>
       <c r="Z456" s="1"/>
     </row>
-    <row r="457" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A457" s="1"/>
       <c r="B457" s="6"/>
       <c r="C457" s="7"/>
@@ -14075,7 +14972,7 @@
       <c r="Y457" s="1"/>
       <c r="Z457" s="1"/>
     </row>
-    <row r="458" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A458" s="1"/>
       <c r="B458" s="6"/>
       <c r="C458" s="7"/>
@@ -14103,7 +15000,7 @@
       <c r="Y458" s="1"/>
       <c r="Z458" s="1"/>
     </row>
-    <row r="459" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A459" s="1"/>
       <c r="B459" s="6"/>
       <c r="C459" s="7"/>
@@ -14131,7 +15028,7 @@
       <c r="Y459" s="1"/>
       <c r="Z459" s="1"/>
     </row>
-    <row r="460" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A460" s="1"/>
       <c r="B460" s="6"/>
       <c r="C460" s="7"/>
@@ -14159,7 +15056,7 @@
       <c r="Y460" s="1"/>
       <c r="Z460" s="1"/>
     </row>
-    <row r="461" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A461" s="1"/>
       <c r="B461" s="6"/>
       <c r="C461" s="7"/>
@@ -14187,7 +15084,7 @@
       <c r="Y461" s="1"/>
       <c r="Z461" s="1"/>
     </row>
-    <row r="462" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A462" s="1"/>
       <c r="B462" s="6"/>
       <c r="C462" s="7"/>
@@ -14215,7 +15112,7 @@
       <c r="Y462" s="1"/>
       <c r="Z462" s="1"/>
     </row>
-    <row r="463" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A463" s="1"/>
       <c r="B463" s="6"/>
       <c r="C463" s="7"/>
@@ -14243,7 +15140,7 @@
       <c r="Y463" s="1"/>
       <c r="Z463" s="1"/>
     </row>
-    <row r="464" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A464" s="1"/>
       <c r="B464" s="6"/>
       <c r="C464" s="7"/>
@@ -14271,7 +15168,7 @@
       <c r="Y464" s="1"/>
       <c r="Z464" s="1"/>
     </row>
-    <row r="465" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A465" s="1"/>
       <c r="B465" s="6"/>
       <c r="C465" s="7"/>
@@ -14299,7 +15196,7 @@
       <c r="Y465" s="1"/>
       <c r="Z465" s="1"/>
     </row>
-    <row r="466" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A466" s="1"/>
       <c r="B466" s="6"/>
       <c r="C466" s="7"/>
@@ -14327,7 +15224,7 @@
       <c r="Y466" s="1"/>
       <c r="Z466" s="1"/>
     </row>
-    <row r="467" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A467" s="1"/>
       <c r="B467" s="6"/>
       <c r="C467" s="7"/>
@@ -14355,7 +15252,7 @@
       <c r="Y467" s="1"/>
       <c r="Z467" s="1"/>
     </row>
-    <row r="468" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A468" s="1"/>
       <c r="B468" s="6"/>
       <c r="C468" s="7"/>
@@ -14383,7 +15280,7 @@
       <c r="Y468" s="1"/>
       <c r="Z468" s="1"/>
     </row>
-    <row r="469" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A469" s="1"/>
       <c r="B469" s="6"/>
       <c r="C469" s="7"/>
@@ -14411,7 +15308,7 @@
       <c r="Y469" s="1"/>
       <c r="Z469" s="1"/>
     </row>
-    <row r="470" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A470" s="1"/>
       <c r="B470" s="6"/>
       <c r="C470" s="7"/>
@@ -14439,7 +15336,7 @@
       <c r="Y470" s="1"/>
       <c r="Z470" s="1"/>
     </row>
-    <row r="471" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A471" s="1"/>
       <c r="B471" s="6"/>
       <c r="C471" s="7"/>
@@ -14467,7 +15364,7 @@
       <c r="Y471" s="1"/>
       <c r="Z471" s="1"/>
     </row>
-    <row r="472" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A472" s="1"/>
       <c r="B472" s="6"/>
       <c r="C472" s="7"/>
@@ -14495,7 +15392,7 @@
       <c r="Y472" s="1"/>
       <c r="Z472" s="1"/>
     </row>
-    <row r="473" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A473" s="1"/>
       <c r="B473" s="6"/>
       <c r="C473" s="7"/>
@@ -14523,7 +15420,7 @@
       <c r="Y473" s="1"/>
       <c r="Z473" s="1"/>
     </row>
-    <row r="474" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A474" s="1"/>
       <c r="B474" s="6"/>
       <c r="C474" s="7"/>
@@ -14551,7 +15448,7 @@
       <c r="Y474" s="1"/>
       <c r="Z474" s="1"/>
     </row>
-    <row r="475" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A475" s="1"/>
       <c r="B475" s="6"/>
       <c r="C475" s="7"/>
@@ -14579,7 +15476,7 @@
       <c r="Y475" s="1"/>
       <c r="Z475" s="1"/>
     </row>
-    <row r="476" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A476" s="1"/>
       <c r="B476" s="6"/>
       <c r="C476" s="7"/>
@@ -14607,7 +15504,7 @@
       <c r="Y476" s="1"/>
       <c r="Z476" s="1"/>
     </row>
-    <row r="477" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A477" s="1"/>
       <c r="B477" s="6"/>
       <c r="C477" s="7"/>
@@ -14635,7 +15532,7 @@
       <c r="Y477" s="1"/>
       <c r="Z477" s="1"/>
     </row>
-    <row r="478" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A478" s="1"/>
       <c r="B478" s="6"/>
       <c r="C478" s="7"/>
@@ -14663,7 +15560,7 @@
       <c r="Y478" s="1"/>
       <c r="Z478" s="1"/>
     </row>
-    <row r="479" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A479" s="1"/>
       <c r="B479" s="6"/>
       <c r="C479" s="7"/>
@@ -14691,7 +15588,7 @@
       <c r="Y479" s="1"/>
       <c r="Z479" s="1"/>
     </row>
-    <row r="480" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A480" s="1"/>
       <c r="B480" s="6"/>
       <c r="C480" s="7"/>
@@ -14719,7 +15616,7 @@
       <c r="Y480" s="1"/>
       <c r="Z480" s="1"/>
     </row>
-    <row r="481" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A481" s="1"/>
       <c r="B481" s="6"/>
       <c r="C481" s="7"/>
@@ -14747,7 +15644,7 @@
       <c r="Y481" s="1"/>
       <c r="Z481" s="1"/>
     </row>
-    <row r="482" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A482" s="1"/>
       <c r="B482" s="6"/>
       <c r="C482" s="7"/>
@@ -14775,7 +15672,7 @@
       <c r="Y482" s="1"/>
       <c r="Z482" s="1"/>
     </row>
-    <row r="483" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A483" s="1"/>
       <c r="B483" s="6"/>
       <c r="C483" s="7"/>
@@ -14803,7 +15700,7 @@
       <c r="Y483" s="1"/>
       <c r="Z483" s="1"/>
     </row>
-    <row r="484" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A484" s="1"/>
       <c r="B484" s="6"/>
       <c r="C484" s="7"/>
@@ -14831,7 +15728,7 @@
       <c r="Y484" s="1"/>
       <c r="Z484" s="1"/>
     </row>
-    <row r="485" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A485" s="1"/>
       <c r="B485" s="6"/>
       <c r="C485" s="7"/>
@@ -14859,7 +15756,7 @@
       <c r="Y485" s="1"/>
       <c r="Z485" s="1"/>
     </row>
-    <row r="486" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A486" s="1"/>
       <c r="B486" s="6"/>
       <c r="C486" s="7"/>
@@ -14887,7 +15784,7 @@
       <c r="Y486" s="1"/>
       <c r="Z486" s="1"/>
     </row>
-    <row r="487" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A487" s="1"/>
       <c r="B487" s="6"/>
       <c r="C487" s="7"/>
@@ -14915,7 +15812,7 @@
       <c r="Y487" s="1"/>
       <c r="Z487" s="1"/>
     </row>
-    <row r="488" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A488" s="1"/>
       <c r="B488" s="6"/>
       <c r="C488" s="7"/>
@@ -14943,7 +15840,7 @@
       <c r="Y488" s="1"/>
       <c r="Z488" s="1"/>
     </row>
-    <row r="489" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A489" s="1"/>
       <c r="B489" s="6"/>
       <c r="C489" s="7"/>
@@ -14971,7 +15868,7 @@
       <c r="Y489" s="1"/>
       <c r="Z489" s="1"/>
     </row>
-    <row r="490" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A490" s="1"/>
       <c r="B490" s="6"/>
       <c r="C490" s="7"/>
@@ -14999,7 +15896,7 @@
       <c r="Y490" s="1"/>
       <c r="Z490" s="1"/>
     </row>
-    <row r="491" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A491" s="1"/>
       <c r="B491" s="6"/>
       <c r="C491" s="7"/>
@@ -15027,7 +15924,7 @@
       <c r="Y491" s="1"/>
       <c r="Z491" s="1"/>
     </row>
-    <row r="492" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A492" s="1"/>
       <c r="B492" s="6"/>
       <c r="C492" s="7"/>
@@ -15055,7 +15952,7 @@
       <c r="Y492" s="1"/>
       <c r="Z492" s="1"/>
     </row>
-    <row r="493" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A493" s="1"/>
       <c r="B493" s="6"/>
       <c r="C493" s="7"/>
@@ -15083,7 +15980,7 @@
       <c r="Y493" s="1"/>
       <c r="Z493" s="1"/>
     </row>
-    <row r="494" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A494" s="1"/>
       <c r="B494" s="6"/>
       <c r="C494" s="7"/>
@@ -15111,7 +16008,7 @@
       <c r="Y494" s="1"/>
       <c r="Z494" s="1"/>
     </row>
-    <row r="495" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A495" s="1"/>
       <c r="B495" s="6"/>
       <c r="C495" s="7"/>
@@ -15139,7 +16036,7 @@
       <c r="Y495" s="1"/>
       <c r="Z495" s="1"/>
     </row>
-    <row r="496" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A496" s="1"/>
       <c r="B496" s="6"/>
       <c r="C496" s="7"/>
@@ -15167,7 +16064,7 @@
       <c r="Y496" s="1"/>
       <c r="Z496" s="1"/>
     </row>
-    <row r="497" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A497" s="1"/>
       <c r="B497" s="6"/>
       <c r="C497" s="7"/>
@@ -15195,7 +16092,7 @@
       <c r="Y497" s="1"/>
       <c r="Z497" s="1"/>
     </row>
-    <row r="498" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A498" s="1"/>
       <c r="B498" s="6"/>
       <c r="C498" s="7"/>
@@ -15223,7 +16120,7 @@
       <c r="Y498" s="1"/>
       <c r="Z498" s="1"/>
     </row>
-    <row r="499" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A499" s="1"/>
       <c r="B499" s="6"/>
       <c r="C499" s="7"/>
@@ -15251,7 +16148,7 @@
       <c r="Y499" s="1"/>
       <c r="Z499" s="1"/>
     </row>
-    <row r="500" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A500" s="1"/>
       <c r="B500" s="6"/>
       <c r="C500" s="7"/>
@@ -15279,7 +16176,7 @@
       <c r="Y500" s="1"/>
       <c r="Z500" s="1"/>
     </row>
-    <row r="501" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A501" s="1"/>
       <c r="B501" s="6"/>
       <c r="C501" s="7"/>
@@ -15307,7 +16204,7 @@
       <c r="Y501" s="1"/>
       <c r="Z501" s="1"/>
     </row>
-    <row r="502" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A502" s="1"/>
       <c r="B502" s="6"/>
       <c r="C502" s="7"/>
@@ -15335,7 +16232,7 @@
       <c r="Y502" s="1"/>
       <c r="Z502" s="1"/>
     </row>
-    <row r="503" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A503" s="1"/>
       <c r="B503" s="6"/>
       <c r="C503" s="7"/>
@@ -15363,7 +16260,7 @@
       <c r="Y503" s="1"/>
       <c r="Z503" s="1"/>
     </row>
-    <row r="504" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A504" s="1"/>
       <c r="B504" s="6"/>
       <c r="C504" s="7"/>
@@ -15391,7 +16288,7 @@
       <c r="Y504" s="1"/>
       <c r="Z504" s="1"/>
     </row>
-    <row r="505" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A505" s="1"/>
       <c r="B505" s="6"/>
       <c r="C505" s="7"/>
@@ -15419,7 +16316,7 @@
       <c r="Y505" s="1"/>
       <c r="Z505" s="1"/>
     </row>
-    <row r="506" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A506" s="1"/>
       <c r="B506" s="6"/>
       <c r="C506" s="7"/>
@@ -15447,7 +16344,7 @@
       <c r="Y506" s="1"/>
       <c r="Z506" s="1"/>
     </row>
-    <row r="507" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A507" s="1"/>
       <c r="B507" s="6"/>
       <c r="C507" s="7"/>
@@ -15475,7 +16372,7 @@
       <c r="Y507" s="1"/>
       <c r="Z507" s="1"/>
     </row>
-    <row r="508" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A508" s="1"/>
       <c r="B508" s="6"/>
       <c r="C508" s="7"/>
@@ -15503,7 +16400,7 @@
       <c r="Y508" s="1"/>
       <c r="Z508" s="1"/>
     </row>
-    <row r="509" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A509" s="1"/>
       <c r="B509" s="6"/>
       <c r="C509" s="7"/>
@@ -15531,7 +16428,7 @@
       <c r="Y509" s="1"/>
       <c r="Z509" s="1"/>
     </row>
-    <row r="510" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A510" s="1"/>
       <c r="B510" s="6"/>
       <c r="C510" s="7"/>
@@ -15559,7 +16456,7 @@
       <c r="Y510" s="1"/>
       <c r="Z510" s="1"/>
     </row>
-    <row r="511" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A511" s="1"/>
       <c r="B511" s="6"/>
       <c r="C511" s="7"/>
@@ -15587,7 +16484,7 @@
       <c r="Y511" s="1"/>
       <c r="Z511" s="1"/>
     </row>
-    <row r="512" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A512" s="1"/>
       <c r="B512" s="6"/>
       <c r="C512" s="7"/>
@@ -15615,7 +16512,7 @@
       <c r="Y512" s="1"/>
       <c r="Z512" s="1"/>
     </row>
-    <row r="513" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A513" s="1"/>
       <c r="B513" s="6"/>
       <c r="C513" s="7"/>
@@ -15643,7 +16540,7 @@
       <c r="Y513" s="1"/>
       <c r="Z513" s="1"/>
     </row>
-    <row r="514" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A514" s="1"/>
       <c r="B514" s="6"/>
       <c r="C514" s="7"/>
@@ -15671,7 +16568,7 @@
       <c r="Y514" s="1"/>
       <c r="Z514" s="1"/>
     </row>
-    <row r="515" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A515" s="1"/>
       <c r="B515" s="6"/>
       <c r="C515" s="7"/>
@@ -15699,7 +16596,7 @@
       <c r="Y515" s="1"/>
       <c r="Z515" s="1"/>
     </row>
-    <row r="516" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A516" s="1"/>
       <c r="B516" s="6"/>
       <c r="C516" s="7"/>
@@ -15727,7 +16624,7 @@
       <c r="Y516" s="1"/>
       <c r="Z516" s="1"/>
     </row>
-    <row r="517" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A517" s="1"/>
       <c r="B517" s="6"/>
       <c r="C517" s="7"/>
@@ -15755,7 +16652,7 @@
       <c r="Y517" s="1"/>
       <c r="Z517" s="1"/>
     </row>
-    <row r="518" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A518" s="1"/>
       <c r="B518" s="6"/>
       <c r="C518" s="7"/>
@@ -15783,7 +16680,7 @@
       <c r="Y518" s="1"/>
       <c r="Z518" s="1"/>
     </row>
-    <row r="519" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A519" s="1"/>
       <c r="B519" s="6"/>
       <c r="C519" s="7"/>
@@ -15811,7 +16708,7 @@
       <c r="Y519" s="1"/>
       <c r="Z519" s="1"/>
     </row>
-    <row r="520" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A520" s="1"/>
       <c r="B520" s="6"/>
       <c r="C520" s="7"/>
@@ -15839,7 +16736,7 @@
       <c r="Y520" s="1"/>
       <c r="Z520" s="1"/>
     </row>
-    <row r="521" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A521" s="1"/>
       <c r="B521" s="6"/>
       <c r="C521" s="7"/>
@@ -15867,7 +16764,7 @@
       <c r="Y521" s="1"/>
       <c r="Z521" s="1"/>
     </row>
-    <row r="522" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A522" s="1"/>
       <c r="B522" s="6"/>
       <c r="C522" s="7"/>
@@ -15895,7 +16792,7 @@
       <c r="Y522" s="1"/>
       <c r="Z522" s="1"/>
     </row>
-    <row r="523" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A523" s="1"/>
       <c r="B523" s="6"/>
       <c r="C523" s="7"/>
@@ -15923,7 +16820,7 @@
       <c r="Y523" s="1"/>
       <c r="Z523" s="1"/>
     </row>
-    <row r="524" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A524" s="1"/>
       <c r="B524" s="6"/>
       <c r="C524" s="7"/>
@@ -15951,7 +16848,7 @@
       <c r="Y524" s="1"/>
       <c r="Z524" s="1"/>
     </row>
-    <row r="525" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A525" s="1"/>
       <c r="B525" s="6"/>
       <c r="C525" s="7"/>
@@ -15979,7 +16876,7 @@
       <c r="Y525" s="1"/>
       <c r="Z525" s="1"/>
     </row>
-    <row r="526" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A526" s="1"/>
       <c r="B526" s="6"/>
       <c r="C526" s="7"/>
@@ -16007,7 +16904,7 @@
       <c r="Y526" s="1"/>
       <c r="Z526" s="1"/>
     </row>
-    <row r="527" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A527" s="1"/>
       <c r="B527" s="6"/>
       <c r="C527" s="7"/>
@@ -16035,7 +16932,7 @@
       <c r="Y527" s="1"/>
       <c r="Z527" s="1"/>
     </row>
-    <row r="528" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A528" s="1"/>
       <c r="B528" s="6"/>
       <c r="C528" s="7"/>
@@ -16063,7 +16960,7 @@
       <c r="Y528" s="1"/>
       <c r="Z528" s="1"/>
     </row>
-    <row r="529" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A529" s="1"/>
       <c r="B529" s="6"/>
       <c r="C529" s="7"/>
@@ -16091,7 +16988,7 @@
       <c r="Y529" s="1"/>
       <c r="Z529" s="1"/>
     </row>
-    <row r="530" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A530" s="1"/>
       <c r="B530" s="6"/>
       <c r="C530" s="7"/>
@@ -16119,7 +17016,7 @@
       <c r="Y530" s="1"/>
       <c r="Z530" s="1"/>
     </row>
-    <row r="531" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A531" s="1"/>
       <c r="B531" s="6"/>
       <c r="C531" s="7"/>
@@ -16147,7 +17044,7 @@
       <c r="Y531" s="1"/>
       <c r="Z531" s="1"/>
     </row>
-    <row r="532" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A532" s="1"/>
       <c r="B532" s="6"/>
       <c r="C532" s="7"/>
@@ -16175,7 +17072,7 @@
       <c r="Y532" s="1"/>
       <c r="Z532" s="1"/>
     </row>
-    <row r="533" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A533" s="1"/>
       <c r="B533" s="6"/>
       <c r="C533" s="7"/>
@@ -16203,7 +17100,7 @@
       <c r="Y533" s="1"/>
       <c r="Z533" s="1"/>
     </row>
-    <row r="534" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A534" s="1"/>
       <c r="B534" s="6"/>
       <c r="C534" s="7"/>
@@ -16231,7 +17128,7 @@
       <c r="Y534" s="1"/>
       <c r="Z534" s="1"/>
     </row>
-    <row r="535" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A535" s="1"/>
       <c r="B535" s="6"/>
       <c r="C535" s="7"/>
@@ -16259,7 +17156,7 @@
       <c r="Y535" s="1"/>
       <c r="Z535" s="1"/>
     </row>
-    <row r="536" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A536" s="1"/>
       <c r="B536" s="6"/>
       <c r="C536" s="7"/>
@@ -16287,7 +17184,7 @@
       <c r="Y536" s="1"/>
       <c r="Z536" s="1"/>
     </row>
-    <row r="537" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A537" s="1"/>
       <c r="B537" s="6"/>
       <c r="C537" s="7"/>
@@ -16315,7 +17212,7 @@
       <c r="Y537" s="1"/>
       <c r="Z537" s="1"/>
     </row>
-    <row r="538" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A538" s="1"/>
       <c r="B538" s="6"/>
       <c r="C538" s="7"/>
@@ -16343,7 +17240,7 @@
       <c r="Y538" s="1"/>
       <c r="Z538" s="1"/>
     </row>
-    <row r="539" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A539" s="1"/>
       <c r="B539" s="6"/>
       <c r="C539" s="7"/>
@@ -16371,7 +17268,7 @@
       <c r="Y539" s="1"/>
       <c r="Z539" s="1"/>
     </row>
-    <row r="540" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A540" s="1"/>
       <c r="B540" s="6"/>
       <c r="C540" s="7"/>
@@ -16399,7 +17296,7 @@
       <c r="Y540" s="1"/>
       <c r="Z540" s="1"/>
     </row>
-    <row r="541" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A541" s="1"/>
       <c r="B541" s="6"/>
       <c r="C541" s="7"/>
@@ -16427,7 +17324,7 @@
       <c r="Y541" s="1"/>
       <c r="Z541" s="1"/>
     </row>
-    <row r="542" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A542" s="1"/>
       <c r="B542" s="6"/>
       <c r="C542" s="7"/>
@@ -16455,7 +17352,7 @@
       <c r="Y542" s="1"/>
       <c r="Z542" s="1"/>
     </row>
-    <row r="543" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A543" s="1"/>
       <c r="B543" s="6"/>
       <c r="C543" s="7"/>
@@ -16483,7 +17380,7 @@
       <c r="Y543" s="1"/>
       <c r="Z543" s="1"/>
     </row>
-    <row r="544" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A544" s="1"/>
       <c r="B544" s="6"/>
       <c r="C544" s="7"/>
@@ -16511,7 +17408,7 @@
       <c r="Y544" s="1"/>
       <c r="Z544" s="1"/>
     </row>
-    <row r="545" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A545" s="1"/>
       <c r="B545" s="6"/>
       <c r="C545" s="7"/>
@@ -16539,7 +17436,7 @@
       <c r="Y545" s="1"/>
       <c r="Z545" s="1"/>
     </row>
-    <row r="546" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A546" s="1"/>
       <c r="B546" s="6"/>
       <c r="C546" s="7"/>
@@ -16567,7 +17464,7 @@
       <c r="Y546" s="1"/>
       <c r="Z546" s="1"/>
     </row>
-    <row r="547" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A547" s="1"/>
       <c r="B547" s="6"/>
       <c r="C547" s="7"/>
@@ -16595,7 +17492,7 @@
       <c r="Y547" s="1"/>
       <c r="Z547" s="1"/>
     </row>
-    <row r="548" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A548" s="1"/>
       <c r="B548" s="6"/>
       <c r="C548" s="7"/>
@@ -16623,7 +17520,7 @@
       <c r="Y548" s="1"/>
       <c r="Z548" s="1"/>
     </row>
-    <row r="549" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A549" s="1"/>
       <c r="B549" s="6"/>
       <c r="C549" s="7"/>
@@ -16651,7 +17548,7 @@
       <c r="Y549" s="1"/>
       <c r="Z549" s="1"/>
     </row>
-    <row r="550" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A550" s="1"/>
       <c r="B550" s="6"/>
       <c r="C550" s="7"/>
@@ -16679,7 +17576,7 @@
       <c r="Y550" s="1"/>
       <c r="Z550" s="1"/>
     </row>
-    <row r="551" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A551" s="1"/>
       <c r="B551" s="6"/>
       <c r="C551" s="7"/>
@@ -16707,7 +17604,7 @@
       <c r="Y551" s="1"/>
       <c r="Z551" s="1"/>
     </row>
-    <row r="552" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A552" s="1"/>
       <c r="B552" s="6"/>
       <c r="C552" s="7"/>
@@ -16735,7 +17632,7 @@
       <c r="Y552" s="1"/>
       <c r="Z552" s="1"/>
     </row>
-    <row r="553" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A553" s="1"/>
       <c r="B553" s="6"/>
       <c r="C553" s="7"/>
@@ -16763,7 +17660,7 @@
       <c r="Y553" s="1"/>
       <c r="Z553" s="1"/>
     </row>
-    <row r="554" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A554" s="1"/>
       <c r="B554" s="6"/>
       <c r="C554" s="7"/>
@@ -16791,7 +17688,7 @@
       <c r="Y554" s="1"/>
       <c r="Z554" s="1"/>
     </row>
-    <row r="555" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A555" s="1"/>
       <c r="B555" s="6"/>
       <c r="C555" s="7"/>
@@ -16819,7 +17716,7 @@
       <c r="Y555" s="1"/>
       <c r="Z555" s="1"/>
     </row>
-    <row r="556" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A556" s="1"/>
       <c r="B556" s="6"/>
       <c r="C556" s="7"/>
@@ -16847,7 +17744,7 @@
       <c r="Y556" s="1"/>
       <c r="Z556" s="1"/>
     </row>
-    <row r="557" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A557" s="1"/>
       <c r="B557" s="6"/>
       <c r="C557" s="7"/>
@@ -16875,7 +17772,7 @@
       <c r="Y557" s="1"/>
       <c r="Z557" s="1"/>
     </row>
-    <row r="558" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A558" s="1"/>
       <c r="B558" s="6"/>
       <c r="C558" s="7"/>
@@ -16903,7 +17800,7 @@
       <c r="Y558" s="1"/>
       <c r="Z558" s="1"/>
     </row>
-    <row r="559" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A559" s="1"/>
       <c r="B559" s="6"/>
       <c r="C559" s="7"/>
@@ -16931,7 +17828,7 @@
       <c r="Y559" s="1"/>
       <c r="Z559" s="1"/>
     </row>
-    <row r="560" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A560" s="1"/>
       <c r="B560" s="6"/>
       <c r="C560" s="7"/>
@@ -16959,7 +17856,7 @@
       <c r="Y560" s="1"/>
       <c r="Z560" s="1"/>
     </row>
-    <row r="561" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A561" s="1"/>
       <c r="B561" s="6"/>
       <c r="C561" s="7"/>
@@ -16987,7 +17884,7 @@
       <c r="Y561" s="1"/>
       <c r="Z561" s="1"/>
     </row>
-    <row r="562" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A562" s="1"/>
       <c r="B562" s="6"/>
       <c r="C562" s="7"/>
@@ -17015,7 +17912,7 @@
       <c r="Y562" s="1"/>
       <c r="Z562" s="1"/>
     </row>
-    <row r="563" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A563" s="1"/>
       <c r="B563" s="6"/>
       <c r="C563" s="7"/>
@@ -17043,7 +17940,7 @@
       <c r="Y563" s="1"/>
       <c r="Z563" s="1"/>
     </row>
-    <row r="564" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A564" s="1"/>
       <c r="B564" s="6"/>
       <c r="C564" s="7"/>
@@ -17071,7 +17968,7 @@
       <c r="Y564" s="1"/>
       <c r="Z564" s="1"/>
     </row>
-    <row r="565" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A565" s="1"/>
       <c r="B565" s="6"/>
       <c r="C565" s="7"/>
@@ -17099,7 +17996,7 @@
       <c r="Y565" s="1"/>
       <c r="Z565" s="1"/>
     </row>
-    <row r="566" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A566" s="1"/>
       <c r="B566" s="6"/>
       <c r="C566" s="7"/>
@@ -17127,7 +18024,7 @@
       <c r="Y566" s="1"/>
       <c r="Z566" s="1"/>
     </row>
-    <row r="567" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A567" s="1"/>
       <c r="B567" s="6"/>
       <c r="C567" s="7"/>
@@ -17155,7 +18052,7 @@
       <c r="Y567" s="1"/>
       <c r="Z567" s="1"/>
     </row>
-    <row r="568" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A568" s="1"/>
       <c r="B568" s="6"/>
       <c r="C568" s="7"/>
@@ -17183,7 +18080,7 @@
       <c r="Y568" s="1"/>
       <c r="Z568" s="1"/>
     </row>
-    <row r="569" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A569" s="1"/>
       <c r="B569" s="6"/>
       <c r="C569" s="7"/>
@@ -17211,7 +18108,7 @@
       <c r="Y569" s="1"/>
       <c r="Z569" s="1"/>
     </row>
-    <row r="570" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A570" s="1"/>
       <c r="B570" s="6"/>
       <c r="C570" s="7"/>
@@ -17239,7 +18136,7 @@
       <c r="Y570" s="1"/>
       <c r="Z570" s="1"/>
     </row>
-    <row r="571" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A571" s="1"/>
       <c r="B571" s="6"/>
       <c r="C571" s="7"/>
@@ -17267,7 +18164,7 @@
       <c r="Y571" s="1"/>
       <c r="Z571" s="1"/>
     </row>
-    <row r="572" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A572" s="1"/>
       <c r="B572" s="6"/>
       <c r="C572" s="7"/>
@@ -17295,7 +18192,7 @@
       <c r="Y572" s="1"/>
       <c r="Z572" s="1"/>
     </row>
-    <row r="573" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A573" s="1"/>
       <c r="B573" s="6"/>
       <c r="C573" s="7"/>
@@ -17323,7 +18220,7 @@
       <c r="Y573" s="1"/>
       <c r="Z573" s="1"/>
     </row>
-    <row r="574" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A574" s="1"/>
       <c r="B574" s="6"/>
       <c r="C574" s="7"/>
@@ -17351,7 +18248,7 @@
       <c r="Y574" s="1"/>
       <c r="Z574" s="1"/>
     </row>
-    <row r="575" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A575" s="1"/>
       <c r="B575" s="6"/>
       <c r="C575" s="7"/>
@@ -17379,7 +18276,7 @@
       <c r="Y575" s="1"/>
       <c r="Z575" s="1"/>
     </row>
-    <row r="576" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A576" s="1"/>
       <c r="B576" s="6"/>
       <c r="C576" s="7"/>
@@ -17407,7 +18304,7 @@
       <c r="Y576" s="1"/>
       <c r="Z576" s="1"/>
     </row>
-    <row r="577" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A577" s="1"/>
       <c r="B577" s="6"/>
       <c r="C577" s="7"/>
@@ -17435,7 +18332,7 @@
       <c r="Y577" s="1"/>
       <c r="Z577" s="1"/>
     </row>
-    <row r="578" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A578" s="1"/>
       <c r="B578" s="6"/>
       <c r="C578" s="7"/>
@@ -17463,7 +18360,7 @@
       <c r="Y578" s="1"/>
       <c r="Z578" s="1"/>
     </row>
-    <row r="579" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A579" s="1"/>
       <c r="B579" s="6"/>
       <c r="C579" s="7"/>
@@ -17491,7 +18388,7 @@
       <c r="Y579" s="1"/>
       <c r="Z579" s="1"/>
     </row>
-    <row r="580" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A580" s="1"/>
       <c r="B580" s="6"/>
       <c r="C580" s="7"/>
@@ -17519,7 +18416,7 @@
       <c r="Y580" s="1"/>
       <c r="Z580" s="1"/>
     </row>
-    <row r="581" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A581" s="1"/>
       <c r="B581" s="6"/>
       <c r="C581" s="7"/>
@@ -17547,7 +18444,7 @@
       <c r="Y581" s="1"/>
       <c r="Z581" s="1"/>
     </row>
-    <row r="582" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A582" s="1"/>
       <c r="B582" s="6"/>
       <c r="C582" s="7"/>
@@ -17575,7 +18472,7 @@
       <c r="Y582" s="1"/>
       <c r="Z582" s="1"/>
     </row>
-    <row r="583" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A583" s="1"/>
       <c r="B583" s="6"/>
       <c r="C583" s="7"/>
@@ -17603,7 +18500,7 @@
       <c r="Y583" s="1"/>
       <c r="Z583" s="1"/>
     </row>
-    <row r="584" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A584" s="1"/>
       <c r="B584" s="6"/>
       <c r="C584" s="7"/>
@@ -17631,7 +18528,7 @@
       <c r="Y584" s="1"/>
       <c r="Z584" s="1"/>
     </row>
-    <row r="585" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A585" s="1"/>
       <c r="B585" s="6"/>
       <c r="C585" s="7"/>
@@ -17659,7 +18556,7 @@
       <c r="Y585" s="1"/>
       <c r="Z585" s="1"/>
     </row>
-    <row r="586" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A586" s="1"/>
       <c r="B586" s="6"/>
       <c r="C586" s="7"/>
@@ -17687,7 +18584,7 @@
       <c r="Y586" s="1"/>
       <c r="Z586" s="1"/>
     </row>
-    <row r="587" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A587" s="1"/>
       <c r="B587" s="6"/>
       <c r="C587" s="7"/>
@@ -17715,7 +18612,7 @@
       <c r="Y587" s="1"/>
       <c r="Z587" s="1"/>
     </row>
-    <row r="588" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A588" s="1"/>
       <c r="B588" s="6"/>
       <c r="C588" s="7"/>
@@ -17743,7 +18640,7 @@
       <c r="Y588" s="1"/>
       <c r="Z588" s="1"/>
     </row>
-    <row r="589" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A589" s="1"/>
       <c r="B589" s="6"/>
       <c r="C589" s="7"/>
@@ -17771,7 +18668,7 @@
       <c r="Y589" s="1"/>
       <c r="Z589" s="1"/>
     </row>
-    <row r="590" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A590" s="1"/>
       <c r="B590" s="6"/>
       <c r="C590" s="7"/>
@@ -17799,7 +18696,7 @@
       <c r="Y590" s="1"/>
       <c r="Z590" s="1"/>
     </row>
-    <row r="591" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A591" s="1"/>
       <c r="B591" s="6"/>
       <c r="C591" s="7"/>
@@ -17827,7 +18724,7 @@
       <c r="Y591" s="1"/>
       <c r="Z591" s="1"/>
     </row>
-    <row r="592" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A592" s="1"/>
       <c r="B592" s="6"/>
       <c r="C592" s="7"/>
@@ -17855,7 +18752,7 @@
       <c r="Y592" s="1"/>
       <c r="Z592" s="1"/>
     </row>
-    <row r="593" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A593" s="1"/>
       <c r="B593" s="6"/>
       <c r="C593" s="7"/>
@@ -17883,7 +18780,7 @@
       <c r="Y593" s="1"/>
       <c r="Z593" s="1"/>
     </row>
-    <row r="594" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A594" s="1"/>
       <c r="B594" s="6"/>
       <c r="C594" s="7"/>
@@ -17911,7 +18808,7 @@
       <c r="Y594" s="1"/>
       <c r="Z594" s="1"/>
     </row>
-    <row r="595" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A595" s="1"/>
       <c r="B595" s="6"/>
       <c r="C595" s="7"/>
@@ -17939,7 +18836,7 @@
       <c r="Y595" s="1"/>
       <c r="Z595" s="1"/>
     </row>
-    <row r="596" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A596" s="1"/>
       <c r="B596" s="6"/>
       <c r="C596" s="7"/>
@@ -17967,7 +18864,7 @@
       <c r="Y596" s="1"/>
       <c r="Z596" s="1"/>
     </row>
-    <row r="597" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A597" s="1"/>
       <c r="B597" s="6"/>
       <c r="C597" s="7"/>
@@ -17995,7 +18892,7 @@
       <c r="Y597" s="1"/>
       <c r="Z597" s="1"/>
     </row>
-    <row r="598" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A598" s="1"/>
       <c r="B598" s="6"/>
       <c r="C598" s="7"/>
@@ -18023,7 +18920,7 @@
       <c r="Y598" s="1"/>
       <c r="Z598" s="1"/>
     </row>
-    <row r="599" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A599" s="1"/>
       <c r="B599" s="6"/>
       <c r="C599" s="7"/>
@@ -18051,7 +18948,7 @@
       <c r="Y599" s="1"/>
       <c r="Z599" s="1"/>
     </row>
-    <row r="600" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A600" s="1"/>
       <c r="B600" s="6"/>
       <c r="C600" s="7"/>
@@ -18079,7 +18976,7 @@
       <c r="Y600" s="1"/>
       <c r="Z600" s="1"/>
     </row>
-    <row r="601" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A601" s="1"/>
       <c r="B601" s="6"/>
       <c r="C601" s="7"/>
@@ -18107,7 +19004,7 @@
       <c r="Y601" s="1"/>
       <c r="Z601" s="1"/>
     </row>
-    <row r="602" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A602" s="1"/>
       <c r="B602" s="6"/>
       <c r="C602" s="7"/>
@@ -18135,7 +19032,7 @@
       <c r="Y602" s="1"/>
       <c r="Z602" s="1"/>
     </row>
-    <row r="603" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A603" s="1"/>
       <c r="B603" s="6"/>
       <c r="C603" s="7"/>
@@ -18163,7 +19060,7 @@
       <c r="Y603" s="1"/>
       <c r="Z603" s="1"/>
     </row>
-    <row r="604" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A604" s="1"/>
       <c r="B604" s="6"/>
       <c r="C604" s="7"/>
@@ -18191,7 +19088,7 @@
       <c r="Y604" s="1"/>
       <c r="Z604" s="1"/>
     </row>
-    <row r="605" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A605" s="1"/>
       <c r="B605" s="6"/>
       <c r="C605" s="7"/>
@@ -18219,7 +19116,7 @@
       <c r="Y605" s="1"/>
       <c r="Z605" s="1"/>
     </row>
-    <row r="606" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A606" s="1"/>
       <c r="B606" s="6"/>
       <c r="C606" s="7"/>
@@ -18247,7 +19144,7 @@
       <c r="Y606" s="1"/>
       <c r="Z606" s="1"/>
     </row>
-    <row r="607" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A607" s="1"/>
       <c r="B607" s="6"/>
       <c r="C607" s="7"/>
@@ -18275,7 +19172,7 @@
       <c r="Y607" s="1"/>
       <c r="Z607" s="1"/>
     </row>
-    <row r="608" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A608" s="1"/>
       <c r="B608" s="6"/>
       <c r="C608" s="7"/>
@@ -18303,7 +19200,7 @@
       <c r="Y608" s="1"/>
       <c r="Z608" s="1"/>
     </row>
-    <row r="609" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A609" s="1"/>
       <c r="B609" s="6"/>
       <c r="C609" s="7"/>
@@ -18331,7 +19228,7 @@
       <c r="Y609" s="1"/>
       <c r="Z609" s="1"/>
     </row>
-    <row r="610" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A610" s="1"/>
       <c r="B610" s="6"/>
       <c r="C610" s="7"/>
@@ -18359,7 +19256,7 @@
       <c r="Y610" s="1"/>
       <c r="Z610" s="1"/>
     </row>
-    <row r="611" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A611" s="1"/>
       <c r="B611" s="6"/>
       <c r="C611" s="7"/>
@@ -18387,7 +19284,7 @@
       <c r="Y611" s="1"/>
       <c r="Z611" s="1"/>
     </row>
-    <row r="612" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A612" s="1"/>
       <c r="B612" s="6"/>
       <c r="C612" s="7"/>
@@ -18415,7 +19312,7 @@
       <c r="Y612" s="1"/>
       <c r="Z612" s="1"/>
     </row>
-    <row r="613" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A613" s="1"/>
       <c r="B613" s="6"/>
       <c r="C613" s="7"/>
@@ -18443,7 +19340,7 @@
       <c r="Y613" s="1"/>
       <c r="Z613" s="1"/>
     </row>
-    <row r="614" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A614" s="1"/>
       <c r="B614" s="6"/>
       <c r="C614" s="7"/>
@@ -18471,7 +19368,7 @@
       <c r="Y614" s="1"/>
       <c r="Z614" s="1"/>
     </row>
-    <row r="615" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A615" s="1"/>
       <c r="B615" s="6"/>
       <c r="C615" s="7"/>
@@ -18499,7 +19396,7 @@
       <c r="Y615" s="1"/>
       <c r="Z615" s="1"/>
     </row>
-    <row r="616" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A616" s="1"/>
       <c r="B616" s="6"/>
       <c r="C616" s="7"/>
@@ -18527,7 +19424,7 @@
       <c r="Y616" s="1"/>
       <c r="Z616" s="1"/>
     </row>
-    <row r="617" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A617" s="1"/>
       <c r="B617" s="6"/>
       <c r="C617" s="7"/>
@@ -18555,7 +19452,7 @@
       <c r="Y617" s="1"/>
       <c r="Z617" s="1"/>
     </row>
-    <row r="618" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A618" s="1"/>
       <c r="B618" s="6"/>
       <c r="C618" s="7"/>
@@ -18583,7 +19480,7 @@
       <c r="Y618" s="1"/>
       <c r="Z618" s="1"/>
     </row>
-    <row r="619" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A619" s="1"/>
       <c r="B619" s="6"/>
       <c r="C619" s="7"/>
@@ -18611,7 +19508,7 @@
       <c r="Y619" s="1"/>
       <c r="Z619" s="1"/>
     </row>
-    <row r="620" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A620" s="1"/>
       <c r="B620" s="6"/>
       <c r="C620" s="7"/>
@@ -18639,7 +19536,7 @@
       <c r="Y620" s="1"/>
       <c r="Z620" s="1"/>
     </row>
-    <row r="621" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A621" s="1"/>
       <c r="B621" s="6"/>
       <c r="C621" s="7"/>
@@ -18667,7 +19564,7 @@
       <c r="Y621" s="1"/>
       <c r="Z621" s="1"/>
     </row>
-    <row r="622" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A622" s="1"/>
       <c r="B622" s="6"/>
       <c r="C622" s="7"/>
@@ -18695,7 +19592,7 @@
       <c r="Y622" s="1"/>
       <c r="Z622" s="1"/>
     </row>
-    <row r="623" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A623" s="1"/>
       <c r="B623" s="6"/>
       <c r="C623" s="7"/>
@@ -18723,7 +19620,7 @@
       <c r="Y623" s="1"/>
       <c r="Z623" s="1"/>
     </row>
-    <row r="624" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A624" s="1"/>
       <c r="B624" s="6"/>
       <c r="C624" s="7"/>
@@ -18751,7 +19648,7 @@
       <c r="Y624" s="1"/>
       <c r="Z624" s="1"/>
     </row>
-    <row r="625" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A625" s="1"/>
       <c r="B625" s="6"/>
       <c r="C625" s="7"/>
@@ -18779,7 +19676,7 @@
       <c r="Y625" s="1"/>
       <c r="Z625" s="1"/>
     </row>
-    <row r="626" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A626" s="1"/>
       <c r="B626" s="6"/>
       <c r="C626" s="7"/>
@@ -18807,7 +19704,7 @@
       <c r="Y626" s="1"/>
       <c r="Z626" s="1"/>
     </row>
-    <row r="627" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A627" s="1"/>
       <c r="B627" s="6"/>
       <c r="C627" s="7"/>
@@ -18835,7 +19732,7 @@
       <c r="Y627" s="1"/>
       <c r="Z627" s="1"/>
     </row>
-    <row r="628" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A628" s="1"/>
       <c r="B628" s="6"/>
       <c r="C628" s="7"/>
@@ -18863,7 +19760,7 @@
       <c r="Y628" s="1"/>
       <c r="Z628" s="1"/>
     </row>
-    <row r="629" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A629" s="1"/>
       <c r="B629" s="6"/>
       <c r="C629" s="7"/>
@@ -18891,7 +19788,7 @@
       <c r="Y629" s="1"/>
       <c r="Z629" s="1"/>
     </row>
-    <row r="630" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A630" s="1"/>
       <c r="B630" s="6"/>
       <c r="C630" s="7"/>
@@ -18919,7 +19816,7 @@
       <c r="Y630" s="1"/>
       <c r="Z630" s="1"/>
     </row>
-    <row r="631" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A631" s="1"/>
       <c r="B631" s="6"/>
       <c r="C631" s="7"/>
@@ -18947,7 +19844,7 @@
       <c r="Y631" s="1"/>
       <c r="Z631" s="1"/>
     </row>
-    <row r="632" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A632" s="1"/>
       <c r="B632" s="6"/>
       <c r="C632" s="7"/>
@@ -18975,7 +19872,7 @@
       <c r="Y632" s="1"/>
       <c r="Z632" s="1"/>
     </row>
-    <row r="633" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A633" s="1"/>
       <c r="B633" s="6"/>
       <c r="C633" s="7"/>
@@ -19003,7 +19900,7 @@
       <c r="Y633" s="1"/>
       <c r="Z633" s="1"/>
     </row>
-    <row r="634" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A634" s="1"/>
       <c r="B634" s="6"/>
       <c r="C634" s="7"/>
@@ -19031,7 +19928,7 @@
       <c r="Y634" s="1"/>
       <c r="Z634" s="1"/>
     </row>
-    <row r="635" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A635" s="1"/>
       <c r="B635" s="6"/>
       <c r="C635" s="7"/>
@@ -19059,7 +19956,7 @@
       <c r="Y635" s="1"/>
       <c r="Z635" s="1"/>
     </row>
-    <row r="636" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A636" s="1"/>
       <c r="B636" s="6"/>
       <c r="C636" s="7"/>
@@ -19087,7 +19984,7 @@
       <c r="Y636" s="1"/>
       <c r="Z636" s="1"/>
     </row>
-    <row r="637" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A637" s="1"/>
       <c r="B637" s="6"/>
       <c r="C637" s="7"/>
@@ -19115,7 +20012,7 @@
       <c r="Y637" s="1"/>
       <c r="Z637" s="1"/>
     </row>
-    <row r="638" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A638" s="1"/>
       <c r="B638" s="6"/>
       <c r="C638" s="7"/>
@@ -19143,7 +20040,7 @@
       <c r="Y638" s="1"/>
       <c r="Z638" s="1"/>
     </row>
-    <row r="639" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A639" s="1"/>
       <c r="B639" s="6"/>
       <c r="C639" s="7"/>
@@ -19171,7 +20068,7 @@
       <c r="Y639" s="1"/>
       <c r="Z639" s="1"/>
     </row>
-    <row r="640" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A640" s="1"/>
       <c r="B640" s="6"/>
       <c r="C640" s="7"/>
@@ -19199,7 +20096,7 @@
       <c r="Y640" s="1"/>
       <c r="Z640" s="1"/>
     </row>
-    <row r="641" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A641" s="1"/>
       <c r="B641" s="6"/>
       <c r="C641" s="7"/>
@@ -19227,7 +20124,7 @@
       <c r="Y641" s="1"/>
       <c r="Z641" s="1"/>
     </row>
-    <row r="642" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A642" s="1"/>
       <c r="B642" s="6"/>
       <c r="C642" s="7"/>
@@ -19255,7 +20152,7 @@
       <c r="Y642" s="1"/>
       <c r="Z642" s="1"/>
     </row>
-    <row r="643" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A643" s="1"/>
       <c r="B643" s="6"/>
       <c r="C643" s="7"/>
@@ -19283,7 +20180,7 @@
       <c r="Y643" s="1"/>
       <c r="Z643" s="1"/>
     </row>
-    <row r="644" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A644" s="1"/>
       <c r="B644" s="6"/>
       <c r="C644" s="7"/>
@@ -19311,7 +20208,7 @@
       <c r="Y644" s="1"/>
       <c r="Z644" s="1"/>
     </row>
-    <row r="645" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A645" s="1"/>
       <c r="B645" s="6"/>
       <c r="C645" s="7"/>
@@ -19339,7 +20236,7 @@
       <c r="Y645" s="1"/>
       <c r="Z645" s="1"/>
     </row>
-    <row r="646" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A646" s="1"/>
       <c r="B646" s="6"/>
       <c r="C646" s="7"/>
@@ -19367,7 +20264,7 @@
       <c r="Y646" s="1"/>
       <c r="Z646" s="1"/>
     </row>
-    <row r="647" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A647" s="1"/>
       <c r="B647" s="6"/>
       <c r="C647" s="7"/>
@@ -19395,7 +20292,7 @@
       <c r="Y647" s="1"/>
       <c r="Z647" s="1"/>
     </row>
-    <row r="648" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A648" s="1"/>
       <c r="B648" s="6"/>
       <c r="C648" s="7"/>
@@ -19423,7 +20320,7 @@
       <c r="Y648" s="1"/>
       <c r="Z648" s="1"/>
     </row>
-    <row r="649" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A649" s="1"/>
       <c r="B649" s="6"/>
       <c r="C649" s="7"/>
@@ -19451,7 +20348,7 @@
       <c r="Y649" s="1"/>
       <c r="Z649" s="1"/>
     </row>
-    <row r="650" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A650" s="1"/>
       <c r="B650" s="6"/>
       <c r="C650" s="7"/>
@@ -19479,7 +20376,7 @@
       <c r="Y650" s="1"/>
       <c r="Z650" s="1"/>
     </row>
-    <row r="651" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A651" s="1"/>
       <c r="B651" s="6"/>
       <c r="C651" s="7"/>
@@ -19507,7 +20404,7 @@
       <c r="Y651" s="1"/>
       <c r="Z651" s="1"/>
     </row>
-    <row r="652" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A652" s="1"/>
       <c r="B652" s="6"/>
       <c r="C652" s="7"/>
@@ -19535,7 +20432,7 @@
       <c r="Y652" s="1"/>
       <c r="Z652" s="1"/>
     </row>
-    <row r="653" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A653" s="1"/>
       <c r="B653" s="6"/>
       <c r="C653" s="7"/>
@@ -19563,7 +20460,7 @@
       <c r="Y653" s="1"/>
       <c r="Z653" s="1"/>
     </row>
-    <row r="654" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A654" s="1"/>
       <c r="B654" s="6"/>
       <c r="C654" s="7"/>
@@ -19591,7 +20488,7 @@
       <c r="Y654" s="1"/>
       <c r="Z654" s="1"/>
     </row>
-    <row r="655" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A655" s="1"/>
       <c r="B655" s="6"/>
       <c r="C655" s="7"/>
@@ -19619,7 +20516,7 @@
       <c r="Y655" s="1"/>
       <c r="Z655" s="1"/>
     </row>
-    <row r="656" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A656" s="1"/>
       <c r="B656" s="6"/>
       <c r="C656" s="7"/>
@@ -19647,7 +20544,7 @@
       <c r="Y656" s="1"/>
       <c r="Z656" s="1"/>
     </row>
-    <row r="657" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A657" s="1"/>
       <c r="B657" s="6"/>
       <c r="C657" s="7"/>
@@ -19675,7 +20572,7 @@
       <c r="Y657" s="1"/>
       <c r="Z657" s="1"/>
     </row>
-    <row r="658" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A658" s="1"/>
       <c r="B658" s="6"/>
       <c r="C658" s="7"/>
@@ -19703,7 +20600,7 @@
       <c r="Y658" s="1"/>
       <c r="Z658" s="1"/>
     </row>
-    <row r="659" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A659" s="1"/>
       <c r="B659" s="6"/>
       <c r="C659" s="7"/>
@@ -19731,7 +20628,7 @@
       <c r="Y659" s="1"/>
       <c r="Z659" s="1"/>
     </row>
-    <row r="660" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A660" s="1"/>
       <c r="B660" s="6"/>
       <c r="C660" s="7"/>
@@ -19759,7 +20656,7 @@
       <c r="Y660" s="1"/>
       <c r="Z660" s="1"/>
     </row>
-    <row r="661" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A661" s="1"/>
       <c r="B661" s="6"/>
       <c r="C661" s="7"/>
@@ -19787,7 +20684,7 @@
       <c r="Y661" s="1"/>
       <c r="Z661" s="1"/>
     </row>
-    <row r="662" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A662" s="1"/>
       <c r="B662" s="6"/>
       <c r="C662" s="7"/>
@@ -19815,7 +20712,7 @@
       <c r="Y662" s="1"/>
       <c r="Z662" s="1"/>
     </row>
-    <row r="663" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A663" s="1"/>
       <c r="B663" s="6"/>
       <c r="C663" s="7"/>
@@ -19843,7 +20740,7 @@
       <c r="Y663" s="1"/>
       <c r="Z663" s="1"/>
     </row>
-    <row r="664" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A664" s="1"/>
       <c r="B664" s="6"/>
       <c r="C664" s="7"/>
@@ -19871,7 +20768,7 @@
       <c r="Y664" s="1"/>
       <c r="Z664" s="1"/>
     </row>
-    <row r="665" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A665" s="1"/>
       <c r="B665" s="6"/>
       <c r="C665" s="7"/>
@@ -19899,7 +20796,7 @@
       <c r="Y665" s="1"/>
       <c r="Z665" s="1"/>
     </row>
-    <row r="666" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A666" s="1"/>
       <c r="B666" s="6"/>
       <c r="C666" s="7"/>
@@ -19927,7 +20824,7 @@
       <c r="Y666" s="1"/>
       <c r="Z666" s="1"/>
     </row>
-    <row r="667" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A667" s="1"/>
       <c r="B667" s="6"/>
       <c r="C667" s="7"/>
@@ -19955,7 +20852,7 @@
       <c r="Y667" s="1"/>
       <c r="Z667" s="1"/>
     </row>
-    <row r="668" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A668" s="1"/>
       <c r="B668" s="6"/>
       <c r="C668" s="7"/>
@@ -19983,7 +20880,7 @@
       <c r="Y668" s="1"/>
       <c r="Z668" s="1"/>
     </row>
-    <row r="669" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A669" s="1"/>
       <c r="B669" s="6"/>
       <c r="C669" s="7"/>
@@ -20011,7 +20908,7 @@
       <c r="Y669" s="1"/>
       <c r="Z669" s="1"/>
     </row>
-    <row r="670" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A670" s="1"/>
       <c r="B670" s="6"/>
       <c r="C670" s="7"/>
@@ -20039,7 +20936,7 @@
       <c r="Y670" s="1"/>
       <c r="Z670" s="1"/>
     </row>
-    <row r="671" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A671" s="1"/>
       <c r="B671" s="6"/>
       <c r="C671" s="7"/>
@@ -20067,7 +20964,7 @@
       <c r="Y671" s="1"/>
       <c r="Z671" s="1"/>
     </row>
-    <row r="672" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A672" s="1"/>
       <c r="B672" s="6"/>
       <c r="C672" s="7"/>
@@ -20095,7 +20992,7 @@
       <c r="Y672" s="1"/>
       <c r="Z672" s="1"/>
     </row>
-    <row r="673" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A673" s="1"/>
       <c r="B673" s="6"/>
       <c r="C673" s="7"/>
@@ -20123,7 +21020,7 @@
       <c r="Y673" s="1"/>
       <c r="Z673" s="1"/>
     </row>
-    <row r="674" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A674" s="1"/>
       <c r="B674" s="6"/>
       <c r="C674" s="7"/>
@@ -20151,7 +21048,7 @@
       <c r="Y674" s="1"/>
       <c r="Z674" s="1"/>
     </row>
-    <row r="675" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A675" s="1"/>
       <c r="B675" s="6"/>
       <c r="C675" s="7"/>
@@ -20179,7 +21076,7 @@
       <c r="Y675" s="1"/>
       <c r="Z675" s="1"/>
     </row>
-    <row r="676" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A676" s="1"/>
       <c r="B676" s="6"/>
       <c r="C676" s="7"/>
@@ -20207,7 +21104,7 @@
       <c r="Y676" s="1"/>
       <c r="Z676" s="1"/>
     </row>
-    <row r="677" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A677" s="1"/>
       <c r="B677" s="6"/>
       <c r="C677" s="7"/>
@@ -20235,7 +21132,7 @@
       <c r="Y677" s="1"/>
       <c r="Z677" s="1"/>
     </row>
-    <row r="678" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A678" s="1"/>
       <c r="B678" s="6"/>
       <c r="C678" s="7"/>
@@ -20263,7 +21160,7 @@
       <c r="Y678" s="1"/>
       <c r="Z678" s="1"/>
     </row>
-    <row r="679" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A679" s="1"/>
       <c r="B679" s="6"/>
       <c r="C679" s="7"/>
@@ -20291,7 +21188,7 @@
       <c r="Y679" s="1"/>
       <c r="Z679" s="1"/>
     </row>
-    <row r="680" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A680" s="1"/>
       <c r="B680" s="6"/>
       <c r="C680" s="7"/>
@@ -20319,7 +21216,7 @@
       <c r="Y680" s="1"/>
       <c r="Z680" s="1"/>
     </row>
-    <row r="681" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A681" s="1"/>
       <c r="B681" s="6"/>
       <c r="C681" s="7"/>
@@ -20347,7 +21244,7 @@
       <c r="Y681" s="1"/>
       <c r="Z681" s="1"/>
     </row>
-    <row r="682" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A682" s="1"/>
       <c r="B682" s="6"/>
       <c r="C682" s="7"/>
@@ -20375,7 +21272,7 @@
       <c r="Y682" s="1"/>
       <c r="Z682" s="1"/>
     </row>
-    <row r="683" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A683" s="1"/>
       <c r="B683" s="6"/>
       <c r="C683" s="7"/>
@@ -20403,7 +21300,7 @@
       <c r="Y683" s="1"/>
       <c r="Z683" s="1"/>
     </row>
-    <row r="684" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A684" s="1"/>
       <c r="B684" s="6"/>
       <c r="C684" s="7"/>
@@ -20431,7 +21328,7 @@
       <c r="Y684" s="1"/>
       <c r="Z684" s="1"/>
     </row>
-    <row r="685" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A685" s="1"/>
       <c r="B685" s="6"/>
       <c r="C685" s="7"/>
@@ -20459,7 +21356,7 @@
       <c r="Y685" s="1"/>
       <c r="Z685" s="1"/>
     </row>
-    <row r="686" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A686" s="1"/>
       <c r="B686" s="6"/>
       <c r="C686" s="7"/>
@@ -20487,7 +21384,7 @@
       <c r="Y686" s="1"/>
       <c r="Z686" s="1"/>
     </row>
-    <row r="687" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A687" s="1"/>
       <c r="B687" s="6"/>
       <c r="C687" s="7"/>
@@ -20515,7 +21412,7 @@
       <c r="Y687" s="1"/>
       <c r="Z687" s="1"/>
     </row>
-    <row r="688" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A688" s="1"/>
       <c r="B688" s="6"/>
       <c r="C688" s="7"/>
@@ -20543,7 +21440,7 @@
       <c r="Y688" s="1"/>
       <c r="Z688" s="1"/>
     </row>
-    <row r="689" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A689" s="1"/>
       <c r="B689" s="6"/>
       <c r="C689" s="7"/>
@@ -20571,7 +21468,7 @@
       <c r="Y689" s="1"/>
       <c r="Z689" s="1"/>
     </row>
-    <row r="690" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A690" s="1"/>
       <c r="B690" s="6"/>
       <c r="C690" s="7"/>
@@ -20599,7 +21496,7 @@
       <c r="Y690" s="1"/>
       <c r="Z690" s="1"/>
     </row>
-    <row r="691" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A691" s="1"/>
       <c r="B691" s="6"/>
       <c r="C691" s="7"/>
@@ -20627,7 +21524,7 @@
       <c r="Y691" s="1"/>
       <c r="Z691" s="1"/>
     </row>
-    <row r="692" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A692" s="1"/>
       <c r="B692" s="6"/>
       <c r="C692" s="7"/>
@@ -20655,7 +21552,7 @@
       <c r="Y692" s="1"/>
       <c r="Z692" s="1"/>
     </row>
-    <row r="693" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A693" s="1"/>
       <c r="B693" s="6"/>
       <c r="C693" s="7"/>
@@ -20683,7 +21580,7 @@
       <c r="Y693" s="1"/>
       <c r="Z693" s="1"/>
     </row>
-    <row r="694" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A694" s="1"/>
       <c r="B694" s="6"/>
       <c r="C694" s="7"/>
@@ -20711,7 +21608,7 @@
       <c r="Y694" s="1"/>
       <c r="Z694" s="1"/>
     </row>
-    <row r="695" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A695" s="1"/>
       <c r="B695" s="6"/>
       <c r="C695" s="7"/>
@@ -20739,7 +21636,7 @@
       <c r="Y695" s="1"/>
       <c r="Z695" s="1"/>
     </row>
-    <row r="696" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A696" s="1"/>
       <c r="B696" s="6"/>
       <c r="C696" s="7"/>
@@ -20767,7 +21664,7 @@
       <c r="Y696" s="1"/>
       <c r="Z696" s="1"/>
     </row>
-    <row r="697" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A697" s="1"/>
       <c r="B697" s="6"/>
       <c r="C697" s="7"/>
@@ -20795,7 +21692,7 @@
       <c r="Y697" s="1"/>
       <c r="Z697" s="1"/>
     </row>
-    <row r="698" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A698" s="1"/>
       <c r="B698" s="6"/>
       <c r="C698" s="7"/>
@@ -20823,7 +21720,7 @@
       <c r="Y698" s="1"/>
       <c r="Z698" s="1"/>
     </row>
-    <row r="699" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A699" s="1"/>
       <c r="B699" s="6"/>
       <c r="C699" s="7"/>
@@ -20851,7 +21748,7 @@
       <c r="Y699" s="1"/>
       <c r="Z699" s="1"/>
     </row>
-    <row r="700" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A700" s="1"/>
       <c r="B700" s="6"/>
       <c r="C700" s="7"/>
@@ -20879,7 +21776,7 @@
       <c r="Y700" s="1"/>
       <c r="Z700" s="1"/>
     </row>
-    <row r="701" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A701" s="1"/>
       <c r="B701" s="6"/>
       <c r="C701" s="7"/>
@@ -20907,7 +21804,7 @@
       <c r="Y701" s="1"/>
       <c r="Z701" s="1"/>
     </row>
-    <row r="702" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A702" s="1"/>
       <c r="B702" s="6"/>
       <c r="C702" s="7"/>
@@ -20935,7 +21832,7 @@
       <c r="Y702" s="1"/>
       <c r="Z702" s="1"/>
     </row>
-    <row r="703" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A703" s="1"/>
       <c r="B703" s="6"/>
       <c r="C703" s="7"/>
@@ -20963,7 +21860,7 @@
       <c r="Y703" s="1"/>
       <c r="Z703" s="1"/>
     </row>
-    <row r="704" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A704" s="1"/>
       <c r="B704" s="6"/>
       <c r="C704" s="7"/>
@@ -20991,7 +21888,7 @@
       <c r="Y704" s="1"/>
       <c r="Z704" s="1"/>
     </row>
-    <row r="705" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A705" s="1"/>
       <c r="B705" s="6"/>
       <c r="C705" s="7"/>
@@ -21019,7 +21916,7 @@
       <c r="Y705" s="1"/>
       <c r="Z705" s="1"/>
     </row>
-    <row r="706" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A706" s="1"/>
       <c r="B706" s="6"/>
       <c r="C706" s="7"/>
@@ -21047,7 +21944,7 @@
       <c r="Y706" s="1"/>
       <c r="Z706" s="1"/>
     </row>
-    <row r="707" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A707" s="1"/>
       <c r="B707" s="6"/>
       <c r="C707" s="7"/>
@@ -21075,7 +21972,7 @@
       <c r="Y707" s="1"/>
       <c r="Z707" s="1"/>
     </row>
-    <row r="708" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A708" s="1"/>
       <c r="B708" s="6"/>
       <c r="C708" s="7"/>
@@ -21103,7 +22000,7 @@
       <c r="Y708" s="1"/>
       <c r="Z708" s="1"/>
     </row>
-    <row r="709" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A709" s="1"/>
       <c r="B709" s="6"/>
       <c r="C709" s="7"/>
@@ -21131,7 +22028,7 @@
       <c r="Y709" s="1"/>
       <c r="Z709" s="1"/>
     </row>
-    <row r="710" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A710" s="1"/>
       <c r="B710" s="6"/>
       <c r="C710" s="7"/>
@@ -21159,7 +22056,7 @@
       <c r="Y710" s="1"/>
       <c r="Z710" s="1"/>
     </row>
-    <row r="711" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A711" s="1"/>
       <c r="B711" s="6"/>
       <c r="C711" s="7"/>
@@ -21187,7 +22084,7 @@
       <c r="Y711" s="1"/>
       <c r="Z711" s="1"/>
     </row>
-    <row r="712" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A712" s="1"/>
       <c r="B712" s="6"/>
       <c r="C712" s="7"/>
@@ -21215,7 +22112,7 @@
       <c r="Y712" s="1"/>
       <c r="Z712" s="1"/>
     </row>
-    <row r="713" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A713" s="1"/>
       <c r="B713" s="6"/>
       <c r="C713" s="7"/>
@@ -21243,7 +22140,7 @@
       <c r="Y713" s="1"/>
       <c r="Z713" s="1"/>
     </row>
-    <row r="714" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A714" s="1"/>
       <c r="B714" s="6"/>
       <c r="C714" s="7"/>
@@ -21271,7 +22168,7 @@
       <c r="Y714" s="1"/>
       <c r="Z714" s="1"/>
     </row>
-    <row r="715" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A715" s="1"/>
       <c r="B715" s="6"/>
       <c r="C715" s="7"/>
@@ -21299,7 +22196,7 @@
       <c r="Y715" s="1"/>
       <c r="Z715" s="1"/>
     </row>
-    <row r="716" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A716" s="1"/>
       <c r="B716" s="6"/>
       <c r="C716" s="7"/>
@@ -21327,7 +22224,7 @@
       <c r="Y716" s="1"/>
       <c r="Z716" s="1"/>
     </row>
-    <row r="717" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A717" s="1"/>
       <c r="B717" s="6"/>
       <c r="C717" s="7"/>
@@ -21355,7 +22252,7 @@
       <c r="Y717" s="1"/>
       <c r="Z717" s="1"/>
     </row>
-    <row r="718" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A718" s="1"/>
       <c r="B718" s="6"/>
       <c r="C718" s="7"/>
@@ -21383,7 +22280,7 @@
       <c r="Y718" s="1"/>
       <c r="Z718" s="1"/>
     </row>
-    <row r="719" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A719" s="1"/>
       <c r="B719" s="6"/>
       <c r="C719" s="7"/>
@@ -21411,7 +22308,7 @@
       <c r="Y719" s="1"/>
       <c r="Z719" s="1"/>
     </row>
-    <row r="720" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A720" s="1"/>
       <c r="B720" s="6"/>
       <c r="C720" s="7"/>
@@ -21439,7 +22336,7 @@
       <c r="Y720" s="1"/>
       <c r="Z720" s="1"/>
     </row>
-    <row r="721" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A721" s="1"/>
       <c r="B721" s="6"/>
       <c r="C721" s="7"/>
@@ -21467,7 +22364,7 @@
       <c r="Y721" s="1"/>
       <c r="Z721" s="1"/>
     </row>
-    <row r="722" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A722" s="1"/>
       <c r="B722" s="6"/>
       <c r="C722" s="7"/>
@@ -21495,7 +22392,7 @@
       <c r="Y722" s="1"/>
       <c r="Z722" s="1"/>
     </row>
-    <row r="723" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A723" s="1"/>
       <c r="B723" s="6"/>
       <c r="C723" s="7"/>
@@ -21523,7 +22420,7 @@
       <c r="Y723" s="1"/>
       <c r="Z723" s="1"/>
     </row>
-    <row r="724" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A724" s="1"/>
       <c r="B724" s="6"/>
       <c r="C724" s="7"/>
@@ -21551,7 +22448,7 @@
       <c r="Y724" s="1"/>
       <c r="Z724" s="1"/>
     </row>
-    <row r="725" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A725" s="1"/>
       <c r="B725" s="6"/>
       <c r="C725" s="7"/>
@@ -21579,7 +22476,7 @@
       <c r="Y725" s="1"/>
       <c r="Z725" s="1"/>
     </row>
-    <row r="726" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A726" s="1"/>
       <c r="B726" s="6"/>
       <c r="C726" s="7"/>
@@ -21607,7 +22504,7 @@
       <c r="Y726" s="1"/>
       <c r="Z726" s="1"/>
     </row>
-    <row r="727" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A727" s="1"/>
       <c r="B727" s="6"/>
       <c r="C727" s="7"/>
@@ -21635,7 +22532,7 @@
       <c r="Y727" s="1"/>
       <c r="Z727" s="1"/>
     </row>
-    <row r="728" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A728" s="1"/>
       <c r="B728" s="6"/>
       <c r="C728" s="7"/>
@@ -21663,7 +22560,7 @@
       <c r="Y728" s="1"/>
       <c r="Z728" s="1"/>
     </row>
-    <row r="729" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A729" s="1"/>
       <c r="B729" s="6"/>
       <c r="C729" s="7"/>
@@ -21691,7 +22588,7 @@
       <c r="Y729" s="1"/>
       <c r="Z729" s="1"/>
     </row>
-    <row r="730" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A730" s="1"/>
       <c r="B730" s="6"/>
       <c r="C730" s="7"/>
@@ -21719,7 +22616,7 @@
       <c r="Y730" s="1"/>
       <c r="Z730" s="1"/>
     </row>
-    <row r="731" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A731" s="1"/>
       <c r="B731" s="6"/>
       <c r="C731" s="7"/>
@@ -21747,7 +22644,7 @@
       <c r="Y731" s="1"/>
       <c r="Z731" s="1"/>
     </row>
-    <row r="732" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A732" s="1"/>
       <c r="B732" s="6"/>
       <c r="C732" s="7"/>
@@ -21775,7 +22672,7 @@
       <c r="Y732" s="1"/>
       <c r="Z732" s="1"/>
     </row>
-    <row r="733" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A733" s="1"/>
       <c r="B733" s="6"/>
       <c r="C733" s="7"/>
@@ -21803,7 +22700,7 @@
       <c r="Y733" s="1"/>
       <c r="Z733" s="1"/>
     </row>
-    <row r="734" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A734" s="1"/>
       <c r="B734" s="6"/>
       <c r="C734" s="7"/>
@@ -21831,7 +22728,7 @@
       <c r="Y734" s="1"/>
       <c r="Z734" s="1"/>
     </row>
-    <row r="735" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A735" s="1"/>
       <c r="B735" s="6"/>
       <c r="C735" s="7"/>
@@ -21859,7 +22756,7 @@
       <c r="Y735" s="1"/>
       <c r="Z735" s="1"/>
     </row>
-    <row r="736" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A736" s="1"/>
       <c r="B736" s="6"/>
       <c r="C736" s="7"/>
@@ -21887,7 +22784,7 @@
       <c r="Y736" s="1"/>
       <c r="Z736" s="1"/>
     </row>
-    <row r="737" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A737" s="1"/>
       <c r="B737" s="6"/>
       <c r="C737" s="7"/>
@@ -21915,7 +22812,7 @@
       <c r="Y737" s="1"/>
       <c r="Z737" s="1"/>
     </row>
-    <row r="738" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A738" s="1"/>
       <c r="B738" s="6"/>
       <c r="C738" s="7"/>
@@ -21943,7 +22840,7 @@
       <c r="Y738" s="1"/>
       <c r="Z738" s="1"/>
     </row>
-    <row r="739" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A739" s="1"/>
       <c r="B739" s="6"/>
       <c r="C739" s="7"/>
@@ -21971,7 +22868,7 @@
       <c r="Y739" s="1"/>
       <c r="Z739" s="1"/>
     </row>
-    <row r="740" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A740" s="1"/>
       <c r="B740" s="6"/>
       <c r="C740" s="7"/>
@@ -21999,7 +22896,7 @@
       <c r="Y740" s="1"/>
       <c r="Z740" s="1"/>
     </row>
-    <row r="741" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A741" s="1"/>
       <c r="B741" s="6"/>
       <c r="C741" s="7"/>
@@ -22027,7 +22924,7 @@
       <c r="Y741" s="1"/>
       <c r="Z741" s="1"/>
     </row>
-    <row r="742" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A742" s="1"/>
       <c r="B742" s="6"/>
       <c r="C742" s="7"/>
@@ -22055,7 +22952,7 @@
       <c r="Y742" s="1"/>
       <c r="Z742" s="1"/>
     </row>
-    <row r="743" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A743" s="1"/>
       <c r="B743" s="6"/>
       <c r="C743" s="7"/>
@@ -22083,7 +22980,7 @@
       <c r="Y743" s="1"/>
       <c r="Z743" s="1"/>
     </row>
-    <row r="744" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A744" s="1"/>
       <c r="B744" s="6"/>
       <c r="C744" s="7"/>
@@ -22111,7 +23008,7 @@
       <c r="Y744" s="1"/>
       <c r="Z744" s="1"/>
     </row>
-    <row r="745" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A745" s="1"/>
       <c r="B745" s="6"/>
       <c r="C745" s="7"/>
@@ -22139,7 +23036,7 @@
       <c r="Y745" s="1"/>
       <c r="Z745" s="1"/>
     </row>
-    <row r="746" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A746" s="1"/>
       <c r="B746" s="6"/>
       <c r="C746" s="7"/>
@@ -22167,7 +23064,7 @@
       <c r="Y746" s="1"/>
       <c r="Z746" s="1"/>
     </row>
-    <row r="747" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A747" s="1"/>
       <c r="B747" s="6"/>
       <c r="C747" s="7"/>
@@ -22195,7 +23092,7 @@
       <c r="Y747" s="1"/>
       <c r="Z747" s="1"/>
     </row>
-    <row r="748" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A748" s="1"/>
       <c r="B748" s="6"/>
       <c r="C748" s="7"/>
@@ -22223,7 +23120,7 @@
       <c r="Y748" s="1"/>
       <c r="Z748" s="1"/>
     </row>
-    <row r="749" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A749" s="1"/>
       <c r="B749" s="6"/>
       <c r="C749" s="7"/>
@@ -22251,7 +23148,7 @@
       <c r="Y749" s="1"/>
       <c r="Z749" s="1"/>
     </row>
-    <row r="750" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A750" s="1"/>
       <c r="B750" s="6"/>
       <c r="C750" s="7"/>
@@ -22279,7 +23176,7 @@
       <c r="Y750" s="1"/>
       <c r="Z750" s="1"/>
     </row>
-    <row r="751" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A751" s="1"/>
       <c r="B751" s="6"/>
       <c r="C751" s="7"/>
@@ -22307,7 +23204,7 @@
       <c r="Y751" s="1"/>
       <c r="Z751" s="1"/>
     </row>
-    <row r="752" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A752" s="1"/>
       <c r="B752" s="6"/>
       <c r="C752" s="7"/>
@@ -22335,7 +23232,7 @@
       <c r="Y752" s="1"/>
       <c r="Z752" s="1"/>
     </row>
-    <row r="753" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A753" s="1"/>
       <c r="B753" s="6"/>
       <c r="C753" s="7"/>
@@ -22363,7 +23260,7 @@
       <c r="Y753" s="1"/>
       <c r="Z753" s="1"/>
     </row>
-    <row r="754" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A754" s="1"/>
       <c r="B754" s="6"/>
       <c r="C754" s="7"/>
@@ -22391,7 +23288,7 @@
       <c r="Y754" s="1"/>
       <c r="Z754" s="1"/>
     </row>
-    <row r="755" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A755" s="1"/>
       <c r="B755" s="6"/>
       <c r="C755" s="7"/>
@@ -22419,7 +23316,7 @@
       <c r="Y755" s="1"/>
       <c r="Z755" s="1"/>
     </row>
-    <row r="756" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A756" s="1"/>
       <c r="B756" s="6"/>
       <c r="C756" s="7"/>
@@ -22447,7 +23344,7 @@
       <c r="Y756" s="1"/>
       <c r="Z756" s="1"/>
     </row>
-    <row r="757" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A757" s="1"/>
       <c r="B757" s="6"/>
       <c r="C757" s="7"/>
@@ -22475,7 +23372,7 @@
       <c r="Y757" s="1"/>
       <c r="Z757" s="1"/>
     </row>
-    <row r="758" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A758" s="1"/>
       <c r="B758" s="6"/>
       <c r="C758" s="7"/>
@@ -22503,7 +23400,7 @@
       <c r="Y758" s="1"/>
       <c r="Z758" s="1"/>
     </row>
-    <row r="759" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A759" s="1"/>
       <c r="B759" s="6"/>
       <c r="C759" s="7"/>
@@ -22531,7 +23428,7 @@
       <c r="Y759" s="1"/>
       <c r="Z759" s="1"/>
     </row>
-    <row r="760" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A760" s="1"/>
       <c r="B760" s="6"/>
       <c r="C760" s="7"/>
@@ -22559,7 +23456,7 @@
       <c r="Y760" s="1"/>
       <c r="Z760" s="1"/>
     </row>
-    <row r="761" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A761" s="1"/>
       <c r="B761" s="6"/>
       <c r="C761" s="7"/>
@@ -22587,7 +23484,7 @@
       <c r="Y761" s="1"/>
       <c r="Z761" s="1"/>
     </row>
-    <row r="762" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A762" s="1"/>
       <c r="B762" s="6"/>
       <c r="C762" s="7"/>
@@ -22615,7 +23512,7 @@
       <c r="Y762" s="1"/>
       <c r="Z762" s="1"/>
     </row>
-    <row r="763" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A763" s="1"/>
       <c r="B763" s="6"/>
       <c r="C763" s="7"/>
@@ -22643,7 +23540,7 @@
       <c r="Y763" s="1"/>
       <c r="Z763" s="1"/>
     </row>
-    <row r="764" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A764" s="1"/>
       <c r="B764" s="6"/>
       <c r="C764" s="7"/>
@@ -22671,7 +23568,7 @@
       <c r="Y764" s="1"/>
       <c r="Z764" s="1"/>
     </row>
-    <row r="765" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A765" s="1"/>
       <c r="B765" s="6"/>
       <c r="C765" s="7"/>
@@ -22699,7 +23596,7 @@
       <c r="Y765" s="1"/>
       <c r="Z765" s="1"/>
     </row>
-    <row r="766" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A766" s="1"/>
       <c r="B766" s="6"/>
       <c r="C766" s="7"/>
@@ -22727,7 +23624,7 @@
       <c r="Y766" s="1"/>
       <c r="Z766" s="1"/>
     </row>
-    <row r="767" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A767" s="1"/>
       <c r="B767" s="6"/>
       <c r="C767" s="7"/>
@@ -22755,7 +23652,7 @@
       <c r="Y767" s="1"/>
       <c r="Z767" s="1"/>
     </row>
-    <row r="768" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A768" s="1"/>
       <c r="B768" s="6"/>
       <c r="C768" s="7"/>
@@ -22783,7 +23680,7 @@
       <c r="Y768" s="1"/>
       <c r="Z768" s="1"/>
     </row>
-    <row r="769" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A769" s="1"/>
       <c r="B769" s="6"/>
       <c r="C769" s="7"/>
@@ -22811,7 +23708,7 @@
       <c r="Y769" s="1"/>
       <c r="Z769" s="1"/>
     </row>
-    <row r="770" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A770" s="1"/>
       <c r="B770" s="6"/>
       <c r="C770" s="7"/>
@@ -22839,7 +23736,7 @@
       <c r="Y770" s="1"/>
       <c r="Z770" s="1"/>
     </row>
-    <row r="771" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A771" s="1"/>
       <c r="B771" s="6"/>
       <c r="C771" s="7"/>
@@ -22867,7 +23764,7 @@
       <c r="Y771" s="1"/>
       <c r="Z771" s="1"/>
     </row>
-    <row r="772" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A772" s="1"/>
       <c r="B772" s="6"/>
       <c r="C772" s="7"/>
@@ -22895,7 +23792,7 @@
       <c r="Y772" s="1"/>
       <c r="Z772" s="1"/>
     </row>
-    <row r="773" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A773" s="1"/>
       <c r="B773" s="6"/>
       <c r="C773" s="7"/>
@@ -22923,7 +23820,7 @@
       <c r="Y773" s="1"/>
       <c r="Z773" s="1"/>
     </row>
-    <row r="774" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A774" s="1"/>
       <c r="B774" s="6"/>
       <c r="C774" s="7"/>
@@ -22951,7 +23848,7 @@
       <c r="Y774" s="1"/>
       <c r="Z774" s="1"/>
     </row>
-    <row r="775" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A775" s="1"/>
       <c r="B775" s="6"/>
       <c r="C775" s="7"/>
@@ -22979,7 +23876,7 @@
       <c r="Y775" s="1"/>
       <c r="Z775" s="1"/>
     </row>
-    <row r="776" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A776" s="1"/>
       <c r="B776" s="6"/>
       <c r="C776" s="7"/>
@@ -23007,7 +23904,7 @@
       <c r="Y776" s="1"/>
       <c r="Z776" s="1"/>
     </row>
-    <row r="777" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A777" s="1"/>
       <c r="B777" s="6"/>
       <c r="C777" s="7"/>
@@ -23035,7 +23932,7 @@
       <c r="Y777" s="1"/>
       <c r="Z777" s="1"/>
     </row>
-    <row r="778" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A778" s="1"/>
       <c r="B778" s="6"/>
       <c r="D778" s="1"/>
@@ -23062,7 +23959,7 @@
       <c r="Y778" s="1"/>
       <c r="Z778" s="1"/>
     </row>
-    <row r="779" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A779" s="1"/>
       <c r="B779" s="6"/>
       <c r="D779" s="1"/>
@@ -23089,7 +23986,7 @@
       <c r="Y779" s="1"/>
       <c r="Z779" s="1"/>
     </row>
-    <row r="780" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A780" s="1"/>
       <c r="B780" s="6"/>
       <c r="D780" s="1"/>
@@ -23116,7 +24013,7 @@
       <c r="Y780" s="1"/>
       <c r="Z780" s="1"/>
     </row>
-    <row r="781" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A781" s="1"/>
       <c r="B781" s="6"/>
       <c r="D781" s="1"/>
@@ -23143,7 +24040,7 @@
       <c r="Y781" s="1"/>
       <c r="Z781" s="1"/>
     </row>
-    <row r="782" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A782" s="1"/>
       <c r="B782" s="6"/>
       <c r="D782" s="1"/>
@@ -23170,7 +24067,7 @@
       <c r="Y782" s="1"/>
       <c r="Z782" s="1"/>
     </row>
-    <row r="783" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A783" s="1"/>
       <c r="B783" s="6"/>
       <c r="D783" s="1"/>
@@ -23197,7 +24094,7 @@
       <c r="Y783" s="1"/>
       <c r="Z783" s="1"/>
     </row>
-    <row r="784" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A784" s="1"/>
       <c r="B784" s="6"/>
       <c r="D784" s="1"/>
@@ -23224,7 +24121,7 @@
       <c r="Y784" s="1"/>
       <c r="Z784" s="1"/>
     </row>
-    <row r="785" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A785" s="1"/>
       <c r="B785" s="6"/>
       <c r="D785" s="1"/>
@@ -23251,7 +24148,7 @@
       <c r="Y785" s="1"/>
       <c r="Z785" s="1"/>
     </row>
-    <row r="786" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A786" s="1"/>
       <c r="B786" s="6"/>
       <c r="D786" s="1"/>
@@ -23278,7 +24175,7 @@
       <c r="Y786" s="1"/>
       <c r="Z786" s="1"/>
     </row>
-    <row r="787" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A787" s="1"/>
       <c r="B787" s="6"/>
       <c r="D787" s="1"/>
@@ -23305,7 +24202,7 @@
       <c r="Y787" s="1"/>
       <c r="Z787" s="1"/>
     </row>
-    <row r="788" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A788" s="1"/>
       <c r="B788" s="6"/>
       <c r="D788" s="1"/>
@@ -23332,7 +24229,7 @@
       <c r="Y788" s="1"/>
       <c r="Z788" s="1"/>
     </row>
-    <row r="789" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A789" s="1"/>
       <c r="B789" s="6"/>
       <c r="D789" s="1"/>
@@ -23359,7 +24256,7 @@
       <c r="Y789" s="1"/>
       <c r="Z789" s="1"/>
     </row>
-    <row r="790" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A790" s="1"/>
       <c r="B790" s="6"/>
       <c r="D790" s="1"/>
@@ -23386,7 +24283,7 @@
       <c r="Y790" s="1"/>
       <c r="Z790" s="1"/>
     </row>
-    <row r="791" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A791" s="1"/>
       <c r="B791" s="6"/>
       <c r="D791" s="1"/>
@@ -23413,7 +24310,7 @@
       <c r="Y791" s="1"/>
       <c r="Z791" s="1"/>
     </row>
-    <row r="792" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A792" s="1"/>
       <c r="B792" s="6"/>
       <c r="D792" s="1"/>
@@ -23440,7 +24337,7 @@
       <c r="Y792" s="1"/>
       <c r="Z792" s="1"/>
     </row>
-    <row r="793" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A793" s="1"/>
       <c r="B793" s="6"/>
       <c r="D793" s="1"/>
@@ -23467,7 +24364,7 @@
       <c r="Y793" s="1"/>
       <c r="Z793" s="1"/>
     </row>
-    <row r="794" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A794" s="1"/>
       <c r="B794" s="6"/>
       <c r="D794" s="1"/>
@@ -23494,7 +24391,7 @@
       <c r="Y794" s="1"/>
       <c r="Z794" s="1"/>
     </row>
-    <row r="795" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A795" s="1"/>
       <c r="B795" s="6"/>
       <c r="D795" s="1"/>
@@ -23521,7 +24418,7 @@
       <c r="Y795" s="1"/>
       <c r="Z795" s="1"/>
     </row>
-    <row r="796" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A796" s="1"/>
       <c r="B796" s="6"/>
       <c r="D796" s="1"/>
@@ -23548,7 +24445,7 @@
       <c r="Y796" s="1"/>
       <c r="Z796" s="1"/>
     </row>
-    <row r="797" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A797" s="1"/>
       <c r="B797" s="6"/>
       <c r="D797" s="1"/>
@@ -23575,7 +24472,7 @@
       <c r="Y797" s="1"/>
       <c r="Z797" s="1"/>
     </row>
-    <row r="798" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A798" s="1"/>
       <c r="B798" s="6"/>
       <c r="D798" s="1"/>
@@ -23602,7 +24499,7 @@
       <c r="Y798" s="1"/>
       <c r="Z798" s="1"/>
     </row>
-    <row r="799" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A799" s="1"/>
       <c r="B799" s="6"/>
       <c r="D799" s="1"/>
@@ -23629,7 +24526,7 @@
       <c r="Y799" s="1"/>
       <c r="Z799" s="1"/>
     </row>
-    <row r="800" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="800" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A800" s="1"/>
       <c r="B800" s="6"/>
       <c r="D800" s="1"/>
@@ -23656,7 +24553,7 @@
       <c r="Y800" s="1"/>
       <c r="Z800" s="1"/>
     </row>
-    <row r="801" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A801" s="1"/>
       <c r="B801" s="6"/>
       <c r="D801" s="1"/>
@@ -23683,7 +24580,7 @@
       <c r="Y801" s="1"/>
       <c r="Z801" s="1"/>
     </row>
-    <row r="802" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A802" s="1"/>
       <c r="B802" s="6"/>
       <c r="D802" s="1"/>
@@ -23710,7 +24607,7 @@
       <c r="Y802" s="1"/>
       <c r="Z802" s="1"/>
     </row>
-    <row r="803" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A803" s="1"/>
       <c r="B803" s="6"/>
       <c r="D803" s="1"/>
@@ -23737,7 +24634,7 @@
       <c r="Y803" s="1"/>
       <c r="Z803" s="1"/>
     </row>
-    <row r="804" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="804" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A804" s="1"/>
       <c r="B804" s="6"/>
       <c r="D804" s="1"/>
@@ -23764,7 +24661,7 @@
       <c r="Y804" s="1"/>
       <c r="Z804" s="1"/>
     </row>
-    <row r="805" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A805" s="1"/>
       <c r="B805" s="6"/>
       <c r="D805" s="1"/>
@@ -23791,7 +24688,7 @@
       <c r="Y805" s="1"/>
       <c r="Z805" s="1"/>
     </row>
-    <row r="806" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A806" s="1"/>
       <c r="B806" s="6"/>
       <c r="D806" s="1"/>
@@ -23818,7 +24715,7 @@
       <c r="Y806" s="1"/>
       <c r="Z806" s="1"/>
     </row>
-    <row r="807" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A807" s="1"/>
       <c r="B807" s="6"/>
       <c r="D807" s="1"/>
@@ -23845,7 +24742,7 @@
       <c r="Y807" s="1"/>
       <c r="Z807" s="1"/>
     </row>
-    <row r="808" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A808" s="1"/>
       <c r="B808" s="6"/>
       <c r="D808" s="1"/>
@@ -23872,7 +24769,7 @@
       <c r="Y808" s="1"/>
       <c r="Z808" s="1"/>
     </row>
-    <row r="809" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A809" s="1"/>
       <c r="B809" s="6"/>
       <c r="D809" s="1"/>
@@ -23899,7 +24796,7 @@
       <c r="Y809" s="1"/>
       <c r="Z809" s="1"/>
     </row>
-    <row r="810" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A810" s="1"/>
       <c r="B810" s="6"/>
       <c r="D810" s="1"/>
@@ -23926,7 +24823,7 @@
       <c r="Y810" s="1"/>
       <c r="Z810" s="1"/>
     </row>
-    <row r="811" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A811" s="1"/>
       <c r="B811" s="6"/>
       <c r="D811" s="1"/>
@@ -23953,7 +24850,7 @@
       <c r="Y811" s="1"/>
       <c r="Z811" s="1"/>
     </row>
-    <row r="812" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="812" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A812" s="1"/>
       <c r="B812" s="6"/>
       <c r="D812" s="1"/>
@@ -23980,7 +24877,7 @@
       <c r="Y812" s="1"/>
       <c r="Z812" s="1"/>
     </row>
-    <row r="813" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A813" s="1"/>
       <c r="B813" s="6"/>
       <c r="D813" s="1"/>
@@ -24007,7 +24904,7 @@
       <c r="Y813" s="1"/>
       <c r="Z813" s="1"/>
     </row>
-    <row r="814" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="814" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A814" s="1"/>
       <c r="B814" s="6"/>
       <c r="D814" s="1"/>
@@ -24034,7 +24931,7 @@
       <c r="Y814" s="1"/>
       <c r="Z814" s="1"/>
     </row>
-    <row r="815" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A815" s="1"/>
       <c r="B815" s="6"/>
       <c r="D815" s="1"/>
@@ -24061,7 +24958,7 @@
       <c r="Y815" s="1"/>
       <c r="Z815" s="1"/>
     </row>
-    <row r="816" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="816" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A816" s="1"/>
       <c r="B816" s="6"/>
       <c r="D816" s="1"/>
@@ -24088,7 +24985,7 @@
       <c r="Y816" s="1"/>
       <c r="Z816" s="1"/>
     </row>
-    <row r="817" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="817" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A817" s="1"/>
       <c r="B817" s="6"/>
       <c r="D817" s="1"/>
@@ -24115,7 +25012,7 @@
       <c r="Y817" s="1"/>
       <c r="Z817" s="1"/>
     </row>
-    <row r="818" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="818" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A818" s="1"/>
       <c r="B818" s="6"/>
       <c r="D818" s="1"/>
@@ -24142,7 +25039,7 @@
       <c r="Y818" s="1"/>
       <c r="Z818" s="1"/>
     </row>
-    <row r="819" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="819" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A819" s="1"/>
       <c r="B819" s="6"/>
       <c r="D819" s="1"/>
@@ -24169,7 +25066,7 @@
       <c r="Y819" s="1"/>
       <c r="Z819" s="1"/>
     </row>
-    <row r="820" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="820" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A820" s="1"/>
       <c r="B820" s="6"/>
       <c r="D820" s="1"/>
@@ -24196,7 +25093,7 @@
       <c r="Y820" s="1"/>
       <c r="Z820" s="1"/>
     </row>
-    <row r="821" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A821" s="1"/>
       <c r="B821" s="6"/>
       <c r="D821" s="1"/>
@@ -24223,7 +25120,7 @@
       <c r="Y821" s="1"/>
       <c r="Z821" s="1"/>
     </row>
-    <row r="822" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="822" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A822" s="1"/>
       <c r="B822" s="6"/>
       <c r="D822" s="1"/>
@@ -24250,7 +25147,7 @@
       <c r="Y822" s="1"/>
       <c r="Z822" s="1"/>
     </row>
-    <row r="823" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="823" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A823" s="1"/>
       <c r="B823" s="6"/>
       <c r="D823" s="1"/>
@@ -24277,7 +25174,7 @@
       <c r="Y823" s="1"/>
       <c r="Z823" s="1"/>
     </row>
-    <row r="824" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A824" s="1"/>
       <c r="B824" s="6"/>
       <c r="D824" s="1"/>
@@ -24304,7 +25201,7 @@
       <c r="Y824" s="1"/>
       <c r="Z824" s="1"/>
     </row>
-    <row r="825" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A825" s="1"/>
       <c r="B825" s="6"/>
       <c r="D825" s="1"/>
@@ -24331,7 +25228,7 @@
       <c r="Y825" s="1"/>
       <c r="Z825" s="1"/>
     </row>
-    <row r="826" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A826" s="1"/>
       <c r="B826" s="6"/>
       <c r="D826" s="1"/>
@@ -24358,7 +25255,7 @@
       <c r="Y826" s="1"/>
       <c r="Z826" s="1"/>
     </row>
-    <row r="827" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A827" s="1"/>
       <c r="B827" s="6"/>
       <c r="D827" s="1"/>
@@ -24385,7 +25282,7 @@
       <c r="Y827" s="1"/>
       <c r="Z827" s="1"/>
     </row>
-    <row r="828" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A828" s="1"/>
       <c r="B828" s="6"/>
       <c r="D828" s="1"/>
@@ -24412,7 +25309,7 @@
       <c r="Y828" s="1"/>
       <c r="Z828" s="1"/>
     </row>
-    <row r="829" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A829" s="1"/>
       <c r="B829" s="6"/>
       <c r="D829" s="1"/>
@@ -24439,7 +25336,7 @@
       <c r="Y829" s="1"/>
       <c r="Z829" s="1"/>
     </row>
-    <row r="830" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="830" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A830" s="1"/>
       <c r="B830" s="6"/>
       <c r="D830" s="1"/>
@@ -24466,7 +25363,7 @@
       <c r="Y830" s="1"/>
       <c r="Z830" s="1"/>
     </row>
-    <row r="831" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A831" s="1"/>
       <c r="B831" s="6"/>
       <c r="D831" s="1"/>
@@ -24493,7 +25390,7 @@
       <c r="Y831" s="1"/>
       <c r="Z831" s="1"/>
     </row>
-    <row r="832" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="832" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A832" s="1"/>
       <c r="B832" s="6"/>
       <c r="D832" s="1"/>
@@ -24520,7 +25417,7 @@
       <c r="Y832" s="1"/>
       <c r="Z832" s="1"/>
     </row>
-    <row r="833" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A833" s="1"/>
       <c r="B833" s="6"/>
       <c r="D833" s="1"/>
@@ -24547,7 +25444,7 @@
       <c r="Y833" s="1"/>
       <c r="Z833" s="1"/>
     </row>
-    <row r="834" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="834" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A834" s="1"/>
       <c r="B834" s="6"/>
       <c r="D834" s="1"/>
@@ -24574,7 +25471,7 @@
       <c r="Y834" s="1"/>
       <c r="Z834" s="1"/>
     </row>
-    <row r="835" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="835" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A835" s="1"/>
       <c r="B835" s="6"/>
       <c r="D835" s="1"/>
@@ -24601,7 +25498,7 @@
       <c r="Y835" s="1"/>
       <c r="Z835" s="1"/>
     </row>
-    <row r="836" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="836" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A836" s="1"/>
       <c r="B836" s="6"/>
       <c r="D836" s="1"/>
@@ -24628,7 +25525,7 @@
       <c r="Y836" s="1"/>
       <c r="Z836" s="1"/>
     </row>
-    <row r="837" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="837" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A837" s="1"/>
       <c r="B837" s="6"/>
       <c r="D837" s="1"/>
@@ -24655,7 +25552,7 @@
       <c r="Y837" s="1"/>
       <c r="Z837" s="1"/>
     </row>
-    <row r="838" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="838" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A838" s="1"/>
       <c r="B838" s="6"/>
       <c r="D838" s="1"/>
@@ -24682,7 +25579,7 @@
       <c r="Y838" s="1"/>
       <c r="Z838" s="1"/>
     </row>
-    <row r="839" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="839" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A839" s="1"/>
       <c r="B839" s="6"/>
       <c r="D839" s="1"/>
@@ -24709,7 +25606,7 @@
       <c r="Y839" s="1"/>
       <c r="Z839" s="1"/>
     </row>
-    <row r="840" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="840" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A840" s="1"/>
       <c r="B840" s="6"/>
       <c r="D840" s="1"/>
@@ -24736,7 +25633,7 @@
       <c r="Y840" s="1"/>
       <c r="Z840" s="1"/>
     </row>
-    <row r="841" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="841" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A841" s="1"/>
       <c r="B841" s="6"/>
       <c r="D841" s="1"/>
@@ -24763,7 +25660,7 @@
       <c r="Y841" s="1"/>
       <c r="Z841" s="1"/>
     </row>
-    <row r="842" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="842" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A842" s="1"/>
       <c r="B842" s="6"/>
       <c r="D842" s="1"/>
@@ -24790,7 +25687,7 @@
       <c r="Y842" s="1"/>
       <c r="Z842" s="1"/>
     </row>
-    <row r="843" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="843" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A843" s="1"/>
       <c r="B843" s="6"/>
       <c r="D843" s="1"/>
@@ -24817,7 +25714,7 @@
       <c r="Y843" s="1"/>
       <c r="Z843" s="1"/>
     </row>
-    <row r="844" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="844" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A844" s="1"/>
       <c r="B844" s="6"/>
       <c r="D844" s="1"/>
@@ -24844,7 +25741,7 @@
       <c r="Y844" s="1"/>
       <c r="Z844" s="1"/>
     </row>
-    <row r="845" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="845" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A845" s="1"/>
       <c r="B845" s="6"/>
       <c r="D845" s="1"/>
@@ -24871,7 +25768,7 @@
       <c r="Y845" s="1"/>
       <c r="Z845" s="1"/>
     </row>
-    <row r="846" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="846" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A846" s="1"/>
       <c r="B846" s="6"/>
       <c r="D846" s="1"/>
@@ -24898,7 +25795,7 @@
       <c r="Y846" s="1"/>
       <c r="Z846" s="1"/>
     </row>
-    <row r="847" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="847" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A847" s="1"/>
       <c r="B847" s="6"/>
       <c r="D847" s="1"/>
@@ -24925,7 +25822,7 @@
       <c r="Y847" s="1"/>
       <c r="Z847" s="1"/>
     </row>
-    <row r="848" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="848" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A848" s="1"/>
       <c r="B848" s="6"/>
       <c r="D848" s="1"/>
@@ -24952,7 +25849,7 @@
       <c r="Y848" s="1"/>
       <c r="Z848" s="1"/>
     </row>
-    <row r="849" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="849" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A849" s="1"/>
       <c r="B849" s="6"/>
       <c r="D849" s="1"/>
@@ -24979,7 +25876,7 @@
       <c r="Y849" s="1"/>
       <c r="Z849" s="1"/>
     </row>
-    <row r="850" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="850" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A850" s="1"/>
       <c r="B850" s="6"/>
       <c r="D850" s="1"/>
@@ -25006,7 +25903,7 @@
       <c r="Y850" s="1"/>
       <c r="Z850" s="1"/>
     </row>
-    <row r="851" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="851" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A851" s="1"/>
       <c r="B851" s="6"/>
       <c r="D851" s="1"/>
@@ -25033,7 +25930,7 @@
       <c r="Y851" s="1"/>
       <c r="Z851" s="1"/>
     </row>
-    <row r="852" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="852" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A852" s="1"/>
       <c r="B852" s="6"/>
       <c r="D852" s="1"/>
@@ -25060,7 +25957,7 @@
       <c r="Y852" s="1"/>
       <c r="Z852" s="1"/>
     </row>
-    <row r="853" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="853" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A853" s="1"/>
       <c r="B853" s="6"/>
       <c r="D853" s="1"/>
@@ -25087,7 +25984,7 @@
       <c r="Y853" s="1"/>
       <c r="Z853" s="1"/>
     </row>
-    <row r="854" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="854" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A854" s="1"/>
       <c r="B854" s="6"/>
       <c r="D854" s="1"/>
@@ -25114,7 +26011,7 @@
       <c r="Y854" s="1"/>
       <c r="Z854" s="1"/>
     </row>
-    <row r="855" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="855" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A855" s="1"/>
       <c r="B855" s="6"/>
       <c r="D855" s="1"/>
@@ -25141,7 +26038,7 @@
       <c r="Y855" s="1"/>
       <c r="Z855" s="1"/>
     </row>
-    <row r="856" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="856" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A856" s="1"/>
       <c r="B856" s="6"/>
       <c r="D856" s="1"/>
@@ -25168,7 +26065,7 @@
       <c r="Y856" s="1"/>
       <c r="Z856" s="1"/>
     </row>
-    <row r="857" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="857" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A857" s="1"/>
       <c r="B857" s="6"/>
       <c r="D857" s="1"/>
@@ -25195,7 +26092,7 @@
       <c r="Y857" s="1"/>
       <c r="Z857" s="1"/>
     </row>
-    <row r="858" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="858" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A858" s="1"/>
       <c r="B858" s="6"/>
       <c r="D858" s="1"/>
@@ -25222,7 +26119,7 @@
       <c r="Y858" s="1"/>
       <c r="Z858" s="1"/>
     </row>
-    <row r="859" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="859" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A859" s="1"/>
       <c r="B859" s="6"/>
       <c r="D859" s="1"/>
@@ -25249,7 +26146,7 @@
       <c r="Y859" s="1"/>
       <c r="Z859" s="1"/>
     </row>
-    <row r="860" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="860" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A860" s="1"/>
       <c r="B860" s="6"/>
       <c r="D860" s="1"/>
@@ -25276,7 +26173,7 @@
       <c r="Y860" s="1"/>
       <c r="Z860" s="1"/>
     </row>
-    <row r="861" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="861" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A861" s="1"/>
       <c r="B861" s="6"/>
       <c r="D861" s="1"/>
@@ -25303,7 +26200,7 @@
       <c r="Y861" s="1"/>
       <c r="Z861" s="1"/>
     </row>
-    <row r="862" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="862" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A862" s="1"/>
       <c r="B862" s="6"/>
       <c r="D862" s="1"/>
@@ -25330,7 +26227,7 @@
       <c r="Y862" s="1"/>
       <c r="Z862" s="1"/>
     </row>
-    <row r="863" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="863" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A863" s="1"/>
       <c r="B863" s="6"/>
       <c r="D863" s="1"/>
@@ -25357,7 +26254,7 @@
       <c r="Y863" s="1"/>
       <c r="Z863" s="1"/>
     </row>
-    <row r="864" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="864" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A864" s="1"/>
       <c r="B864" s="6"/>
       <c r="D864" s="1"/>
@@ -25384,7 +26281,7 @@
       <c r="Y864" s="1"/>
       <c r="Z864" s="1"/>
     </row>
-    <row r="865" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="865" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A865" s="1"/>
       <c r="B865" s="6"/>
       <c r="D865" s="1"/>
@@ -25411,7 +26308,7 @@
       <c r="Y865" s="1"/>
       <c r="Z865" s="1"/>
     </row>
-    <row r="866" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="866" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A866" s="1"/>
       <c r="B866" s="6"/>
       <c r="D866" s="1"/>
@@ -25438,7 +26335,7 @@
       <c r="Y866" s="1"/>
       <c r="Z866" s="1"/>
     </row>
-    <row r="867" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="867" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A867" s="1"/>
       <c r="B867" s="6"/>
       <c r="D867" s="1"/>
@@ -25465,7 +26362,7 @@
       <c r="Y867" s="1"/>
       <c r="Z867" s="1"/>
     </row>
-    <row r="868" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="868" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A868" s="1"/>
       <c r="B868" s="6"/>
       <c r="D868" s="1"/>
@@ -25492,7 +26389,7 @@
       <c r="Y868" s="1"/>
       <c r="Z868" s="1"/>
     </row>
-    <row r="869" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="869" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A869" s="1"/>
       <c r="B869" s="6"/>
       <c r="D869" s="1"/>
@@ -25519,7 +26416,7 @@
       <c r="Y869" s="1"/>
       <c r="Z869" s="1"/>
     </row>
-    <row r="870" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="870" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A870" s="1"/>
       <c r="B870" s="6"/>
       <c r="D870" s="1"/>
@@ -25546,7 +26443,7 @@
       <c r="Y870" s="1"/>
       <c r="Z870" s="1"/>
     </row>
-    <row r="871" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="871" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A871" s="1"/>
       <c r="B871" s="6"/>
       <c r="D871" s="1"/>
@@ -25573,7 +26470,7 @@
       <c r="Y871" s="1"/>
       <c r="Z871" s="1"/>
     </row>
-    <row r="872" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="872" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A872" s="1"/>
       <c r="B872" s="6"/>
       <c r="D872" s="1"/>
@@ -25600,7 +26497,7 @@
       <c r="Y872" s="1"/>
       <c r="Z872" s="1"/>
     </row>
-    <row r="873" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="873" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A873" s="1"/>
       <c r="B873" s="6"/>
       <c r="D873" s="1"/>
@@ -25627,7 +26524,7 @@
       <c r="Y873" s="1"/>
       <c r="Z873" s="1"/>
     </row>
-    <row r="874" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="874" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A874" s="1"/>
       <c r="B874" s="6"/>
       <c r="D874" s="1"/>
@@ -25654,7 +26551,7 @@
       <c r="Y874" s="1"/>
       <c r="Z874" s="1"/>
     </row>
-    <row r="875" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="875" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A875" s="1"/>
       <c r="B875" s="6"/>
       <c r="D875" s="1"/>
@@ -25681,7 +26578,7 @@
       <c r="Y875" s="1"/>
       <c r="Z875" s="1"/>
     </row>
-    <row r="876" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="876" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A876" s="1"/>
       <c r="B876" s="6"/>
       <c r="D876" s="1"/>
@@ -25708,7 +26605,7 @@
       <c r="Y876" s="1"/>
       <c r="Z876" s="1"/>
     </row>
-    <row r="877" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="877" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A877" s="1"/>
       <c r="B877" s="6"/>
       <c r="D877" s="1"/>
@@ -25735,7 +26632,7 @@
       <c r="Y877" s="1"/>
       <c r="Z877" s="1"/>
     </row>
-    <row r="878" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="878" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A878" s="1"/>
       <c r="B878" s="6"/>
       <c r="D878" s="1"/>
@@ -25762,7 +26659,7 @@
       <c r="Y878" s="1"/>
       <c r="Z878" s="1"/>
     </row>
-    <row r="879" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="879" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A879" s="1"/>
       <c r="B879" s="6"/>
       <c r="D879" s="1"/>
@@ -25789,7 +26686,7 @@
       <c r="Y879" s="1"/>
       <c r="Z879" s="1"/>
     </row>
-    <row r="880" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="880" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A880" s="1"/>
       <c r="B880" s="6"/>
       <c r="D880" s="1"/>
@@ -25816,7 +26713,7 @@
       <c r="Y880" s="1"/>
       <c r="Z880" s="1"/>
     </row>
-    <row r="881" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="881" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A881" s="1"/>
       <c r="B881" s="6"/>
       <c r="D881" s="1"/>
@@ -25843,7 +26740,7 @@
       <c r="Y881" s="1"/>
       <c r="Z881" s="1"/>
     </row>
-    <row r="882" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="882" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A882" s="1"/>
       <c r="B882" s="6"/>
       <c r="D882" s="1"/>
@@ -25870,7 +26767,7 @@
       <c r="Y882" s="1"/>
       <c r="Z882" s="1"/>
     </row>
-    <row r="883" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="883" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A883" s="1"/>
       <c r="B883" s="6"/>
       <c r="D883" s="1"/>
@@ -25897,7 +26794,7 @@
       <c r="Y883" s="1"/>
       <c r="Z883" s="1"/>
     </row>
-    <row r="884" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="884" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A884" s="1"/>
       <c r="B884" s="6"/>
       <c r="D884" s="1"/>
@@ -25924,7 +26821,7 @@
       <c r="Y884" s="1"/>
       <c r="Z884" s="1"/>
     </row>
-    <row r="885" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="885" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A885" s="1"/>
       <c r="B885" s="6"/>
       <c r="D885" s="1"/>
@@ -25951,7 +26848,7 @@
       <c r="Y885" s="1"/>
       <c r="Z885" s="1"/>
     </row>
-    <row r="886" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="886" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A886" s="1"/>
       <c r="B886" s="6"/>
       <c r="D886" s="1"/>
@@ -25978,7 +26875,7 @@
       <c r="Y886" s="1"/>
       <c r="Z886" s="1"/>
     </row>
-    <row r="887" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="887" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A887" s="1"/>
       <c r="B887" s="6"/>
       <c r="D887" s="1"/>
@@ -26005,7 +26902,7 @@
       <c r="Y887" s="1"/>
       <c r="Z887" s="1"/>
     </row>
-    <row r="888" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="888" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A888" s="1"/>
       <c r="B888" s="6"/>
       <c r="D888" s="1"/>
@@ -26032,7 +26929,7 @@
       <c r="Y888" s="1"/>
       <c r="Z888" s="1"/>
     </row>
-    <row r="889" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="889" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A889" s="1"/>
       <c r="B889" s="6"/>
       <c r="D889" s="1"/>
@@ -26059,7 +26956,7 @@
       <c r="Y889" s="1"/>
       <c r="Z889" s="1"/>
     </row>
-    <row r="890" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="890" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A890" s="1"/>
       <c r="B890" s="6"/>
       <c r="D890" s="1"/>
@@ -26086,7 +26983,7 @@
       <c r="Y890" s="1"/>
       <c r="Z890" s="1"/>
     </row>
-    <row r="891" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="891" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A891" s="1"/>
       <c r="B891" s="6"/>
       <c r="D891" s="1"/>
@@ -26113,7 +27010,7 @@
       <c r="Y891" s="1"/>
       <c r="Z891" s="1"/>
     </row>
-    <row r="892" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="892" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A892" s="1"/>
       <c r="B892" s="6"/>
       <c r="D892" s="1"/>
@@ -26140,7 +27037,7 @@
       <c r="Y892" s="1"/>
       <c r="Z892" s="1"/>
     </row>
-    <row r="893" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="893" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A893" s="1"/>
       <c r="B893" s="6"/>
       <c r="D893" s="1"/>
@@ -26167,7 +27064,7 @@
       <c r="Y893" s="1"/>
       <c r="Z893" s="1"/>
     </row>
-    <row r="894" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="894" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A894" s="1"/>
       <c r="B894" s="6"/>
       <c r="D894" s="1"/>
@@ -26194,7 +27091,7 @@
       <c r="Y894" s="1"/>
       <c r="Z894" s="1"/>
     </row>
-    <row r="895" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="895" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A895" s="1"/>
       <c r="B895" s="6"/>
       <c r="D895" s="1"/>
@@ -26221,7 +27118,7 @@
       <c r="Y895" s="1"/>
       <c r="Z895" s="1"/>
     </row>
-    <row r="896" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="896" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A896" s="1"/>
       <c r="B896" s="6"/>
       <c r="D896" s="1"/>
@@ -26248,7 +27145,7 @@
       <c r="Y896" s="1"/>
       <c r="Z896" s="1"/>
     </row>
-    <row r="897" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="897" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A897" s="1"/>
       <c r="B897" s="6"/>
       <c r="D897" s="1"/>
@@ -26275,7 +27172,7 @@
       <c r="Y897" s="1"/>
       <c r="Z897" s="1"/>
     </row>
-    <row r="898" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="898" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A898" s="1"/>
       <c r="B898" s="6"/>
       <c r="D898" s="1"/>
@@ -26302,7 +27199,7 @@
       <c r="Y898" s="1"/>
       <c r="Z898" s="1"/>
     </row>
-    <row r="899" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="899" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A899" s="1"/>
       <c r="B899" s="6"/>
       <c r="D899" s="1"/>
@@ -26329,7 +27226,7 @@
       <c r="Y899" s="1"/>
       <c r="Z899" s="1"/>
     </row>
-    <row r="900" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="900" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A900" s="1"/>
       <c r="B900" s="6"/>
       <c r="D900" s="1"/>
@@ -26356,7 +27253,7 @@
       <c r="Y900" s="1"/>
       <c r="Z900" s="1"/>
     </row>
-    <row r="901" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="901" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A901" s="1"/>
       <c r="B901" s="6"/>
       <c r="D901" s="1"/>
@@ -26383,7 +27280,7 @@
       <c r="Y901" s="1"/>
       <c r="Z901" s="1"/>
     </row>
-    <row r="902" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="902" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A902" s="1"/>
       <c r="B902" s="6"/>
       <c r="D902" s="1"/>
@@ -26410,7 +27307,7 @@
       <c r="Y902" s="1"/>
       <c r="Z902" s="1"/>
     </row>
-    <row r="903" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="903" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A903" s="1"/>
       <c r="B903" s="6"/>
       <c r="D903" s="1"/>
@@ -26437,7 +27334,7 @@
       <c r="Y903" s="1"/>
       <c r="Z903" s="1"/>
     </row>
-    <row r="904" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="904" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A904" s="1"/>
       <c r="B904" s="6"/>
       <c r="D904" s="1"/>
@@ -26464,7 +27361,7 @@
       <c r="Y904" s="1"/>
       <c r="Z904" s="1"/>
     </row>
-    <row r="905" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="905" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A905" s="1"/>
       <c r="B905" s="6"/>
       <c r="D905" s="1"/>
@@ -26491,7 +27388,7 @@
       <c r="Y905" s="1"/>
       <c r="Z905" s="1"/>
     </row>
-    <row r="906" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="906" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A906" s="1"/>
       <c r="B906" s="6"/>
       <c r="D906" s="1"/>
@@ -26518,7 +27415,7 @@
       <c r="Y906" s="1"/>
       <c r="Z906" s="1"/>
     </row>
-    <row r="907" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="907" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A907" s="1"/>
       <c r="B907" s="6"/>
       <c r="D907" s="1"/>
@@ -26545,7 +27442,7 @@
       <c r="Y907" s="1"/>
       <c r="Z907" s="1"/>
     </row>
-    <row r="908" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="908" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A908" s="1"/>
       <c r="B908" s="6"/>
       <c r="D908" s="1"/>
@@ -26572,7 +27469,7 @@
       <c r="Y908" s="1"/>
       <c r="Z908" s="1"/>
     </row>
-    <row r="909" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="909" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A909" s="1"/>
       <c r="B909" s="6"/>
       <c r="D909" s="1"/>
@@ -26599,7 +27496,7 @@
       <c r="Y909" s="1"/>
       <c r="Z909" s="1"/>
     </row>
-    <row r="910" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="910" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A910" s="1"/>
       <c r="B910" s="6"/>
       <c r="D910" s="1"/>
@@ -26626,7 +27523,7 @@
       <c r="Y910" s="1"/>
       <c r="Z910" s="1"/>
     </row>
-    <row r="911" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="911" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A911" s="1"/>
       <c r="B911" s="6"/>
       <c r="D911" s="1"/>
@@ -26653,7 +27550,7 @@
       <c r="Y911" s="1"/>
       <c r="Z911" s="1"/>
     </row>
-    <row r="912" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="912" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A912" s="1"/>
       <c r="B912" s="6"/>
       <c r="D912" s="1"/>
@@ -26680,7 +27577,7 @@
       <c r="Y912" s="1"/>
       <c r="Z912" s="1"/>
     </row>
-    <row r="913" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="913" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A913" s="1"/>
       <c r="B913" s="6"/>
       <c r="D913" s="1"/>
@@ -26707,7 +27604,7 @@
       <c r="Y913" s="1"/>
       <c r="Z913" s="1"/>
     </row>
-    <row r="914" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="914" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A914" s="1"/>
       <c r="B914" s="6"/>
       <c r="D914" s="1"/>
@@ -26734,7 +27631,7 @@
       <c r="Y914" s="1"/>
       <c r="Z914" s="1"/>
     </row>
-    <row r="915" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="915" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A915" s="1"/>
       <c r="B915" s="6"/>
       <c r="D915" s="1"/>
@@ -26761,7 +27658,7 @@
       <c r="Y915" s="1"/>
       <c r="Z915" s="1"/>
     </row>
-    <row r="916" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="916" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A916" s="1"/>
       <c r="B916" s="6"/>
       <c r="D916" s="1"/>
@@ -26788,7 +27685,7 @@
       <c r="Y916" s="1"/>
       <c r="Z916" s="1"/>
     </row>
-    <row r="917" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="917" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A917" s="1"/>
       <c r="B917" s="6"/>
       <c r="D917" s="1"/>
@@ -26815,7 +27712,7 @@
       <c r="Y917" s="1"/>
       <c r="Z917" s="1"/>
     </row>
-    <row r="918" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="918" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A918" s="1"/>
       <c r="B918" s="6"/>
       <c r="D918" s="1"/>
@@ -26842,7 +27739,7 @@
       <c r="Y918" s="1"/>
       <c r="Z918" s="1"/>
     </row>
-    <row r="919" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="919" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A919" s="1"/>
       <c r="B919" s="6"/>
       <c r="D919" s="1"/>
@@ -26869,7 +27766,7 @@
       <c r="Y919" s="1"/>
       <c r="Z919" s="1"/>
     </row>
-    <row r="920" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="920" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A920" s="1"/>
       <c r="B920" s="6"/>
       <c r="D920" s="1"/>
@@ -26896,7 +27793,7 @@
       <c r="Y920" s="1"/>
       <c r="Z920" s="1"/>
     </row>
-    <row r="921" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="921" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A921" s="1"/>
       <c r="B921" s="6"/>
       <c r="D921" s="1"/>
@@ -26923,7 +27820,7 @@
       <c r="Y921" s="1"/>
       <c r="Z921" s="1"/>
     </row>
-    <row r="922" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="922" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A922" s="1"/>
       <c r="B922" s="6"/>
       <c r="D922" s="1"/>
@@ -26950,7 +27847,7 @@
       <c r="Y922" s="1"/>
       <c r="Z922" s="1"/>
     </row>
-    <row r="923" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="923" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A923" s="1"/>
       <c r="B923" s="6"/>
       <c r="D923" s="1"/>
@@ -26977,7 +27874,7 @@
       <c r="Y923" s="1"/>
       <c r="Z923" s="1"/>
     </row>
-    <row r="924" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="924" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A924" s="1"/>
       <c r="B924" s="6"/>
       <c r="D924" s="1"/>
@@ -27004,7 +27901,7 @@
       <c r="Y924" s="1"/>
       <c r="Z924" s="1"/>
     </row>
-    <row r="925" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="925" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A925" s="1"/>
       <c r="B925" s="6"/>
       <c r="D925" s="1"/>
@@ -27031,7 +27928,7 @@
       <c r="Y925" s="1"/>
       <c r="Z925" s="1"/>
     </row>
-    <row r="926" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="926" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A926" s="1"/>
       <c r="B926" s="6"/>
       <c r="D926" s="1"/>
@@ -27058,7 +27955,7 @@
       <c r="Y926" s="1"/>
       <c r="Z926" s="1"/>
     </row>
-    <row r="927" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="927" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A927" s="1"/>
       <c r="B927" s="6"/>
       <c r="D927" s="1"/>
@@ -27085,7 +27982,7 @@
       <c r="Y927" s="1"/>
       <c r="Z927" s="1"/>
     </row>
-    <row r="928" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="928" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A928" s="1"/>
       <c r="B928" s="6"/>
       <c r="D928" s="1"/>
@@ -27112,7 +28009,7 @@
       <c r="Y928" s="1"/>
       <c r="Z928" s="1"/>
     </row>
-    <row r="929" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="929" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A929" s="1"/>
       <c r="B929" s="6"/>
       <c r="D929" s="1"/>
@@ -27139,7 +28036,7 @@
       <c r="Y929" s="1"/>
       <c r="Z929" s="1"/>
     </row>
-    <row r="930" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="930" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A930" s="1"/>
       <c r="B930" s="6"/>
       <c r="D930" s="1"/>
@@ -27166,7 +28063,7 @@
       <c r="Y930" s="1"/>
       <c r="Z930" s="1"/>
     </row>
-    <row r="931" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="931" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A931" s="1"/>
       <c r="B931" s="6"/>
       <c r="D931" s="1"/>
@@ -27193,7 +28090,7 @@
       <c r="Y931" s="1"/>
       <c r="Z931" s="1"/>
     </row>
-    <row r="932" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="932" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A932" s="1"/>
       <c r="B932" s="6"/>
       <c r="D932" s="1"/>
@@ -27220,7 +28117,7 @@
       <c r="Y932" s="1"/>
       <c r="Z932" s="1"/>
     </row>
-    <row r="933" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="933" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A933" s="1"/>
       <c r="B933" s="6"/>
       <c r="D933" s="1"/>
@@ -27247,7 +28144,7 @@
       <c r="Y933" s="1"/>
       <c r="Z933" s="1"/>
     </row>
-    <row r="934" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="934" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A934" s="1"/>
       <c r="B934" s="6"/>
       <c r="D934" s="1"/>
@@ -27274,7 +28171,7 @@
       <c r="Y934" s="1"/>
       <c r="Z934" s="1"/>
     </row>
-    <row r="935" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="935" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A935" s="1"/>
       <c r="B935" s="6"/>
       <c r="D935" s="1"/>
@@ -27301,7 +28198,7 @@
       <c r="Y935" s="1"/>
       <c r="Z935" s="1"/>
     </row>
-    <row r="936" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="936" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A936" s="1"/>
       <c r="B936" s="6"/>
       <c r="D936" s="1"/>
@@ -27328,7 +28225,7 @@
       <c r="Y936" s="1"/>
       <c r="Z936" s="1"/>
     </row>
-    <row r="937" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="937" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A937" s="1"/>
       <c r="B937" s="6"/>
       <c r="D937" s="1"/>
@@ -27355,7 +28252,7 @@
       <c r="Y937" s="1"/>
       <c r="Z937" s="1"/>
     </row>
-    <row r="938" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="938" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A938" s="1"/>
       <c r="B938" s="6"/>
       <c r="D938" s="1"/>
@@ -27382,7 +28279,7 @@
       <c r="Y938" s="1"/>
       <c r="Z938" s="1"/>
     </row>
-    <row r="939" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="939" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A939" s="1"/>
       <c r="B939" s="6"/>
       <c r="D939" s="1"/>
@@ -27409,7 +28306,7 @@
       <c r="Y939" s="1"/>
       <c r="Z939" s="1"/>
     </row>
-    <row r="940" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="940" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A940" s="1"/>
       <c r="B940" s="6"/>
       <c r="D940" s="1"/>
@@ -27436,7 +28333,7 @@
       <c r="Y940" s="1"/>
       <c r="Z940" s="1"/>
     </row>
-    <row r="941" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="941" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A941" s="1"/>
       <c r="B941" s="6"/>
       <c r="D941" s="1"/>
@@ -27463,7 +28360,7 @@
       <c r="Y941" s="1"/>
       <c r="Z941" s="1"/>
     </row>
-    <row r="942" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="942" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A942" s="1"/>
       <c r="B942" s="6"/>
       <c r="D942" s="1"/>
@@ -27490,7 +28387,7 @@
       <c r="Y942" s="1"/>
       <c r="Z942" s="1"/>
     </row>
-    <row r="943" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="943" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A943" s="1"/>
       <c r="B943" s="6"/>
       <c r="D943" s="1"/>
@@ -27517,7 +28414,7 @@
       <c r="Y943" s="1"/>
       <c r="Z943" s="1"/>
     </row>
-    <row r="944" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="944" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A944" s="1"/>
       <c r="B944" s="6"/>
       <c r="D944" s="1"/>
@@ -27544,7 +28441,7 @@
       <c r="Y944" s="1"/>
       <c r="Z944" s="1"/>
     </row>
-    <row r="945" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="945" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A945" s="1"/>
       <c r="B945" s="6"/>
       <c r="D945" s="1"/>
@@ -27571,7 +28468,7 @@
       <c r="Y945" s="1"/>
       <c r="Z945" s="1"/>
     </row>
-    <row r="946" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="946" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A946" s="1"/>
       <c r="B946" s="6"/>
       <c r="D946" s="1"/>
@@ -27598,7 +28495,7 @@
       <c r="Y946" s="1"/>
       <c r="Z946" s="1"/>
     </row>
-    <row r="947" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="947" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A947" s="1"/>
       <c r="B947" s="6"/>
       <c r="D947" s="1"/>
@@ -27625,7 +28522,7 @@
       <c r="Y947" s="1"/>
       <c r="Z947" s="1"/>
     </row>
-    <row r="948" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="948" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A948" s="1"/>
       <c r="B948" s="6"/>
       <c r="D948" s="1"/>
@@ -27652,7 +28549,7 @@
       <c r="Y948" s="1"/>
       <c r="Z948" s="1"/>
     </row>
-    <row r="949" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="949" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A949" s="1"/>
       <c r="B949" s="6"/>
       <c r="D949" s="1"/>
@@ -27679,7 +28576,7 @@
       <c r="Y949" s="1"/>
       <c r="Z949" s="1"/>
     </row>
-    <row r="950" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="950" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A950" s="1"/>
       <c r="B950" s="6"/>
       <c r="D950" s="1"/>
@@ -27706,7 +28603,7 @@
       <c r="Y950" s="1"/>
       <c r="Z950" s="1"/>
     </row>
-    <row r="951" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="951" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A951" s="1"/>
       <c r="B951" s="6"/>
       <c r="D951" s="1"/>
@@ -27733,7 +28630,7 @@
       <c r="Y951" s="1"/>
       <c r="Z951" s="1"/>
     </row>
-    <row r="952" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="952" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A952" s="1"/>
       <c r="B952" s="6"/>
       <c r="D952" s="1"/>
@@ -27760,7 +28657,7 @@
       <c r="Y952" s="1"/>
       <c r="Z952" s="1"/>
     </row>
-    <row r="953" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="953" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A953" s="1"/>
       <c r="B953" s="6"/>
       <c r="D953" s="1"/>
@@ -27787,7 +28684,7 @@
       <c r="Y953" s="1"/>
       <c r="Z953" s="1"/>
     </row>
-    <row r="954" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="954" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A954" s="1"/>
       <c r="B954" s="6"/>
       <c r="D954" s="1"/>
@@ -27814,7 +28711,7 @@
       <c r="Y954" s="1"/>
       <c r="Z954" s="1"/>
     </row>
-    <row r="955" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="955" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A955" s="1"/>
       <c r="B955" s="6"/>
       <c r="D955" s="1"/>
@@ -27841,7 +28738,7 @@
       <c r="Y955" s="1"/>
       <c r="Z955" s="1"/>
     </row>
-    <row r="956" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="956" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A956" s="1"/>
       <c r="B956" s="6"/>
       <c r="D956" s="1"/>
@@ -27868,7 +28765,7 @@
       <c r="Y956" s="1"/>
       <c r="Z956" s="1"/>
     </row>
-    <row r="957" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="957" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A957" s="1"/>
       <c r="B957" s="6"/>
       <c r="D957" s="1"/>
@@ -27895,7 +28792,7 @@
       <c r="Y957" s="1"/>
       <c r="Z957" s="1"/>
     </row>
-    <row r="958" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="958" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A958" s="1"/>
       <c r="B958" s="6"/>
       <c r="D958" s="1"/>
@@ -27922,7 +28819,7 @@
       <c r="Y958" s="1"/>
       <c r="Z958" s="1"/>
     </row>
-    <row r="959" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="959" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A959" s="1"/>
       <c r="B959" s="6"/>
       <c r="D959" s="1"/>
@@ -27949,7 +28846,7 @@
       <c r="Y959" s="1"/>
       <c r="Z959" s="1"/>
     </row>
-    <row r="960" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="960" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A960" s="1"/>
       <c r="B960" s="6"/>
       <c r="D960" s="1"/>
@@ -27976,7 +28873,7 @@
       <c r="Y960" s="1"/>
       <c r="Z960" s="1"/>
     </row>
-    <row r="961" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="961" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A961" s="1"/>
       <c r="B961" s="6"/>
       <c r="D961" s="1"/>
@@ -28003,7 +28900,7 @@
       <c r="Y961" s="1"/>
       <c r="Z961" s="1"/>
     </row>
-    <row r="962" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="962" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A962" s="1"/>
       <c r="B962" s="6"/>
       <c r="D962" s="1"/>
@@ -28030,7 +28927,7 @@
       <c r="Y962" s="1"/>
       <c r="Z962" s="1"/>
     </row>
-    <row r="963" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="963" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A963" s="1"/>
       <c r="B963" s="6"/>
       <c r="D963" s="1"/>
@@ -28057,7 +28954,7 @@
       <c r="Y963" s="1"/>
       <c r="Z963" s="1"/>
     </row>
-    <row r="964" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="964" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A964" s="1"/>
       <c r="B964" s="6"/>
       <c r="D964" s="1"/>
@@ -28084,7 +28981,7 @@
       <c r="Y964" s="1"/>
       <c r="Z964" s="1"/>
     </row>
-    <row r="965" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="965" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A965" s="1"/>
       <c r="B965" s="6"/>
       <c r="D965" s="1"/>
@@ -28111,7 +29008,7 @@
       <c r="Y965" s="1"/>
       <c r="Z965" s="1"/>
     </row>
-    <row r="966" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="966" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A966" s="1"/>
       <c r="B966" s="6"/>
       <c r="D966" s="1"/>
@@ -28138,7 +29035,7 @@
       <c r="Y966" s="1"/>
       <c r="Z966" s="1"/>
     </row>
-    <row r="967" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="967" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A967" s="1"/>
       <c r="B967" s="6"/>
       <c r="D967" s="1"/>
@@ -28165,7 +29062,7 @@
       <c r="Y967" s="1"/>
       <c r="Z967" s="1"/>
     </row>
-    <row r="968" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="968" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A968" s="1"/>
       <c r="B968" s="6"/>
       <c r="D968" s="1"/>
@@ -28192,7 +29089,7 @@
       <c r="Y968" s="1"/>
       <c r="Z968" s="1"/>
     </row>
-    <row r="969" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="969" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A969" s="1"/>
       <c r="B969" s="6"/>
       <c r="D969" s="1"/>
@@ -28219,7 +29116,7 @@
       <c r="Y969" s="1"/>
       <c r="Z969" s="1"/>
     </row>
-    <row r="970" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="970" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A970" s="1"/>
       <c r="B970" s="6"/>
       <c r="D970" s="1"/>
@@ -28246,7 +29143,7 @@
       <c r="Y970" s="1"/>
       <c r="Z970" s="1"/>
     </row>
-    <row r="971" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="971" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A971" s="1"/>
       <c r="B971" s="6"/>
       <c r="D971" s="1"/>
@@ -28273,7 +29170,7 @@
       <c r="Y971" s="1"/>
       <c r="Z971" s="1"/>
     </row>
-    <row r="972" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="972" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A972" s="1"/>
       <c r="B972" s="6"/>
       <c r="D972" s="1"/>
@@ -28300,7 +29197,7 @@
       <c r="Y972" s="1"/>
       <c r="Z972" s="1"/>
     </row>
-    <row r="973" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="973" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A973" s="1"/>
       <c r="B973" s="6"/>
       <c r="D973" s="1"/>
@@ -28327,7 +29224,7 @@
       <c r="Y973" s="1"/>
       <c r="Z973" s="1"/>
     </row>
-    <row r="974" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="974" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A974" s="1"/>
       <c r="B974" s="6"/>
       <c r="D974" s="1"/>
@@ -28354,7 +29251,7 @@
       <c r="Y974" s="1"/>
       <c r="Z974" s="1"/>
     </row>
-    <row r="975" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="975" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A975" s="1"/>
       <c r="B975" s="6"/>
       <c r="D975" s="1"/>
@@ -28381,7 +29278,7 @@
       <c r="Y975" s="1"/>
       <c r="Z975" s="1"/>
     </row>
-    <row r="976" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="976" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A976" s="1"/>
       <c r="B976" s="6"/>
       <c r="D976" s="1"/>
@@ -28408,7 +29305,7 @@
       <c r="Y976" s="1"/>
       <c r="Z976" s="1"/>
     </row>
-    <row r="977" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="977" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A977" s="1"/>
       <c r="B977" s="6"/>
       <c r="D977" s="1"/>
@@ -28435,7 +29332,7 @@
       <c r="Y977" s="1"/>
       <c r="Z977" s="1"/>
     </row>
-    <row r="978" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="978" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A978" s="1"/>
       <c r="B978" s="6"/>
       <c r="D978" s="1"/>
@@ -28462,7 +29359,7 @@
       <c r="Y978" s="1"/>
       <c r="Z978" s="1"/>
     </row>
-    <row r="979" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="979" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A979" s="1"/>
       <c r="B979" s="6"/>
       <c r="D979" s="1"/>
@@ -28489,7 +29386,7 @@
       <c r="Y979" s="1"/>
       <c r="Z979" s="1"/>
     </row>
-    <row r="980" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="980" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A980" s="1"/>
       <c r="B980" s="6"/>
       <c r="D980" s="1"/>
@@ -28516,7 +29413,7 @@
       <c r="Y980" s="1"/>
       <c r="Z980" s="1"/>
     </row>
-    <row r="981" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="981" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A981" s="1"/>
       <c r="B981" s="6"/>
       <c r="D981" s="1"/>
@@ -28543,7 +29440,7 @@
       <c r="Y981" s="1"/>
       <c r="Z981" s="1"/>
     </row>
-    <row r="982" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="982" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A982" s="1"/>
       <c r="B982" s="6"/>
       <c r="D982" s="1"/>
@@ -28570,7 +29467,7 @@
       <c r="Y982" s="1"/>
       <c r="Z982" s="1"/>
     </row>
-    <row r="983" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="983" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A983" s="1"/>
       <c r="B983" s="6"/>
       <c r="D983" s="1"/>
@@ -28597,7 +29494,7 @@
       <c r="Y983" s="1"/>
       <c r="Z983" s="1"/>
     </row>
-    <row r="984" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="984" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A984" s="1"/>
       <c r="B984" s="6"/>
       <c r="D984" s="1"/>
@@ -28624,7 +29521,7 @@
       <c r="Y984" s="1"/>
       <c r="Z984" s="1"/>
     </row>
-    <row r="985" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="985" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A985" s="1"/>
       <c r="B985" s="6"/>
       <c r="D985" s="1"/>
@@ -28651,7 +29548,7 @@
       <c r="Y985" s="1"/>
       <c r="Z985" s="1"/>
     </row>
-    <row r="986" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="986" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A986" s="1"/>
       <c r="B986" s="6"/>
       <c r="D986" s="1"/>
@@ -28678,7 +29575,7 @@
       <c r="Y986" s="1"/>
       <c r="Z986" s="1"/>
     </row>
-    <row r="987" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="987" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A987" s="1"/>
       <c r="B987" s="6"/>
       <c r="D987" s="1"/>
@@ -28705,7 +29602,7 @@
       <c r="Y987" s="1"/>
       <c r="Z987" s="1"/>
     </row>
-    <row r="988" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="988" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A988" s="1"/>
       <c r="B988" s="6"/>
       <c r="D988" s="1"/>
@@ -28732,7 +29629,7 @@
       <c r="Y988" s="1"/>
       <c r="Z988" s="1"/>
     </row>
-    <row r="989" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="989" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A989" s="1"/>
       <c r="B989" s="6"/>
       <c r="D989" s="1"/>
@@ -28759,7 +29656,7 @@
       <c r="Y989" s="1"/>
       <c r="Z989" s="1"/>
     </row>
-    <row r="990" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="990" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A990" s="1"/>
       <c r="B990" s="6"/>
       <c r="D990" s="1"/>
@@ -28786,7 +29683,7 @@
       <c r="Y990" s="1"/>
       <c r="Z990" s="1"/>
     </row>
-    <row r="991" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="991" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A991" s="1"/>
       <c r="B991" s="6"/>
       <c r="D991" s="1"/>
@@ -28813,7 +29710,7 @@
       <c r="Y991" s="1"/>
       <c r="Z991" s="1"/>
     </row>
-    <row r="992" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="992" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A992" s="1"/>
       <c r="B992" s="6"/>
       <c r="D992" s="1"/>
@@ -28840,7 +29737,7 @@
       <c r="Y992" s="1"/>
       <c r="Z992" s="1"/>
     </row>
-    <row r="993" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="993" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A993" s="1"/>
       <c r="B993" s="6"/>
       <c r="D993" s="1"/>
@@ -28867,7 +29764,7 @@
       <c r="Y993" s="1"/>
       <c r="Z993" s="1"/>
     </row>
-    <row r="994" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="994" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A994" s="1"/>
       <c r="B994" s="6"/>
       <c r="D994" s="1"/>
@@ -28894,7 +29791,7 @@
       <c r="Y994" s="1"/>
       <c r="Z994" s="1"/>
     </row>
-    <row r="995" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="995" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A995" s="1"/>
       <c r="B995" s="6"/>
       <c r="D995" s="1"/>
@@ -28921,7 +29818,7 @@
       <c r="Y995" s="1"/>
       <c r="Z995" s="1"/>
     </row>
-    <row r="996" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="996" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A996" s="1"/>
       <c r="B996" s="6"/>
       <c r="D996" s="1"/>
@@ -28948,7 +29845,7 @@
       <c r="Y996" s="1"/>
       <c r="Z996" s="1"/>
     </row>
-    <row r="997" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="997" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A997" s="1"/>
       <c r="B997" s="6"/>
       <c r="D997" s="1"/>
@@ -28975,7 +29872,7 @@
       <c r="Y997" s="1"/>
       <c r="Z997" s="1"/>
     </row>
-    <row r="998" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="998" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A998" s="1"/>
       <c r="B998" s="6"/>
       <c r="D998" s="1"/>
@@ -29002,7 +29899,7 @@
       <c r="Y998" s="1"/>
       <c r="Z998" s="1"/>
     </row>
-    <row r="999" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="999" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A999" s="1"/>
       <c r="B999" s="6"/>
       <c r="D999" s="1"/>
@@ -29029,7 +29926,7 @@
       <c r="Y999" s="1"/>
       <c r="Z999" s="1"/>
     </row>
-    <row r="1000" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="1000" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A1000" s="1"/>
       <c r="B1000" s="6"/>
       <c r="D1000" s="1"/>
@@ -29056,7 +29953,7 @@
       <c r="Y1000" s="1"/>
       <c r="Z1000" s="1"/>
     </row>
-    <row r="1001" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="1001" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A1001" s="1"/>
       <c r="B1001" s="6"/>
       <c r="D1001" s="1"/>
